--- a/CapStone Project/Capstone Resources/Capstone 2 Resources/Gantt Chart Capstone.xlsx
+++ b/CapStone Project/Capstone Resources/Capstone 2 Resources/Gantt Chart Capstone.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72DA9E93-D7CB-4D04-8D60-BE2F16EF5B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{72DA9E93-D7CB-4D04-8D60-BE2F16EF5B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EF4C701-CAC1-41DA-8AA9-34DE0D3066A2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="602" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectSchedule" sheetId="11" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <definedName name="task_start" localSheetId="0">ProjectSchedule!$E1</definedName>
     <definedName name="today" localSheetId="0">TODAY()</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="71">
   <si>
     <t>Create a Project Schedule in this worksheet.
 Enter title of this project in cell B1. 
@@ -178,9 +178,6 @@
     <t>Capstone 2</t>
   </si>
   <si>
-    <t>Start of Classes</t>
-  </si>
-  <si>
     <t>Marcus  &amp; Liam</t>
   </si>
   <si>
@@ -191,9 +188,6 @@
   </si>
   <si>
     <t>App Research/Learning Code (Swift, X)</t>
-  </si>
-  <si>
-    <t>Victoria Day/School Closed</t>
   </si>
   <si>
     <t>Leaning Code (Swift, X)</t>
@@ -214,16 +208,10 @@
     <t>Leaning More Targeted Code (Swift, X)</t>
   </si>
   <si>
-    <t>June Day/School Closed</t>
-  </si>
-  <si>
     <t>Using Machine Learning With Xcode</t>
   </si>
   <si>
     <t>Sprint 2</t>
-  </si>
-  <si>
-    <t>Canada Day/School Clased</t>
   </si>
   <si>
     <t>Creating the App</t>
@@ -245,9 +233,6 @@
   </si>
   <si>
     <t>Complete Presentation</t>
-  </si>
-  <si>
-    <t>Exam Period</t>
   </si>
   <si>
     <t>Insert new rows ABOVE this one</t>
@@ -315,7 +300,7 @@
     <numFmt numFmtId="167" formatCode="d"/>
     <numFmt numFmtId="168" formatCode="[$-409]d/mmm/yy;@"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -894,6 +879,9 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -903,19 +891,16 @@
     <xf numFmtId="166" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="3" xfId="9" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="3" xfId="9" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
@@ -932,7 +917,72 @@
     <cellStyle name="Title" xfId="5" builtinId="15" customBuiltin="1"/>
     <cellStyle name="zHiddenText" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="22">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1008,105 +1058,6 @@
           <bgColor theme="0" tint="-0.34998626667073579"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <border>
@@ -1204,15 +1155,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="ToDoList" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="24"/>
-      <tableStyleElement type="headerRow" dxfId="23"/>
-      <tableStyleElement type="totalRow" dxfId="22"/>
-      <tableStyleElement type="firstColumn" dxfId="21"/>
-      <tableStyleElement type="lastColumn" dxfId="20"/>
-      <tableStyleElement type="firstRowStripe" dxfId="19"/>
-      <tableStyleElement type="secondRowStripe" dxfId="18"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="17"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="16"/>
+      <tableStyleElement type="wholeTable" dxfId="21"/>
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="totalRow" dxfId="19"/>
+      <tableStyleElement type="firstColumn" dxfId="18"/>
+      <tableStyleElement type="lastColumn" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="secondRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="13"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -1627,8 +1578,8 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:NA51"/>
-  <sheetFormatPr defaultRowHeight="30" customHeight="1"/>
+  <dimension ref="A1:NA45"/>
+  <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="41" customWidth="1"/>
     <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
@@ -1641,7 +1592,7 @@
     <col min="9" max="365" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:365" ht="30" customHeight="1">
+    <row r="1" spans="1:365" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
@@ -1655,7 +1606,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="14"/>
     </row>
-    <row r="2" spans="1:365" ht="30" customHeight="1">
+    <row r="2" spans="1:365" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="41" t="s">
         <v>2</v>
       </c>
@@ -1664,543 +1615,543 @@
       </c>
       <c r="I2" s="44"/>
     </row>
-    <row r="3" spans="1:365" ht="30" customHeight="1">
+    <row r="3" spans="1:365" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="48"/>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="76"/>
-      <c r="E3" s="77">
+      <c r="D3" s="77"/>
+      <c r="E3" s="75">
         <v>45909</v>
       </c>
-      <c r="F3" s="77"/>
+      <c r="F3" s="75"/>
     </row>
-    <row r="4" spans="1:365" ht="30" customHeight="1">
+    <row r="4" spans="1:365" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="75" t="s">
+      <c r="C4" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="76"/>
+      <c r="D4" s="77"/>
       <c r="E4" s="7">
         <v>36</v>
       </c>
-      <c r="I4" s="71">
+      <c r="I4" s="72">
         <f>I5</f>
         <v>46153</v>
       </c>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="71">
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="72">
         <f>P5</f>
         <v>46160</v>
       </c>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="72"/>
-      <c r="T4" s="72"/>
-      <c r="U4" s="72"/>
-      <c r="V4" s="73"/>
-      <c r="W4" s="71">
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="74"/>
+      <c r="W4" s="72">
         <f>W5</f>
         <v>46167</v>
       </c>
-      <c r="X4" s="72"/>
-      <c r="Y4" s="72"/>
-      <c r="Z4" s="72"/>
-      <c r="AA4" s="72"/>
-      <c r="AB4" s="72"/>
-      <c r="AC4" s="73"/>
-      <c r="AD4" s="71">
+      <c r="X4" s="73"/>
+      <c r="Y4" s="73"/>
+      <c r="Z4" s="73"/>
+      <c r="AA4" s="73"/>
+      <c r="AB4" s="73"/>
+      <c r="AC4" s="74"/>
+      <c r="AD4" s="72">
         <f>AD5</f>
         <v>46174</v>
       </c>
-      <c r="AE4" s="72"/>
-      <c r="AF4" s="72"/>
-      <c r="AG4" s="72"/>
-      <c r="AH4" s="72"/>
-      <c r="AI4" s="72"/>
-      <c r="AJ4" s="73"/>
-      <c r="AK4" s="71">
+      <c r="AE4" s="73"/>
+      <c r="AF4" s="73"/>
+      <c r="AG4" s="73"/>
+      <c r="AH4" s="73"/>
+      <c r="AI4" s="73"/>
+      <c r="AJ4" s="74"/>
+      <c r="AK4" s="72">
         <f>AK5</f>
         <v>46181</v>
       </c>
-      <c r="AL4" s="72"/>
-      <c r="AM4" s="72"/>
-      <c r="AN4" s="72"/>
-      <c r="AO4" s="72"/>
-      <c r="AP4" s="72"/>
-      <c r="AQ4" s="73"/>
-      <c r="AR4" s="71">
+      <c r="AL4" s="73"/>
+      <c r="AM4" s="73"/>
+      <c r="AN4" s="73"/>
+      <c r="AO4" s="73"/>
+      <c r="AP4" s="73"/>
+      <c r="AQ4" s="74"/>
+      <c r="AR4" s="72">
         <f>AR5</f>
         <v>46188</v>
       </c>
-      <c r="AS4" s="72"/>
-      <c r="AT4" s="72"/>
-      <c r="AU4" s="72"/>
-      <c r="AV4" s="72"/>
-      <c r="AW4" s="72"/>
-      <c r="AX4" s="73"/>
-      <c r="AY4" s="71">
+      <c r="AS4" s="73"/>
+      <c r="AT4" s="73"/>
+      <c r="AU4" s="73"/>
+      <c r="AV4" s="73"/>
+      <c r="AW4" s="73"/>
+      <c r="AX4" s="74"/>
+      <c r="AY4" s="72">
         <f>AY5</f>
         <v>46195</v>
       </c>
-      <c r="AZ4" s="72"/>
-      <c r="BA4" s="72"/>
-      <c r="BB4" s="72"/>
-      <c r="BC4" s="72"/>
-      <c r="BD4" s="72"/>
-      <c r="BE4" s="73"/>
-      <c r="BF4" s="71">
+      <c r="AZ4" s="73"/>
+      <c r="BA4" s="73"/>
+      <c r="BB4" s="73"/>
+      <c r="BC4" s="73"/>
+      <c r="BD4" s="73"/>
+      <c r="BE4" s="74"/>
+      <c r="BF4" s="72">
         <f>BF5</f>
         <v>46202</v>
       </c>
-      <c r="BG4" s="72"/>
-      <c r="BH4" s="72"/>
-      <c r="BI4" s="72"/>
-      <c r="BJ4" s="72"/>
-      <c r="BK4" s="72"/>
-      <c r="BL4" s="73"/>
-      <c r="BM4" s="71">
+      <c r="BG4" s="73"/>
+      <c r="BH4" s="73"/>
+      <c r="BI4" s="73"/>
+      <c r="BJ4" s="73"/>
+      <c r="BK4" s="73"/>
+      <c r="BL4" s="74"/>
+      <c r="BM4" s="72">
         <f>BM5</f>
         <v>46209</v>
       </c>
-      <c r="BN4" s="72"/>
-      <c r="BO4" s="72"/>
-      <c r="BP4" s="72"/>
-      <c r="BQ4" s="72"/>
-      <c r="BR4" s="72"/>
-      <c r="BS4" s="73"/>
-      <c r="BT4" s="71">
+      <c r="BN4" s="73"/>
+      <c r="BO4" s="73"/>
+      <c r="BP4" s="73"/>
+      <c r="BQ4" s="73"/>
+      <c r="BR4" s="73"/>
+      <c r="BS4" s="74"/>
+      <c r="BT4" s="72">
         <f>BT5</f>
         <v>46216</v>
       </c>
-      <c r="BU4" s="72"/>
-      <c r="BV4" s="72"/>
-      <c r="BW4" s="72"/>
-      <c r="BX4" s="72"/>
-      <c r="BY4" s="72"/>
-      <c r="BZ4" s="73"/>
-      <c r="CA4" s="71">
+      <c r="BU4" s="73"/>
+      <c r="BV4" s="73"/>
+      <c r="BW4" s="73"/>
+      <c r="BX4" s="73"/>
+      <c r="BY4" s="73"/>
+      <c r="BZ4" s="74"/>
+      <c r="CA4" s="72">
         <f t="shared" ref="CA4" si="0">CA5</f>
         <v>46223</v>
       </c>
-      <c r="CB4" s="72"/>
-      <c r="CC4" s="72"/>
-      <c r="CD4" s="72"/>
-      <c r="CE4" s="72"/>
-      <c r="CF4" s="72"/>
-      <c r="CG4" s="73"/>
-      <c r="CH4" s="71">
+      <c r="CB4" s="73"/>
+      <c r="CC4" s="73"/>
+      <c r="CD4" s="73"/>
+      <c r="CE4" s="73"/>
+      <c r="CF4" s="73"/>
+      <c r="CG4" s="74"/>
+      <c r="CH4" s="72">
         <f t="shared" ref="CH4" si="1">CH5</f>
         <v>46230</v>
       </c>
-      <c r="CI4" s="72"/>
-      <c r="CJ4" s="72"/>
-      <c r="CK4" s="72"/>
-      <c r="CL4" s="72"/>
-      <c r="CM4" s="72"/>
-      <c r="CN4" s="73"/>
-      <c r="CO4" s="71">
+      <c r="CI4" s="73"/>
+      <c r="CJ4" s="73"/>
+      <c r="CK4" s="73"/>
+      <c r="CL4" s="73"/>
+      <c r="CM4" s="73"/>
+      <c r="CN4" s="74"/>
+      <c r="CO4" s="72">
         <f t="shared" ref="CO4" si="2">CO5</f>
         <v>46237</v>
       </c>
-      <c r="CP4" s="72"/>
-      <c r="CQ4" s="72"/>
-      <c r="CR4" s="72"/>
-      <c r="CS4" s="72"/>
-      <c r="CT4" s="72"/>
-      <c r="CU4" s="73"/>
-      <c r="CV4" s="71">
+      <c r="CP4" s="73"/>
+      <c r="CQ4" s="73"/>
+      <c r="CR4" s="73"/>
+      <c r="CS4" s="73"/>
+      <c r="CT4" s="73"/>
+      <c r="CU4" s="74"/>
+      <c r="CV4" s="72">
         <f t="shared" ref="CV4" si="3">CV5</f>
         <v>46244</v>
       </c>
-      <c r="CW4" s="72"/>
-      <c r="CX4" s="72"/>
-      <c r="CY4" s="72"/>
-      <c r="CZ4" s="72"/>
-      <c r="DA4" s="72"/>
-      <c r="DB4" s="73"/>
-      <c r="DC4" s="71">
+      <c r="CW4" s="73"/>
+      <c r="CX4" s="73"/>
+      <c r="CY4" s="73"/>
+      <c r="CZ4" s="73"/>
+      <c r="DA4" s="73"/>
+      <c r="DB4" s="74"/>
+      <c r="DC4" s="72">
         <f t="shared" ref="DC4" si="4">DC5</f>
         <v>46251</v>
       </c>
-      <c r="DD4" s="72"/>
-      <c r="DE4" s="72"/>
-      <c r="DF4" s="72"/>
-      <c r="DG4" s="72"/>
-      <c r="DH4" s="72"/>
-      <c r="DI4" s="73"/>
-      <c r="DJ4" s="71">
+      <c r="DD4" s="73"/>
+      <c r="DE4" s="73"/>
+      <c r="DF4" s="73"/>
+      <c r="DG4" s="73"/>
+      <c r="DH4" s="73"/>
+      <c r="DI4" s="74"/>
+      <c r="DJ4" s="72">
         <f t="shared" ref="DJ4" si="5">DJ5</f>
         <v>46258</v>
       </c>
-      <c r="DK4" s="72"/>
-      <c r="DL4" s="72"/>
-      <c r="DM4" s="72"/>
-      <c r="DN4" s="72"/>
-      <c r="DO4" s="72"/>
-      <c r="DP4" s="73"/>
-      <c r="DQ4" s="71">
+      <c r="DK4" s="73"/>
+      <c r="DL4" s="73"/>
+      <c r="DM4" s="73"/>
+      <c r="DN4" s="73"/>
+      <c r="DO4" s="73"/>
+      <c r="DP4" s="74"/>
+      <c r="DQ4" s="72">
         <f t="shared" ref="DQ4" si="6">DQ5</f>
         <v>46265</v>
       </c>
-      <c r="DR4" s="72"/>
-      <c r="DS4" s="72"/>
-      <c r="DT4" s="72"/>
-      <c r="DU4" s="72"/>
-      <c r="DV4" s="72"/>
-      <c r="DW4" s="73"/>
-      <c r="DX4" s="71">
+      <c r="DR4" s="73"/>
+      <c r="DS4" s="73"/>
+      <c r="DT4" s="73"/>
+      <c r="DU4" s="73"/>
+      <c r="DV4" s="73"/>
+      <c r="DW4" s="74"/>
+      <c r="DX4" s="72">
         <f t="shared" ref="DX4" si="7">DX5</f>
         <v>46272</v>
       </c>
-      <c r="DY4" s="72"/>
-      <c r="DZ4" s="72"/>
-      <c r="EA4" s="72"/>
-      <c r="EB4" s="72"/>
-      <c r="EC4" s="72"/>
-      <c r="ED4" s="73"/>
-      <c r="EE4" s="71">
+      <c r="DY4" s="73"/>
+      <c r="DZ4" s="73"/>
+      <c r="EA4" s="73"/>
+      <c r="EB4" s="73"/>
+      <c r="EC4" s="73"/>
+      <c r="ED4" s="74"/>
+      <c r="EE4" s="72">
         <f t="shared" ref="EE4" si="8">EE5</f>
         <v>46279</v>
       </c>
-      <c r="EF4" s="72"/>
-      <c r="EG4" s="72"/>
-      <c r="EH4" s="72"/>
-      <c r="EI4" s="72"/>
-      <c r="EJ4" s="72"/>
-      <c r="EK4" s="73"/>
-      <c r="EL4" s="71">
+      <c r="EF4" s="73"/>
+      <c r="EG4" s="73"/>
+      <c r="EH4" s="73"/>
+      <c r="EI4" s="73"/>
+      <c r="EJ4" s="73"/>
+      <c r="EK4" s="74"/>
+      <c r="EL4" s="72">
         <f t="shared" ref="EL4" si="9">EL5</f>
         <v>46286</v>
       </c>
-      <c r="EM4" s="72"/>
-      <c r="EN4" s="72"/>
-      <c r="EO4" s="72"/>
-      <c r="EP4" s="72"/>
-      <c r="EQ4" s="72"/>
-      <c r="ER4" s="73"/>
-      <c r="ES4" s="71">
+      <c r="EM4" s="73"/>
+      <c r="EN4" s="73"/>
+      <c r="EO4" s="73"/>
+      <c r="EP4" s="73"/>
+      <c r="EQ4" s="73"/>
+      <c r="ER4" s="74"/>
+      <c r="ES4" s="72">
         <f t="shared" ref="ES4" si="10">ES5</f>
         <v>46293</v>
       </c>
-      <c r="ET4" s="72"/>
-      <c r="EU4" s="72"/>
-      <c r="EV4" s="72"/>
-      <c r="EW4" s="72"/>
-      <c r="EX4" s="72"/>
-      <c r="EY4" s="73"/>
-      <c r="EZ4" s="71">
+      <c r="ET4" s="73"/>
+      <c r="EU4" s="73"/>
+      <c r="EV4" s="73"/>
+      <c r="EW4" s="73"/>
+      <c r="EX4" s="73"/>
+      <c r="EY4" s="74"/>
+      <c r="EZ4" s="72">
         <f t="shared" ref="EZ4" si="11">EZ5</f>
         <v>46300</v>
       </c>
-      <c r="FA4" s="72"/>
-      <c r="FB4" s="72"/>
-      <c r="FC4" s="72"/>
-      <c r="FD4" s="72"/>
-      <c r="FE4" s="72"/>
-      <c r="FF4" s="73"/>
-      <c r="FG4" s="71">
+      <c r="FA4" s="73"/>
+      <c r="FB4" s="73"/>
+      <c r="FC4" s="73"/>
+      <c r="FD4" s="73"/>
+      <c r="FE4" s="73"/>
+      <c r="FF4" s="74"/>
+      <c r="FG4" s="72">
         <f t="shared" ref="FG4" si="12">FG5</f>
         <v>46307</v>
       </c>
-      <c r="FH4" s="72"/>
-      <c r="FI4" s="72"/>
-      <c r="FJ4" s="72"/>
-      <c r="FK4" s="72"/>
-      <c r="FL4" s="72"/>
-      <c r="FM4" s="73"/>
-      <c r="FN4" s="71">
+      <c r="FH4" s="73"/>
+      <c r="FI4" s="73"/>
+      <c r="FJ4" s="73"/>
+      <c r="FK4" s="73"/>
+      <c r="FL4" s="73"/>
+      <c r="FM4" s="74"/>
+      <c r="FN4" s="72">
         <f t="shared" ref="FN4" si="13">FN5</f>
         <v>46314</v>
       </c>
-      <c r="FO4" s="72"/>
-      <c r="FP4" s="72"/>
-      <c r="FQ4" s="72"/>
-      <c r="FR4" s="72"/>
-      <c r="FS4" s="72"/>
-      <c r="FT4" s="73"/>
-      <c r="FU4" s="71">
+      <c r="FO4" s="73"/>
+      <c r="FP4" s="73"/>
+      <c r="FQ4" s="73"/>
+      <c r="FR4" s="73"/>
+      <c r="FS4" s="73"/>
+      <c r="FT4" s="74"/>
+      <c r="FU4" s="72">
         <f t="shared" ref="FU4" si="14">FU5</f>
         <v>46321</v>
       </c>
-      <c r="FV4" s="72"/>
-      <c r="FW4" s="72"/>
-      <c r="FX4" s="72"/>
-      <c r="FY4" s="72"/>
-      <c r="FZ4" s="72"/>
-      <c r="GA4" s="73"/>
-      <c r="GB4" s="71">
+      <c r="FV4" s="73"/>
+      <c r="FW4" s="73"/>
+      <c r="FX4" s="73"/>
+      <c r="FY4" s="73"/>
+      <c r="FZ4" s="73"/>
+      <c r="GA4" s="74"/>
+      <c r="GB4" s="72">
         <f t="shared" ref="GB4" si="15">GB5</f>
         <v>46328</v>
       </c>
-      <c r="GC4" s="72"/>
-      <c r="GD4" s="72"/>
-      <c r="GE4" s="72"/>
-      <c r="GF4" s="72"/>
-      <c r="GG4" s="72"/>
-      <c r="GH4" s="73"/>
-      <c r="GI4" s="71">
+      <c r="GC4" s="73"/>
+      <c r="GD4" s="73"/>
+      <c r="GE4" s="73"/>
+      <c r="GF4" s="73"/>
+      <c r="GG4" s="73"/>
+      <c r="GH4" s="74"/>
+      <c r="GI4" s="72">
         <f t="shared" ref="GI4" si="16">GI5</f>
         <v>46335</v>
       </c>
-      <c r="GJ4" s="72"/>
-      <c r="GK4" s="72"/>
-      <c r="GL4" s="72"/>
-      <c r="GM4" s="72"/>
-      <c r="GN4" s="72"/>
-      <c r="GO4" s="73"/>
-      <c r="GP4" s="71">
+      <c r="GJ4" s="73"/>
+      <c r="GK4" s="73"/>
+      <c r="GL4" s="73"/>
+      <c r="GM4" s="73"/>
+      <c r="GN4" s="73"/>
+      <c r="GO4" s="74"/>
+      <c r="GP4" s="72">
         <f t="shared" ref="GP4" si="17">GP5</f>
         <v>46342</v>
       </c>
-      <c r="GQ4" s="72"/>
-      <c r="GR4" s="72"/>
-      <c r="GS4" s="72"/>
-      <c r="GT4" s="72"/>
-      <c r="GU4" s="72"/>
-      <c r="GV4" s="73"/>
-      <c r="GW4" s="71">
+      <c r="GQ4" s="73"/>
+      <c r="GR4" s="73"/>
+      <c r="GS4" s="73"/>
+      <c r="GT4" s="73"/>
+      <c r="GU4" s="73"/>
+      <c r="GV4" s="74"/>
+      <c r="GW4" s="72">
         <f t="shared" ref="GW4" si="18">GW5</f>
         <v>46349</v>
       </c>
-      <c r="GX4" s="72"/>
-      <c r="GY4" s="72"/>
-      <c r="GZ4" s="72"/>
-      <c r="HA4" s="72"/>
-      <c r="HB4" s="72"/>
-      <c r="HC4" s="73"/>
-      <c r="HD4" s="71">
+      <c r="GX4" s="73"/>
+      <c r="GY4" s="73"/>
+      <c r="GZ4" s="73"/>
+      <c r="HA4" s="73"/>
+      <c r="HB4" s="73"/>
+      <c r="HC4" s="74"/>
+      <c r="HD4" s="72">
         <f t="shared" ref="HD4" si="19">HD5</f>
         <v>46356</v>
       </c>
-      <c r="HE4" s="72"/>
-      <c r="HF4" s="72"/>
-      <c r="HG4" s="72"/>
-      <c r="HH4" s="72"/>
-      <c r="HI4" s="72"/>
-      <c r="HJ4" s="73"/>
-      <c r="HK4" s="71">
+      <c r="HE4" s="73"/>
+      <c r="HF4" s="73"/>
+      <c r="HG4" s="73"/>
+      <c r="HH4" s="73"/>
+      <c r="HI4" s="73"/>
+      <c r="HJ4" s="74"/>
+      <c r="HK4" s="72">
         <f t="shared" ref="HK4" si="20">HK5</f>
         <v>46363</v>
       </c>
-      <c r="HL4" s="72"/>
-      <c r="HM4" s="72"/>
-      <c r="HN4" s="72"/>
-      <c r="HO4" s="72"/>
-      <c r="HP4" s="72"/>
-      <c r="HQ4" s="73"/>
-      <c r="HR4" s="71">
+      <c r="HL4" s="73"/>
+      <c r="HM4" s="73"/>
+      <c r="HN4" s="73"/>
+      <c r="HO4" s="73"/>
+      <c r="HP4" s="73"/>
+      <c r="HQ4" s="74"/>
+      <c r="HR4" s="72">
         <f t="shared" ref="HR4" si="21">HR5</f>
         <v>46370</v>
       </c>
-      <c r="HS4" s="72"/>
-      <c r="HT4" s="72"/>
-      <c r="HU4" s="72"/>
-      <c r="HV4" s="72"/>
-      <c r="HW4" s="72"/>
-      <c r="HX4" s="73"/>
-      <c r="HY4" s="71">
+      <c r="HS4" s="73"/>
+      <c r="HT4" s="73"/>
+      <c r="HU4" s="73"/>
+      <c r="HV4" s="73"/>
+      <c r="HW4" s="73"/>
+      <c r="HX4" s="74"/>
+      <c r="HY4" s="72">
         <f t="shared" ref="HY4" si="22">HY5</f>
         <v>46377</v>
       </c>
-      <c r="HZ4" s="72"/>
-      <c r="IA4" s="72"/>
-      <c r="IB4" s="72"/>
-      <c r="IC4" s="72"/>
-      <c r="ID4" s="72"/>
-      <c r="IE4" s="73"/>
-      <c r="IF4" s="71">
+      <c r="HZ4" s="73"/>
+      <c r="IA4" s="73"/>
+      <c r="IB4" s="73"/>
+      <c r="IC4" s="73"/>
+      <c r="ID4" s="73"/>
+      <c r="IE4" s="74"/>
+      <c r="IF4" s="72">
         <f t="shared" ref="IF4" si="23">IF5</f>
         <v>46384</v>
       </c>
-      <c r="IG4" s="72"/>
-      <c r="IH4" s="72"/>
-      <c r="II4" s="72"/>
-      <c r="IJ4" s="72"/>
-      <c r="IK4" s="72"/>
-      <c r="IL4" s="73"/>
-      <c r="IM4" s="71">
+      <c r="IG4" s="73"/>
+      <c r="IH4" s="73"/>
+      <c r="II4" s="73"/>
+      <c r="IJ4" s="73"/>
+      <c r="IK4" s="73"/>
+      <c r="IL4" s="74"/>
+      <c r="IM4" s="72">
         <f t="shared" ref="IM4" si="24">IM5</f>
         <v>46391</v>
       </c>
-      <c r="IN4" s="72"/>
-      <c r="IO4" s="72"/>
-      <c r="IP4" s="72"/>
-      <c r="IQ4" s="72"/>
-      <c r="IR4" s="72"/>
-      <c r="IS4" s="73"/>
-      <c r="IT4" s="71">
+      <c r="IN4" s="73"/>
+      <c r="IO4" s="73"/>
+      <c r="IP4" s="73"/>
+      <c r="IQ4" s="73"/>
+      <c r="IR4" s="73"/>
+      <c r="IS4" s="74"/>
+      <c r="IT4" s="72">
         <f t="shared" ref="IT4" si="25">IT5</f>
         <v>46398</v>
       </c>
-      <c r="IU4" s="72"/>
-      <c r="IV4" s="72"/>
-      <c r="IW4" s="72"/>
-      <c r="IX4" s="72"/>
-      <c r="IY4" s="72"/>
-      <c r="IZ4" s="73"/>
-      <c r="JA4" s="71">
+      <c r="IU4" s="73"/>
+      <c r="IV4" s="73"/>
+      <c r="IW4" s="73"/>
+      <c r="IX4" s="73"/>
+      <c r="IY4" s="73"/>
+      <c r="IZ4" s="74"/>
+      <c r="JA4" s="72">
         <f t="shared" ref="JA4" si="26">JA5</f>
         <v>46405</v>
       </c>
-      <c r="JB4" s="72"/>
-      <c r="JC4" s="72"/>
-      <c r="JD4" s="72"/>
-      <c r="JE4" s="72"/>
-      <c r="JF4" s="72"/>
-      <c r="JG4" s="73"/>
-      <c r="JH4" s="71">
+      <c r="JB4" s="73"/>
+      <c r="JC4" s="73"/>
+      <c r="JD4" s="73"/>
+      <c r="JE4" s="73"/>
+      <c r="JF4" s="73"/>
+      <c r="JG4" s="74"/>
+      <c r="JH4" s="72">
         <f t="shared" ref="JH4" si="27">JH5</f>
         <v>46412</v>
       </c>
-      <c r="JI4" s="72"/>
-      <c r="JJ4" s="72"/>
-      <c r="JK4" s="72"/>
-      <c r="JL4" s="72"/>
-      <c r="JM4" s="72"/>
-      <c r="JN4" s="73"/>
-      <c r="JO4" s="71">
+      <c r="JI4" s="73"/>
+      <c r="JJ4" s="73"/>
+      <c r="JK4" s="73"/>
+      <c r="JL4" s="73"/>
+      <c r="JM4" s="73"/>
+      <c r="JN4" s="74"/>
+      <c r="JO4" s="72">
         <f t="shared" ref="JO4" si="28">JO5</f>
         <v>46419</v>
       </c>
-      <c r="JP4" s="72"/>
-      <c r="JQ4" s="72"/>
-      <c r="JR4" s="72"/>
-      <c r="JS4" s="72"/>
-      <c r="JT4" s="72"/>
-      <c r="JU4" s="73"/>
-      <c r="JV4" s="71">
+      <c r="JP4" s="73"/>
+      <c r="JQ4" s="73"/>
+      <c r="JR4" s="73"/>
+      <c r="JS4" s="73"/>
+      <c r="JT4" s="73"/>
+      <c r="JU4" s="74"/>
+      <c r="JV4" s="72">
         <f t="shared" ref="JV4" si="29">JV5</f>
         <v>46426</v>
       </c>
-      <c r="JW4" s="72"/>
-      <c r="JX4" s="72"/>
-      <c r="JY4" s="72"/>
-      <c r="JZ4" s="72"/>
-      <c r="KA4" s="72"/>
-      <c r="KB4" s="73"/>
-      <c r="KC4" s="71">
+      <c r="JW4" s="73"/>
+      <c r="JX4" s="73"/>
+      <c r="JY4" s="73"/>
+      <c r="JZ4" s="73"/>
+      <c r="KA4" s="73"/>
+      <c r="KB4" s="74"/>
+      <c r="KC4" s="72">
         <f t="shared" ref="KC4" si="30">KC5</f>
         <v>46433</v>
       </c>
-      <c r="KD4" s="72"/>
-      <c r="KE4" s="72"/>
-      <c r="KF4" s="72"/>
-      <c r="KG4" s="72"/>
-      <c r="KH4" s="72"/>
-      <c r="KI4" s="73"/>
-      <c r="KJ4" s="71">
+      <c r="KD4" s="73"/>
+      <c r="KE4" s="73"/>
+      <c r="KF4" s="73"/>
+      <c r="KG4" s="73"/>
+      <c r="KH4" s="73"/>
+      <c r="KI4" s="74"/>
+      <c r="KJ4" s="72">
         <f t="shared" ref="KJ4" si="31">KJ5</f>
         <v>46440</v>
       </c>
-      <c r="KK4" s="72"/>
-      <c r="KL4" s="72"/>
-      <c r="KM4" s="72"/>
-      <c r="KN4" s="72"/>
-      <c r="KO4" s="72"/>
-      <c r="KP4" s="73"/>
-      <c r="KQ4" s="71">
+      <c r="KK4" s="73"/>
+      <c r="KL4" s="73"/>
+      <c r="KM4" s="73"/>
+      <c r="KN4" s="73"/>
+      <c r="KO4" s="73"/>
+      <c r="KP4" s="74"/>
+      <c r="KQ4" s="72">
         <f t="shared" ref="KQ4" si="32">KQ5</f>
         <v>46447</v>
       </c>
-      <c r="KR4" s="72"/>
-      <c r="KS4" s="72"/>
-      <c r="KT4" s="72"/>
-      <c r="KU4" s="72"/>
-      <c r="KV4" s="72"/>
-      <c r="KW4" s="73"/>
-      <c r="KX4" s="71">
+      <c r="KR4" s="73"/>
+      <c r="KS4" s="73"/>
+      <c r="KT4" s="73"/>
+      <c r="KU4" s="73"/>
+      <c r="KV4" s="73"/>
+      <c r="KW4" s="74"/>
+      <c r="KX4" s="72">
         <f t="shared" ref="KX4" si="33">KX5</f>
         <v>46454</v>
       </c>
-      <c r="KY4" s="72"/>
-      <c r="KZ4" s="72"/>
-      <c r="LA4" s="72"/>
-      <c r="LB4" s="72"/>
-      <c r="LC4" s="72"/>
-      <c r="LD4" s="73"/>
-      <c r="LE4" s="71">
+      <c r="KY4" s="73"/>
+      <c r="KZ4" s="73"/>
+      <c r="LA4" s="73"/>
+      <c r="LB4" s="73"/>
+      <c r="LC4" s="73"/>
+      <c r="LD4" s="74"/>
+      <c r="LE4" s="72">
         <f t="shared" ref="LE4" si="34">LE5</f>
         <v>46461</v>
       </c>
-      <c r="LF4" s="72"/>
-      <c r="LG4" s="72"/>
-      <c r="LH4" s="72"/>
-      <c r="LI4" s="72"/>
-      <c r="LJ4" s="72"/>
-      <c r="LK4" s="73"/>
-      <c r="LL4" s="71">
+      <c r="LF4" s="73"/>
+      <c r="LG4" s="73"/>
+      <c r="LH4" s="73"/>
+      <c r="LI4" s="73"/>
+      <c r="LJ4" s="73"/>
+      <c r="LK4" s="74"/>
+      <c r="LL4" s="72">
         <f t="shared" ref="LL4" si="35">LL5</f>
         <v>46468</v>
       </c>
-      <c r="LM4" s="72"/>
-      <c r="LN4" s="72"/>
-      <c r="LO4" s="72"/>
-      <c r="LP4" s="72"/>
-      <c r="LQ4" s="72"/>
-      <c r="LR4" s="73"/>
-      <c r="LS4" s="71">
+      <c r="LM4" s="73"/>
+      <c r="LN4" s="73"/>
+      <c r="LO4" s="73"/>
+      <c r="LP4" s="73"/>
+      <c r="LQ4" s="73"/>
+      <c r="LR4" s="74"/>
+      <c r="LS4" s="72">
         <f t="shared" ref="LS4" si="36">LS5</f>
         <v>46475</v>
       </c>
-      <c r="LT4" s="72"/>
-      <c r="LU4" s="72"/>
-      <c r="LV4" s="72"/>
-      <c r="LW4" s="72"/>
-      <c r="LX4" s="72"/>
-      <c r="LY4" s="73"/>
-      <c r="LZ4" s="71">
+      <c r="LT4" s="73"/>
+      <c r="LU4" s="73"/>
+      <c r="LV4" s="73"/>
+      <c r="LW4" s="73"/>
+      <c r="LX4" s="73"/>
+      <c r="LY4" s="74"/>
+      <c r="LZ4" s="72">
         <f t="shared" ref="LZ4" si="37">LZ5</f>
         <v>46482</v>
       </c>
-      <c r="MA4" s="72"/>
-      <c r="MB4" s="72"/>
-      <c r="MC4" s="72"/>
-      <c r="MD4" s="72"/>
-      <c r="ME4" s="72"/>
-      <c r="MF4" s="73"/>
-      <c r="MG4" s="71">
+      <c r="MA4" s="73"/>
+      <c r="MB4" s="73"/>
+      <c r="MC4" s="73"/>
+      <c r="MD4" s="73"/>
+      <c r="ME4" s="73"/>
+      <c r="MF4" s="74"/>
+      <c r="MG4" s="72">
         <f t="shared" ref="MG4" si="38">MG5</f>
         <v>46489</v>
       </c>
-      <c r="MH4" s="72"/>
-      <c r="MI4" s="72"/>
-      <c r="MJ4" s="72"/>
-      <c r="MK4" s="72"/>
-      <c r="ML4" s="72"/>
-      <c r="MM4" s="73"/>
-      <c r="MN4" s="71">
+      <c r="MH4" s="73"/>
+      <c r="MI4" s="73"/>
+      <c r="MJ4" s="73"/>
+      <c r="MK4" s="73"/>
+      <c r="ML4" s="73"/>
+      <c r="MM4" s="74"/>
+      <c r="MN4" s="72">
         <f t="shared" ref="MN4" si="39">MN5</f>
         <v>46496</v>
       </c>
-      <c r="MO4" s="72"/>
-      <c r="MP4" s="72"/>
-      <c r="MQ4" s="72"/>
-      <c r="MR4" s="72"/>
-      <c r="MS4" s="72"/>
-      <c r="MT4" s="73"/>
-      <c r="MU4" s="71">
+      <c r="MO4" s="73"/>
+      <c r="MP4" s="73"/>
+      <c r="MQ4" s="73"/>
+      <c r="MR4" s="73"/>
+      <c r="MS4" s="73"/>
+      <c r="MT4" s="74"/>
+      <c r="MU4" s="72">
         <f t="shared" ref="MU4" si="40">MU5</f>
         <v>46503</v>
       </c>
-      <c r="MV4" s="72"/>
-      <c r="MW4" s="72"/>
-      <c r="MX4" s="72"/>
-      <c r="MY4" s="72"/>
-      <c r="MZ4" s="72"/>
-      <c r="NA4" s="73"/>
+      <c r="MV4" s="73"/>
+      <c r="MW4" s="73"/>
+      <c r="MX4" s="73"/>
+      <c r="MY4" s="73"/>
+      <c r="MZ4" s="73"/>
+      <c r="NA4" s="74"/>
     </row>
-    <row r="5" spans="1:365" ht="15" customHeight="1">
+    <row r="5" spans="1:365" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="42" t="s">
         <v>8</v>
       </c>
@@ -3639,7 +3590,7 @@
         <v>46509</v>
       </c>
     </row>
-    <row r="6" spans="1:365" ht="30" customHeight="1" thickBot="1">
+    <row r="6" spans="1:365" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="42" t="s">
         <v>9</v>
       </c>
@@ -5091,14 +5042,14 @@
         <v>S</v>
       </c>
     </row>
-    <row r="7" spans="1:365" ht="30" hidden="1" customHeight="1" thickBot="1">
+    <row r="7" spans="1:365" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="41" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="45"/>
       <c r="E7"/>
       <c r="H7" t="str">
-        <f ca="1">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I7" s="28"/>
@@ -5459,7 +5410,7 @@
       <c r="MZ7" s="28"/>
       <c r="NA7" s="28"/>
     </row>
-    <row r="8" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="8" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="42" t="s">
         <v>17</v>
       </c>
@@ -5472,7 +5423,7 @@
       <c r="F8" s="20"/>
       <c r="G8" s="17"/>
       <c r="H8" s="17" t="str">
-        <f t="shared" ref="H8:H48" ca="1" si="346">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H8:H42" si="346">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I8" s="28"/>
@@ -5833,7 +5784,7 @@
       <c r="MZ8" s="28"/>
       <c r="NA8" s="28"/>
     </row>
-    <row r="9" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="9" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="42" t="s">
         <v>19</v>
       </c>
@@ -5855,7 +5806,7 @@
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="17">
-        <f t="shared" ca="1" si="346"/>
+        <f t="shared" si="346"/>
         <v>17</v>
       </c>
       <c r="I9" s="28"/>
@@ -6216,7 +6167,7 @@
       <c r="MZ9" s="28"/>
       <c r="NA9" s="28"/>
     </row>
-    <row r="10" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="10" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="42" t="s">
         <v>22</v>
       </c>
@@ -6237,7 +6188,7 @@
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="17">
-        <f t="shared" ca="1" si="346"/>
+        <f t="shared" si="346"/>
         <v>31</v>
       </c>
       <c r="I10" s="28"/>
@@ -6598,7 +6549,7 @@
       <c r="MZ10" s="28"/>
       <c r="NA10" s="28"/>
     </row>
-    <row r="11" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="11" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="41"/>
       <c r="B11" s="59" t="s">
         <v>23</v>
@@ -6617,7 +6568,7 @@
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="17">
-        <f t="shared" ca="1" si="346"/>
+        <f t="shared" si="346"/>
         <v>31</v>
       </c>
       <c r="I11" s="28"/>
@@ -6978,7 +6929,7 @@
       <c r="MZ11" s="28"/>
       <c r="NA11" s="28"/>
     </row>
-    <row r="12" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="12" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41"/>
       <c r="B12" s="58" t="s">
         <v>26</v>
@@ -7357,7 +7308,7 @@
       <c r="MZ12" s="28"/>
       <c r="NA12" s="28"/>
     </row>
-    <row r="13" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="13" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="41"/>
       <c r="B13" s="58" t="s">
         <v>27</v>
@@ -7376,7 +7327,7 @@
       </c>
       <c r="G13" s="17"/>
       <c r="H13" s="17">
-        <f t="shared" ca="1" si="346"/>
+        <f t="shared" si="346"/>
         <v>4</v>
       </c>
       <c r="I13" s="28"/>
@@ -7737,7 +7688,7 @@
       <c r="MZ13" s="28"/>
       <c r="NA13" s="28"/>
     </row>
-    <row r="14" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="14" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="42"/>
       <c r="B14" s="59" t="s">
         <v>28</v>
@@ -7756,7 +7707,7 @@
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17">
-        <f t="shared" ca="1" si="346"/>
+        <f t="shared" si="346"/>
         <v>18</v>
       </c>
       <c r="I14" s="28"/>
@@ -8117,7 +8068,7 @@
       <c r="MZ14" s="28"/>
       <c r="NA14" s="28"/>
     </row>
-    <row r="15" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="15" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="42"/>
       <c r="B15" s="59" t="s">
         <v>29</v>
@@ -8136,7 +8087,7 @@
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="17">
-        <f t="shared" ca="1" si="346"/>
+        <f t="shared" si="346"/>
         <v>2</v>
       </c>
       <c r="I15" s="28"/>
@@ -8497,7 +8448,7 @@
       <c r="MZ15" s="28"/>
       <c r="NA15" s="28"/>
     </row>
-    <row r="16" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="16" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41"/>
       <c r="B16" s="59" t="s">
         <v>30</v>
@@ -8516,7 +8467,7 @@
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17">
-        <f t="shared" ca="1" si="346"/>
+        <f t="shared" si="346"/>
         <v>1</v>
       </c>
       <c r="I16" s="28"/>
@@ -8877,7 +8828,7 @@
       <c r="MZ16" s="28"/>
       <c r="NA16" s="28"/>
     </row>
-    <row r="17" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="17" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="41"/>
       <c r="B17" s="60" t="s">
         <v>31</v>
@@ -8896,7 +8847,7 @@
       </c>
       <c r="G17" s="17"/>
       <c r="H17" s="17">
-        <f t="shared" ca="1" si="346"/>
+        <f t="shared" si="346"/>
         <v>11</v>
       </c>
       <c r="I17" s="28"/>
@@ -9257,7 +9208,7 @@
       <c r="MZ17" s="28"/>
       <c r="NA17" s="28"/>
     </row>
-    <row r="18" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="18" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="41"/>
       <c r="B18" s="60" t="s">
         <v>31</v>
@@ -9276,7 +9227,7 @@
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17">
-        <f t="shared" ca="1" si="346"/>
+        <f t="shared" si="346"/>
         <v>16</v>
       </c>
       <c r="I18" s="28"/>
@@ -9637,7 +9588,7 @@
       <c r="MZ18" s="28"/>
       <c r="NA18" s="28"/>
     </row>
-    <row r="19" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="19" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="41"/>
       <c r="B19" s="60" t="s">
         <v>32</v>
@@ -9656,7 +9607,7 @@
       </c>
       <c r="G19" s="17"/>
       <c r="H19" s="17">
-        <f t="shared" ca="1" si="346"/>
+        <f t="shared" si="346"/>
         <v>3</v>
       </c>
       <c r="I19" s="28"/>
@@ -10017,7 +9968,7 @@
       <c r="MZ19" s="28"/>
       <c r="NA19" s="28"/>
     </row>
-    <row r="20" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="20" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41"/>
       <c r="B20" s="59" t="s">
         <v>33</v>
@@ -10396,7 +10347,7 @@
       <c r="MZ20" s="28"/>
       <c r="NA20" s="28"/>
     </row>
-    <row r="21" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="21" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="41"/>
       <c r="B21" s="59" t="s">
         <v>34</v>
@@ -10773,7 +10724,7 @@
       <c r="MZ21" s="28"/>
       <c r="NA21" s="28"/>
     </row>
-    <row r="22" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="22" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41"/>
       <c r="B22" s="65" t="s">
         <v>35</v>
@@ -11142,22 +11093,22 @@
       <c r="MZ22" s="28"/>
       <c r="NA22" s="28"/>
     </row>
-    <row r="23" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="23" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="41"/>
       <c r="B23" s="69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C23" s="66" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D23" s="67">
         <v>1</v>
       </c>
       <c r="E23" s="68">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="F23" s="68">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="G23" s="17"/>
       <c r="H23" s="17">
@@ -11521,26 +11472,26 @@
       <c r="MZ23" s="28"/>
       <c r="NA23" s="28"/>
     </row>
-    <row r="24" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="24" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="41"/>
       <c r="B24" s="69" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D24" s="67">
         <v>1</v>
       </c>
       <c r="E24" s="68">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="F24" s="68">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="G24" s="17"/>
       <c r="H24" s="17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I24" s="28"/>
       <c r="J24" s="28"/>
@@ -11900,7 +11851,7 @@
       <c r="MZ24" s="28"/>
       <c r="NA24" s="28"/>
     </row>
-    <row r="25" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="25" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="41"/>
       <c r="B25" s="69" t="s">
         <v>39</v>
@@ -11912,14 +11863,14 @@
         <v>1</v>
       </c>
       <c r="E25" s="68">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="F25" s="68">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="G25" s="17"/>
       <c r="H25" s="17">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I25" s="28"/>
       <c r="J25" s="28"/>
@@ -12279,9 +12230,9 @@
       <c r="MZ25" s="28"/>
       <c r="NA25" s="28"/>
     </row>
-    <row r="26" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
+    <row r="26" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41"/>
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="70" t="s">
         <v>40</v>
       </c>
       <c r="C26" s="66" t="s">
@@ -12291,14 +12242,14 @@
         <v>1</v>
       </c>
       <c r="E26" s="68">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="F26" s="68">
-        <v>46171</v>
+        <v>46189</v>
       </c>
       <c r="G26" s="17"/>
       <c r="H26" s="17">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I26" s="28"/>
       <c r="J26" s="28"/>
@@ -12658,26 +12609,25 @@
       <c r="MZ26" s="28"/>
       <c r="NA26" s="28"/>
     </row>
-    <row r="27" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
+    <row r="27" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="41"/>
-      <c r="B27" s="69" t="s">
+      <c r="B27" s="70" t="s">
         <v>41</v>
       </c>
       <c r="C27" s="66" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D27" s="67">
         <v>1</v>
       </c>
       <c r="E27" s="68">
-        <v>46160</v>
+        <v>46175</v>
       </c>
       <c r="F27" s="68">
-        <v>46160</v>
-      </c>
-      <c r="G27" s="17"/>
+        <v>46190</v>
+      </c>
       <c r="H27" s="17">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I27" s="28"/>
       <c r="J27" s="28"/>
@@ -13037,10 +12987,10 @@
       <c r="MZ27" s="28"/>
       <c r="NA27" s="28"/>
     </row>
-    <row r="28" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
+    <row r="28" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="41"/>
       <c r="B28" s="70" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C28" s="66" t="s">
         <v>21</v>
@@ -13049,14 +12999,13 @@
         <v>1</v>
       </c>
       <c r="E28" s="68">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="F28" s="68">
         <v>46189</v>
       </c>
-      <c r="G28" s="17"/>
       <c r="H28" s="17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I28" s="28"/>
       <c r="J28" s="28"/>
@@ -13416,25 +13365,29 @@
       <c r="MZ28" s="28"/>
       <c r="NA28" s="28"/>
     </row>
-    <row r="29" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="29" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="41"/>
-      <c r="B29" s="70" t="s">
-        <v>43</v>
+      <c r="B29" s="69" t="s">
+        <v>44</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="D29" s="67">
         <v>1</v>
       </c>
       <c r="E29" s="68">
-        <v>46175</v>
+        <f>F26</f>
+        <v>46189</v>
       </c>
       <c r="F29" s="68">
-        <v>46190</v>
-      </c>
+        <f>E29+14</f>
+        <v>46203</v>
+      </c>
+      <c r="G29" s="17"/>
       <c r="H29" s="17">
-        <v>15</v>
+        <f>F29-E29</f>
+        <v>14</v>
       </c>
       <c r="I29" s="28"/>
       <c r="J29" s="28"/>
@@ -13794,9 +13747,9 @@
       <c r="MZ29" s="28"/>
       <c r="NA29" s="28"/>
     </row>
-    <row r="30" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
+    <row r="30" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="41"/>
-      <c r="B30" s="70" t="s">
+      <c r="B30" s="69" t="s">
         <v>45</v>
       </c>
       <c r="C30" s="66" t="s">
@@ -13806,13 +13759,14 @@
         <v>1</v>
       </c>
       <c r="E30" s="68">
-        <v>46175</v>
+        <v>46189</v>
       </c>
       <c r="F30" s="68">
-        <v>46189</v>
-      </c>
+        <v>46211</v>
+      </c>
+      <c r="G30" s="17"/>
       <c r="H30" s="17">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I30" s="28"/>
       <c r="J30" s="28"/>
@@ -14172,29 +14126,26 @@
       <c r="MZ30" s="28"/>
       <c r="NA30" s="28"/>
     </row>
-    <row r="31" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="31" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="41"/>
       <c r="B31" s="69" t="s">
         <v>46</v>
       </c>
       <c r="C31" s="66" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D31" s="67">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E31" s="68">
-        <f>F28</f>
-        <v>46189</v>
+        <v>46197</v>
       </c>
       <c r="F31" s="68">
-        <f>E31+14</f>
-        <v>46203</v>
+        <v>46213</v>
       </c>
       <c r="G31" s="17"/>
       <c r="H31" s="17">
-        <f>F31-E31</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I31" s="28"/>
       <c r="J31" s="28"/>
@@ -14554,7 +14505,7 @@
       <c r="MZ31" s="28"/>
       <c r="NA31" s="28"/>
     </row>
-    <row r="32" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
+    <row r="32" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="41"/>
       <c r="B32" s="69" t="s">
         <v>47</v>
@@ -14566,14 +14517,16 @@
         <v>0</v>
       </c>
       <c r="E32" s="68">
-        <v>46189</v>
+        <f>F29</f>
+        <v>46203</v>
       </c>
       <c r="F32" s="68">
-        <v>46211</v>
+        <f>E32+14</f>
+        <v>46217</v>
       </c>
       <c r="G32" s="17"/>
       <c r="H32" s="17">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
@@ -14933,7 +14886,7 @@
       <c r="MZ32" s="28"/>
       <c r="NA32" s="28"/>
     </row>
-    <row r="33" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="33" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="41"/>
       <c r="B33" s="69" t="s">
         <v>48</v>
@@ -14942,17 +14895,17 @@
         <v>21</v>
       </c>
       <c r="D33" s="67">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E33" s="68">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="F33" s="68">
-        <v>46195</v>
+        <v>46217</v>
       </c>
       <c r="G33" s="17"/>
       <c r="H33" s="17">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I33" s="28"/>
       <c r="J33" s="28"/>
@@ -15312,7 +15265,7 @@
       <c r="MZ33" s="28"/>
       <c r="NA33" s="28"/>
     </row>
-    <row r="34" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="34" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="41"/>
       <c r="B34" s="69" t="s">
         <v>49</v>
@@ -15324,14 +15277,16 @@
         <v>0</v>
       </c>
       <c r="E34" s="68">
-        <v>46197</v>
+        <f>F32</f>
+        <v>46217</v>
       </c>
       <c r="F34" s="68">
-        <v>46213</v>
+        <f>E34+12</f>
+        <v>46229</v>
       </c>
       <c r="G34" s="17"/>
       <c r="H34" s="17">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I34" s="28"/>
       <c r="J34" s="28"/>
@@ -15691,28 +15646,27 @@
       <c r="MZ34" s="28"/>
       <c r="NA34" s="28"/>
     </row>
-    <row r="35" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="35" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="41"/>
       <c r="B35" s="69" t="s">
         <v>50</v>
       </c>
       <c r="C35" s="66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D35" s="67">
         <v>0</v>
       </c>
       <c r="E35" s="68">
-        <f>F31</f>
-        <v>46203</v>
+        <v>46223</v>
       </c>
       <c r="F35" s="68">
-        <f>E35+14</f>
-        <v>46217</v>
+        <f>E35+12</f>
+        <v>46235</v>
       </c>
       <c r="G35" s="17"/>
       <c r="H35" s="17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I35" s="28"/>
       <c r="J35" s="28"/>
@@ -16072,7 +16026,7 @@
       <c r="MZ35" s="28"/>
       <c r="NA35" s="28"/>
     </row>
-    <row r="36" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="36" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="41"/>
       <c r="B36" s="69" t="s">
         <v>51</v>
@@ -16084,14 +16038,15 @@
         <v>0</v>
       </c>
       <c r="E36" s="68">
-        <v>46204</v>
+        <f>F34</f>
+        <v>46229</v>
       </c>
       <c r="F36" s="68">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="G36" s="17"/>
       <c r="H36" s="17">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I36" s="28"/>
       <c r="J36" s="28"/>
@@ -16451,26 +16406,28 @@
       <c r="MZ36" s="28"/>
       <c r="NA36" s="28"/>
     </row>
-    <row r="37" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
+    <row r="37" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="41"/>
       <c r="B37" s="69" t="s">
         <v>52</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D37" s="67">
         <v>0</v>
       </c>
       <c r="E37" s="68">
-        <v>46205</v>
+        <f>F36-2</f>
+        <v>46233</v>
       </c>
       <c r="F37" s="68">
-        <v>46217</v>
+        <f>E37+4</f>
+        <v>46237</v>
       </c>
       <c r="G37" s="17"/>
       <c r="H37" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I37" s="28"/>
       <c r="J37" s="28"/>
@@ -16830,28 +16787,28 @@
       <c r="MZ37" s="28"/>
       <c r="NA37" s="28"/>
     </row>
-    <row r="38" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="A38" s="41"/>
+    <row r="38" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="41" t="s">
+        <v>53</v>
+      </c>
       <c r="B38" s="69" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C38" s="66" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D38" s="67">
         <v>0</v>
       </c>
       <c r="E38" s="68">
-        <f>F35</f>
-        <v>46217</v>
+        <v>46235</v>
       </c>
       <c r="F38" s="68">
-        <f>E38+12</f>
-        <v>46229</v>
+        <v>46242</v>
       </c>
       <c r="G38" s="17"/>
       <c r="H38" s="17">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I38" s="28"/>
       <c r="J38" s="28"/>
@@ -17211,390 +17168,389 @@
       <c r="MZ38" s="28"/>
       <c r="NA38" s="28"/>
     </row>
-    <row r="39" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="A39" s="41"/>
+    <row r="39" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="42"/>
       <c r="B39" s="69" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C39" s="66" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D39" s="67">
         <v>0</v>
       </c>
       <c r="E39" s="68">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="F39" s="68">
-        <f>E39+12</f>
-        <v>46235</v>
+        <v>46243</v>
       </c>
       <c r="G39" s="17"/>
       <c r="H39" s="17">
-        <v>12</v>
-      </c>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
-      <c r="V39" s="28"/>
-      <c r="W39" s="28"/>
-      <c r="X39" s="28"/>
-      <c r="Y39" s="28"/>
-      <c r="Z39" s="28"/>
-      <c r="AA39" s="28"/>
-      <c r="AB39" s="28"/>
-      <c r="AC39" s="28"/>
-      <c r="AD39" s="28"/>
-      <c r="AE39" s="28"/>
-      <c r="AF39" s="28"/>
-      <c r="AG39" s="28"/>
-      <c r="AH39" s="28"/>
-      <c r="AI39" s="28"/>
-      <c r="AJ39" s="28"/>
-      <c r="AK39" s="28"/>
-      <c r="AL39" s="28"/>
-      <c r="AM39" s="28"/>
-      <c r="AN39" s="28"/>
-      <c r="AO39" s="28"/>
-      <c r="AP39" s="28"/>
-      <c r="AQ39" s="28"/>
-      <c r="AR39" s="28"/>
-      <c r="AS39" s="28"/>
-      <c r="AT39" s="28"/>
-      <c r="AU39" s="28"/>
-      <c r="AV39" s="28"/>
-      <c r="AW39" s="28"/>
-      <c r="AX39" s="28"/>
-      <c r="AY39" s="28"/>
-      <c r="AZ39" s="28"/>
-      <c r="BA39" s="28"/>
-      <c r="BB39" s="28"/>
-      <c r="BC39" s="28"/>
-      <c r="BD39" s="28"/>
-      <c r="BE39" s="28"/>
-      <c r="BF39" s="28"/>
-      <c r="BG39" s="28"/>
-      <c r="BH39" s="28"/>
-      <c r="BI39" s="28"/>
-      <c r="BJ39" s="28"/>
-      <c r="BK39" s="28"/>
-      <c r="BL39" s="28"/>
-      <c r="BM39" s="28"/>
-      <c r="BN39" s="28"/>
-      <c r="BO39" s="28"/>
-      <c r="BP39" s="28"/>
-      <c r="BQ39" s="28"/>
-      <c r="BR39" s="28"/>
-      <c r="BS39" s="28"/>
-      <c r="BT39" s="28"/>
-      <c r="BU39" s="28"/>
-      <c r="BV39" s="28"/>
-      <c r="BW39" s="28"/>
-      <c r="BX39" s="28"/>
-      <c r="BY39" s="28"/>
-      <c r="BZ39" s="28"/>
-      <c r="CA39" s="28"/>
-      <c r="CB39" s="28"/>
-      <c r="CC39" s="28"/>
-      <c r="CD39" s="28"/>
-      <c r="CE39" s="28"/>
-      <c r="CF39" s="28"/>
-      <c r="CG39" s="28"/>
-      <c r="CH39" s="28"/>
-      <c r="CI39" s="28"/>
-      <c r="CJ39" s="28"/>
-      <c r="CK39" s="28"/>
-      <c r="CL39" s="28"/>
-      <c r="CM39" s="28"/>
-      <c r="CN39" s="28"/>
-      <c r="CO39" s="28"/>
-      <c r="CP39" s="28"/>
-      <c r="CQ39" s="28"/>
-      <c r="CR39" s="28"/>
-      <c r="CS39" s="28"/>
-      <c r="CT39" s="28"/>
-      <c r="CU39" s="28"/>
-      <c r="CV39" s="28"/>
-      <c r="CW39" s="28"/>
-      <c r="CX39" s="28"/>
-      <c r="CY39" s="28"/>
-      <c r="CZ39" s="28"/>
-      <c r="DA39" s="28"/>
-      <c r="DB39" s="28"/>
-      <c r="DC39" s="28"/>
-      <c r="DD39" s="28"/>
-      <c r="DE39" s="28"/>
-      <c r="DF39" s="28"/>
-      <c r="DG39" s="28"/>
-      <c r="DH39" s="28"/>
-      <c r="DI39" s="28"/>
-      <c r="DJ39" s="28"/>
-      <c r="DK39" s="28"/>
-      <c r="DL39" s="28"/>
-      <c r="DM39" s="28"/>
-      <c r="DN39" s="28"/>
-      <c r="DO39" s="28"/>
-      <c r="DP39" s="28"/>
-      <c r="DQ39" s="28"/>
-      <c r="DR39" s="28"/>
-      <c r="DS39" s="28"/>
-      <c r="DT39" s="28"/>
-      <c r="DU39" s="28"/>
-      <c r="DV39" s="28"/>
-      <c r="DW39" s="28"/>
-      <c r="DX39" s="28"/>
-      <c r="DY39" s="28"/>
-      <c r="DZ39" s="28"/>
-      <c r="EA39" s="28"/>
-      <c r="EB39" s="28"/>
-      <c r="EC39" s="28"/>
-      <c r="ED39" s="28"/>
-      <c r="EE39" s="28"/>
-      <c r="EF39" s="28"/>
-      <c r="EG39" s="28"/>
-      <c r="EH39" s="28"/>
-      <c r="EI39" s="28"/>
-      <c r="EJ39" s="28"/>
-      <c r="EK39" s="28"/>
-      <c r="EL39" s="28"/>
-      <c r="EM39" s="28"/>
-      <c r="EN39" s="28"/>
-      <c r="EO39" s="28"/>
-      <c r="EP39" s="28"/>
-      <c r="EQ39" s="28"/>
-      <c r="ER39" s="28"/>
-      <c r="ES39" s="28"/>
-      <c r="ET39" s="28"/>
-      <c r="EU39" s="28"/>
-      <c r="EV39" s="28"/>
-      <c r="EW39" s="28"/>
-      <c r="EX39" s="28"/>
-      <c r="EY39" s="28"/>
-      <c r="EZ39" s="28"/>
-      <c r="FA39" s="28"/>
-      <c r="FB39" s="28"/>
-      <c r="FC39" s="28"/>
-      <c r="FD39" s="28"/>
-      <c r="FE39" s="28"/>
-      <c r="FF39" s="28"/>
-      <c r="FG39" s="28"/>
-      <c r="FH39" s="28"/>
-      <c r="FI39" s="28"/>
-      <c r="FJ39" s="28"/>
-      <c r="FK39" s="28"/>
-      <c r="FL39" s="28"/>
-      <c r="FM39" s="28"/>
-      <c r="FN39" s="28"/>
-      <c r="FO39" s="28"/>
-      <c r="FP39" s="28"/>
-      <c r="FQ39" s="28"/>
-      <c r="FR39" s="28"/>
-      <c r="FS39" s="28"/>
-      <c r="FT39" s="28"/>
-      <c r="FU39" s="28"/>
-      <c r="FV39" s="28"/>
-      <c r="FW39" s="28"/>
-      <c r="FX39" s="28"/>
-      <c r="FY39" s="28"/>
-      <c r="FZ39" s="28"/>
-      <c r="GA39" s="28"/>
-      <c r="GB39" s="28"/>
-      <c r="GC39" s="28"/>
-      <c r="GD39" s="28"/>
-      <c r="GE39" s="28"/>
-      <c r="GF39" s="28"/>
-      <c r="GG39" s="28"/>
-      <c r="GH39" s="28"/>
-      <c r="GI39" s="28"/>
-      <c r="GJ39" s="28"/>
-      <c r="GK39" s="28"/>
-      <c r="GL39" s="28"/>
-      <c r="GM39" s="28"/>
-      <c r="GN39" s="28"/>
-      <c r="GO39" s="28"/>
-      <c r="GP39" s="28"/>
-      <c r="GQ39" s="28"/>
-      <c r="GR39" s="28"/>
-      <c r="GS39" s="28"/>
-      <c r="GT39" s="28"/>
-      <c r="GU39" s="28"/>
-      <c r="GV39" s="28"/>
-      <c r="GW39" s="28"/>
-      <c r="GX39" s="28"/>
-      <c r="GY39" s="28"/>
-      <c r="GZ39" s="28"/>
-      <c r="HA39" s="28"/>
-      <c r="HB39" s="28"/>
-      <c r="HC39" s="28"/>
-      <c r="HD39" s="28"/>
-      <c r="HE39" s="28"/>
-      <c r="HF39" s="28"/>
-      <c r="HG39" s="28"/>
-      <c r="HH39" s="28"/>
-      <c r="HI39" s="28"/>
-      <c r="HJ39" s="28"/>
-      <c r="HK39" s="28"/>
-      <c r="HL39" s="28"/>
-      <c r="HM39" s="28"/>
-      <c r="HN39" s="28"/>
-      <c r="HO39" s="28"/>
-      <c r="HP39" s="28"/>
-      <c r="HQ39" s="28"/>
-      <c r="HR39" s="28"/>
-      <c r="HS39" s="28"/>
-      <c r="HT39" s="28"/>
-      <c r="HU39" s="28"/>
-      <c r="HV39" s="28"/>
-      <c r="HW39" s="28"/>
-      <c r="HX39" s="28"/>
-      <c r="HY39" s="28"/>
-      <c r="HZ39" s="28"/>
-      <c r="IA39" s="28"/>
-      <c r="IB39" s="28"/>
-      <c r="IC39" s="28"/>
-      <c r="ID39" s="28"/>
-      <c r="IE39" s="28"/>
-      <c r="IF39" s="28"/>
-      <c r="IG39" s="28"/>
-      <c r="IH39" s="28"/>
-      <c r="II39" s="28"/>
-      <c r="IJ39" s="28"/>
-      <c r="IK39" s="28"/>
-      <c r="IL39" s="28"/>
-      <c r="IM39" s="28"/>
-      <c r="IN39" s="28"/>
-      <c r="IO39" s="28"/>
-      <c r="IP39" s="28"/>
-      <c r="IQ39" s="28"/>
-      <c r="IR39" s="28"/>
-      <c r="IS39" s="28"/>
-      <c r="IT39" s="28"/>
-      <c r="IU39" s="28"/>
-      <c r="IV39" s="28"/>
-      <c r="IW39" s="28"/>
-      <c r="IX39" s="28"/>
-      <c r="IY39" s="28"/>
-      <c r="IZ39" s="28"/>
-      <c r="JA39" s="28"/>
-      <c r="JB39" s="28"/>
-      <c r="JC39" s="28"/>
-      <c r="JD39" s="28"/>
-      <c r="JE39" s="28"/>
-      <c r="JF39" s="28"/>
-      <c r="JG39" s="28"/>
-      <c r="JH39" s="28"/>
-      <c r="JI39" s="28"/>
-      <c r="JJ39" s="28"/>
-      <c r="JK39" s="28"/>
-      <c r="JL39" s="28"/>
-      <c r="JM39" s="28"/>
-      <c r="JN39" s="28"/>
-      <c r="JO39" s="28"/>
-      <c r="JP39" s="28"/>
-      <c r="JQ39" s="28"/>
-      <c r="JR39" s="28"/>
-      <c r="JS39" s="28"/>
-      <c r="JT39" s="28"/>
-      <c r="JU39" s="28"/>
-      <c r="JV39" s="28"/>
-      <c r="JW39" s="28"/>
-      <c r="JX39" s="28"/>
-      <c r="JY39" s="28"/>
-      <c r="JZ39" s="28"/>
-      <c r="KA39" s="28"/>
-      <c r="KB39" s="28"/>
-      <c r="KC39" s="28"/>
-      <c r="KD39" s="28"/>
-      <c r="KE39" s="28"/>
-      <c r="KF39" s="28"/>
-      <c r="KG39" s="28"/>
-      <c r="KH39" s="28"/>
-      <c r="KI39" s="28"/>
-      <c r="KJ39" s="28"/>
-      <c r="KK39" s="28"/>
-      <c r="KL39" s="28"/>
-      <c r="KM39" s="28"/>
-      <c r="KN39" s="28"/>
-      <c r="KO39" s="28"/>
-      <c r="KP39" s="28"/>
-      <c r="KQ39" s="28"/>
-      <c r="KR39" s="28"/>
-      <c r="KS39" s="28"/>
-      <c r="KT39" s="28"/>
-      <c r="KU39" s="28"/>
-      <c r="KV39" s="28"/>
-      <c r="KW39" s="28"/>
-      <c r="KX39" s="28"/>
-      <c r="KY39" s="28"/>
-      <c r="KZ39" s="28"/>
-      <c r="LA39" s="28"/>
-      <c r="LB39" s="28"/>
-      <c r="LC39" s="28"/>
-      <c r="LD39" s="28"/>
-      <c r="LE39" s="28"/>
-      <c r="LF39" s="28"/>
-      <c r="LG39" s="28"/>
-      <c r="LH39" s="28"/>
-      <c r="LI39" s="28"/>
-      <c r="LJ39" s="28"/>
-      <c r="LK39" s="28"/>
-      <c r="LL39" s="28"/>
-      <c r="LM39" s="28"/>
-      <c r="LN39" s="28"/>
-      <c r="LO39" s="28"/>
-      <c r="LP39" s="28"/>
-      <c r="LQ39" s="28"/>
-      <c r="LR39" s="28"/>
-      <c r="LS39" s="28"/>
-      <c r="LT39" s="28"/>
-      <c r="LU39" s="28"/>
-      <c r="LV39" s="28"/>
-      <c r="LW39" s="28"/>
-      <c r="LX39" s="28"/>
-      <c r="LY39" s="28"/>
-      <c r="LZ39" s="28"/>
-      <c r="MA39" s="28"/>
-      <c r="MB39" s="28"/>
-      <c r="MC39" s="28"/>
-      <c r="MD39" s="28"/>
-      <c r="ME39" s="28"/>
-      <c r="MF39" s="28"/>
-      <c r="MG39" s="28"/>
-      <c r="MH39" s="28"/>
-      <c r="MI39" s="28"/>
-      <c r="MJ39" s="28"/>
-      <c r="MK39" s="28"/>
-      <c r="ML39" s="28"/>
-      <c r="MM39" s="28"/>
-      <c r="MN39" s="28"/>
-      <c r="MO39" s="28"/>
-      <c r="MP39" s="28"/>
-      <c r="MQ39" s="28"/>
-      <c r="MR39" s="28"/>
-      <c r="MS39" s="28"/>
-      <c r="MT39" s="28"/>
-      <c r="MU39" s="28"/>
-      <c r="MV39" s="28"/>
-      <c r="MW39" s="28"/>
-      <c r="MX39" s="28"/>
-      <c r="MY39" s="28"/>
-      <c r="MZ39" s="28"/>
-      <c r="NA39" s="28"/>
+        <v>5</v>
+      </c>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="71"/>
+      <c r="M39" s="71"/>
+      <c r="N39" s="71"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="71"/>
+      <c r="S39" s="71"/>
+      <c r="T39" s="71"/>
+      <c r="U39" s="71"/>
+      <c r="V39" s="71"/>
+      <c r="W39" s="71"/>
+      <c r="X39" s="71"/>
+      <c r="Y39" s="71"/>
+      <c r="Z39" s="71"/>
+      <c r="AA39" s="71"/>
+      <c r="AB39" s="71"/>
+      <c r="AC39" s="71"/>
+      <c r="AD39" s="71"/>
+      <c r="AE39" s="71"/>
+      <c r="AF39" s="71"/>
+      <c r="AG39" s="71"/>
+      <c r="AH39" s="71"/>
+      <c r="AI39" s="71"/>
+      <c r="AJ39" s="71"/>
+      <c r="AK39" s="71"/>
+      <c r="AL39" s="71"/>
+      <c r="AM39" s="71"/>
+      <c r="AN39" s="71"/>
+      <c r="AO39" s="71"/>
+      <c r="AP39" s="71"/>
+      <c r="AQ39" s="71"/>
+      <c r="AR39" s="71"/>
+      <c r="AS39" s="71"/>
+      <c r="AT39" s="71"/>
+      <c r="AU39" s="71"/>
+      <c r="AV39" s="71"/>
+      <c r="AW39" s="71"/>
+      <c r="AX39" s="71"/>
+      <c r="AY39" s="71"/>
+      <c r="AZ39" s="71"/>
+      <c r="BA39" s="71"/>
+      <c r="BB39" s="71"/>
+      <c r="BC39" s="71"/>
+      <c r="BD39" s="71"/>
+      <c r="BE39" s="71"/>
+      <c r="BF39" s="71"/>
+      <c r="BG39" s="71"/>
+      <c r="BH39" s="71"/>
+      <c r="BI39" s="71"/>
+      <c r="BJ39" s="71"/>
+      <c r="BK39" s="71"/>
+      <c r="BL39" s="71"/>
+      <c r="BM39" s="71"/>
+      <c r="BN39" s="71"/>
+      <c r="BO39" s="71"/>
+      <c r="BP39" s="71"/>
+      <c r="BQ39" s="71"/>
+      <c r="BR39" s="71"/>
+      <c r="BS39" s="71"/>
+      <c r="BT39" s="71"/>
+      <c r="BU39" s="71"/>
+      <c r="BV39" s="71"/>
+      <c r="BW39" s="71"/>
+      <c r="BX39" s="71"/>
+      <c r="BY39" s="71"/>
+      <c r="BZ39" s="71"/>
+      <c r="CA39" s="71"/>
+      <c r="CB39" s="71"/>
+      <c r="CC39" s="71"/>
+      <c r="CD39" s="71"/>
+      <c r="CE39" s="71"/>
+      <c r="CF39" s="71"/>
+      <c r="CG39" s="71"/>
+      <c r="CH39" s="71"/>
+      <c r="CI39" s="71"/>
+      <c r="CJ39" s="71"/>
+      <c r="CK39" s="71"/>
+      <c r="CL39" s="71"/>
+      <c r="CM39" s="71"/>
+      <c r="CN39" s="71"/>
+      <c r="CO39" s="71"/>
+      <c r="CP39" s="71"/>
+      <c r="CQ39" s="71"/>
+      <c r="CR39" s="71"/>
+      <c r="CS39" s="71"/>
+      <c r="CT39" s="71"/>
+      <c r="CU39" s="71"/>
+      <c r="CV39" s="71"/>
+      <c r="CW39" s="71"/>
+      <c r="CX39" s="71"/>
+      <c r="CY39" s="71"/>
+      <c r="CZ39" s="71"/>
+      <c r="DA39" s="71"/>
+      <c r="DB39" s="71"/>
+      <c r="DC39" s="71"/>
+      <c r="DD39" s="71"/>
+      <c r="DE39" s="71"/>
+      <c r="DF39" s="71"/>
+      <c r="DG39" s="71"/>
+      <c r="DH39" s="71"/>
+      <c r="DI39" s="71"/>
+      <c r="DJ39" s="71"/>
+      <c r="DK39" s="71"/>
+      <c r="DL39" s="71"/>
+      <c r="DM39" s="71"/>
+      <c r="DN39" s="71"/>
+      <c r="DO39" s="71"/>
+      <c r="DP39" s="71"/>
+      <c r="DQ39" s="71"/>
+      <c r="DR39" s="71"/>
+      <c r="DS39" s="71"/>
+      <c r="DT39" s="71"/>
+      <c r="DU39" s="71"/>
+      <c r="DV39" s="71"/>
+      <c r="DW39" s="71"/>
+      <c r="DX39" s="71"/>
+      <c r="DY39" s="71"/>
+      <c r="DZ39" s="71"/>
+      <c r="EA39" s="71"/>
+      <c r="EB39" s="71"/>
+      <c r="EC39" s="71"/>
+      <c r="ED39" s="71"/>
+      <c r="EE39" s="71"/>
+      <c r="EF39" s="71"/>
+      <c r="EG39" s="71"/>
+      <c r="EH39" s="71"/>
+      <c r="EI39" s="71"/>
+      <c r="EJ39" s="71"/>
+      <c r="EK39" s="71"/>
+      <c r="EL39" s="71"/>
+      <c r="EM39" s="71"/>
+      <c r="EN39" s="71"/>
+      <c r="EO39" s="71"/>
+      <c r="EP39" s="71"/>
+      <c r="EQ39" s="71"/>
+      <c r="ER39" s="71"/>
+      <c r="ES39" s="71"/>
+      <c r="ET39" s="71"/>
+      <c r="EU39" s="71"/>
+      <c r="EV39" s="71"/>
+      <c r="EW39" s="71"/>
+      <c r="EX39" s="71"/>
+      <c r="EY39" s="71"/>
+      <c r="EZ39" s="71"/>
+      <c r="FA39" s="71"/>
+      <c r="FB39" s="71"/>
+      <c r="FC39" s="71"/>
+      <c r="FD39" s="71"/>
+      <c r="FE39" s="71"/>
+      <c r="FF39" s="71"/>
+      <c r="FG39" s="71"/>
+      <c r="FH39" s="71"/>
+      <c r="FI39" s="71"/>
+      <c r="FJ39" s="71"/>
+      <c r="FK39" s="71"/>
+      <c r="FL39" s="71"/>
+      <c r="FM39" s="71"/>
+      <c r="FN39" s="71"/>
+      <c r="FO39" s="71"/>
+      <c r="FP39" s="71"/>
+      <c r="FQ39" s="71"/>
+      <c r="FR39" s="71"/>
+      <c r="FS39" s="71"/>
+      <c r="FT39" s="71"/>
+      <c r="FU39" s="71"/>
+      <c r="FV39" s="71"/>
+      <c r="FW39" s="71"/>
+      <c r="FX39" s="71"/>
+      <c r="FY39" s="71"/>
+      <c r="FZ39" s="71"/>
+      <c r="GA39" s="71"/>
+      <c r="GB39" s="71"/>
+      <c r="GC39" s="71"/>
+      <c r="GD39" s="71"/>
+      <c r="GE39" s="71"/>
+      <c r="GF39" s="71"/>
+      <c r="GG39" s="71"/>
+      <c r="GH39" s="71"/>
+      <c r="GI39" s="71"/>
+      <c r="GJ39" s="71"/>
+      <c r="GK39" s="71"/>
+      <c r="GL39" s="71"/>
+      <c r="GM39" s="71"/>
+      <c r="GN39" s="71"/>
+      <c r="GO39" s="71"/>
+      <c r="GP39" s="71"/>
+      <c r="GQ39" s="71"/>
+      <c r="GR39" s="71"/>
+      <c r="GS39" s="71"/>
+      <c r="GT39" s="71"/>
+      <c r="GU39" s="71"/>
+      <c r="GV39" s="71"/>
+      <c r="GW39" s="71"/>
+      <c r="GX39" s="71"/>
+      <c r="GY39" s="71"/>
+      <c r="GZ39" s="71"/>
+      <c r="HA39" s="71"/>
+      <c r="HB39" s="71"/>
+      <c r="HC39" s="71"/>
+      <c r="HD39" s="71"/>
+      <c r="HE39" s="71"/>
+      <c r="HF39" s="71"/>
+      <c r="HG39" s="71"/>
+      <c r="HH39" s="71"/>
+      <c r="HI39" s="71"/>
+      <c r="HJ39" s="71"/>
+      <c r="HK39" s="71"/>
+      <c r="HL39" s="71"/>
+      <c r="HM39" s="71"/>
+      <c r="HN39" s="71"/>
+      <c r="HO39" s="71"/>
+      <c r="HP39" s="71"/>
+      <c r="HQ39" s="71"/>
+      <c r="HR39" s="71"/>
+      <c r="HS39" s="71"/>
+      <c r="HT39" s="71"/>
+      <c r="HU39" s="71"/>
+      <c r="HV39" s="71"/>
+      <c r="HW39" s="71"/>
+      <c r="HX39" s="71"/>
+      <c r="HY39" s="71"/>
+      <c r="HZ39" s="71"/>
+      <c r="IA39" s="71"/>
+      <c r="IB39" s="71"/>
+      <c r="IC39" s="71"/>
+      <c r="ID39" s="71"/>
+      <c r="IE39" s="71"/>
+      <c r="IF39" s="71"/>
+      <c r="IG39" s="71"/>
+      <c r="IH39" s="71"/>
+      <c r="II39" s="71"/>
+      <c r="IJ39" s="71"/>
+      <c r="IK39" s="71"/>
+      <c r="IL39" s="71"/>
+      <c r="IM39" s="71"/>
+      <c r="IN39" s="71"/>
+      <c r="IO39" s="71"/>
+      <c r="IP39" s="71"/>
+      <c r="IQ39" s="71"/>
+      <c r="IR39" s="71"/>
+      <c r="IS39" s="71"/>
+      <c r="IT39" s="71"/>
+      <c r="IU39" s="71"/>
+      <c r="IV39" s="71"/>
+      <c r="IW39" s="71"/>
+      <c r="IX39" s="71"/>
+      <c r="IY39" s="71"/>
+      <c r="IZ39" s="71"/>
+      <c r="JA39" s="71"/>
+      <c r="JB39" s="71"/>
+      <c r="JC39" s="71"/>
+      <c r="JD39" s="71"/>
+      <c r="JE39" s="71"/>
+      <c r="JF39" s="71"/>
+      <c r="JG39" s="71"/>
+      <c r="JH39" s="71"/>
+      <c r="JI39" s="71"/>
+      <c r="JJ39" s="71"/>
+      <c r="JK39" s="71"/>
+      <c r="JL39" s="71"/>
+      <c r="JM39" s="71"/>
+      <c r="JN39" s="71"/>
+      <c r="JO39" s="71"/>
+      <c r="JP39" s="71"/>
+      <c r="JQ39" s="71"/>
+      <c r="JR39" s="71"/>
+      <c r="JS39" s="71"/>
+      <c r="JT39" s="71"/>
+      <c r="JU39" s="71"/>
+      <c r="JV39" s="71"/>
+      <c r="JW39" s="71"/>
+      <c r="JX39" s="71"/>
+      <c r="JY39" s="71"/>
+      <c r="JZ39" s="71"/>
+      <c r="KA39" s="71"/>
+      <c r="KB39" s="71"/>
+      <c r="KC39" s="71"/>
+      <c r="KD39" s="71"/>
+      <c r="KE39" s="71"/>
+      <c r="KF39" s="71"/>
+      <c r="KG39" s="71"/>
+      <c r="KH39" s="71"/>
+      <c r="KI39" s="71"/>
+      <c r="KJ39" s="71"/>
+      <c r="KK39" s="71"/>
+      <c r="KL39" s="71"/>
+      <c r="KM39" s="71"/>
+      <c r="KN39" s="71"/>
+      <c r="KO39" s="71"/>
+      <c r="KP39" s="71"/>
+      <c r="KQ39" s="71"/>
+      <c r="KR39" s="71"/>
+      <c r="KS39" s="71"/>
+      <c r="KT39" s="71"/>
+      <c r="KU39" s="71"/>
+      <c r="KV39" s="71"/>
+      <c r="KW39" s="71"/>
+      <c r="KX39" s="71"/>
+      <c r="KY39" s="71"/>
+      <c r="KZ39" s="71"/>
+      <c r="LA39" s="71"/>
+      <c r="LB39" s="71"/>
+      <c r="LC39" s="71"/>
+      <c r="LD39" s="71"/>
+      <c r="LE39" s="71"/>
+      <c r="LF39" s="71"/>
+      <c r="LG39" s="71"/>
+      <c r="LH39" s="71"/>
+      <c r="LI39" s="71"/>
+      <c r="LJ39" s="71"/>
+      <c r="LK39" s="71"/>
+      <c r="LL39" s="71"/>
+      <c r="LM39" s="71"/>
+      <c r="LN39" s="71"/>
+      <c r="LO39" s="71"/>
+      <c r="LP39" s="71"/>
+      <c r="LQ39" s="71"/>
+      <c r="LR39" s="71"/>
+      <c r="LS39" s="71"/>
+      <c r="LT39" s="71"/>
+      <c r="LU39" s="71"/>
+      <c r="LV39" s="71"/>
+      <c r="LW39" s="71"/>
+      <c r="LX39" s="71"/>
+      <c r="LY39" s="71"/>
+      <c r="LZ39" s="71"/>
+      <c r="MA39" s="71"/>
+      <c r="MB39" s="71"/>
+      <c r="MC39" s="71"/>
+      <c r="MD39" s="71"/>
+      <c r="ME39" s="71"/>
+      <c r="MF39" s="71"/>
+      <c r="MG39" s="71"/>
+      <c r="MH39" s="71"/>
+      <c r="MI39" s="71"/>
+      <c r="MJ39" s="71"/>
+      <c r="MK39" s="71"/>
+      <c r="ML39" s="71"/>
+      <c r="MM39" s="71"/>
+      <c r="MN39" s="71"/>
+      <c r="MO39" s="71"/>
+      <c r="MP39" s="71"/>
+      <c r="MQ39" s="71"/>
+      <c r="MR39" s="71"/>
+      <c r="MS39" s="71"/>
+      <c r="MT39" s="71"/>
+      <c r="MU39" s="71"/>
+      <c r="MV39" s="71"/>
+      <c r="MW39" s="71"/>
+      <c r="MX39" s="71"/>
+      <c r="MY39" s="71"/>
+      <c r="MZ39" s="71"/>
+      <c r="NA39" s="71"/>
     </row>
-    <row r="40" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A40" s="41"/>
+    <row r="40" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="42"/>
       <c r="B40" s="69" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C40" s="66" t="s">
         <v>21</v>
@@ -17603,2687 +17559,408 @@
         <v>0</v>
       </c>
       <c r="E40" s="68">
-        <f>F38</f>
-        <v>46229</v>
+        <v>46245</v>
       </c>
       <c r="F40" s="68">
-        <v>46235</v>
+        <v>46245</v>
       </c>
       <c r="G40" s="17"/>
       <c r="H40" s="17">
-        <v>20</v>
-      </c>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="28"/>
-      <c r="V40" s="28"/>
-      <c r="W40" s="28"/>
-      <c r="X40" s="28"/>
-      <c r="Y40" s="28"/>
-      <c r="Z40" s="28"/>
-      <c r="AA40" s="28"/>
-      <c r="AB40" s="28"/>
-      <c r="AC40" s="28"/>
-      <c r="AD40" s="28"/>
-      <c r="AE40" s="28"/>
-      <c r="AF40" s="28"/>
-      <c r="AG40" s="28"/>
-      <c r="AH40" s="28"/>
-      <c r="AI40" s="28"/>
-      <c r="AJ40" s="28"/>
-      <c r="AK40" s="28"/>
-      <c r="AL40" s="28"/>
-      <c r="AM40" s="28"/>
-      <c r="AN40" s="28"/>
-      <c r="AO40" s="28"/>
-      <c r="AP40" s="28"/>
-      <c r="AQ40" s="28"/>
-      <c r="AR40" s="28"/>
-      <c r="AS40" s="28"/>
-      <c r="AT40" s="28"/>
-      <c r="AU40" s="28"/>
-      <c r="AV40" s="28"/>
-      <c r="AW40" s="28"/>
-      <c r="AX40" s="28"/>
-      <c r="AY40" s="28"/>
-      <c r="AZ40" s="28"/>
-      <c r="BA40" s="28"/>
-      <c r="BB40" s="28"/>
-      <c r="BC40" s="28"/>
-      <c r="BD40" s="28"/>
-      <c r="BE40" s="28"/>
-      <c r="BF40" s="28"/>
-      <c r="BG40" s="28"/>
-      <c r="BH40" s="28"/>
-      <c r="BI40" s="28"/>
-      <c r="BJ40" s="28"/>
-      <c r="BK40" s="28"/>
-      <c r="BL40" s="28"/>
-      <c r="BM40" s="28"/>
-      <c r="BN40" s="28"/>
-      <c r="BO40" s="28"/>
-      <c r="BP40" s="28"/>
-      <c r="BQ40" s="28"/>
-      <c r="BR40" s="28"/>
-      <c r="BS40" s="28"/>
-      <c r="BT40" s="28"/>
-      <c r="BU40" s="28"/>
-      <c r="BV40" s="28"/>
-      <c r="BW40" s="28"/>
-      <c r="BX40" s="28"/>
-      <c r="BY40" s="28"/>
-      <c r="BZ40" s="28"/>
-      <c r="CA40" s="28"/>
-      <c r="CB40" s="28"/>
-      <c r="CC40" s="28"/>
-      <c r="CD40" s="28"/>
-      <c r="CE40" s="28"/>
-      <c r="CF40" s="28"/>
-      <c r="CG40" s="28"/>
-      <c r="CH40" s="28"/>
-      <c r="CI40" s="28"/>
-      <c r="CJ40" s="28"/>
-      <c r="CK40" s="28"/>
-      <c r="CL40" s="28"/>
-      <c r="CM40" s="28"/>
-      <c r="CN40" s="28"/>
-      <c r="CO40" s="28"/>
-      <c r="CP40" s="28"/>
-      <c r="CQ40" s="28"/>
-      <c r="CR40" s="28"/>
-      <c r="CS40" s="28"/>
-      <c r="CT40" s="28"/>
-      <c r="CU40" s="28"/>
-      <c r="CV40" s="28"/>
-      <c r="CW40" s="28"/>
-      <c r="CX40" s="28"/>
-      <c r="CY40" s="28"/>
-      <c r="CZ40" s="28"/>
-      <c r="DA40" s="28"/>
-      <c r="DB40" s="28"/>
-      <c r="DC40" s="28"/>
-      <c r="DD40" s="28"/>
-      <c r="DE40" s="28"/>
-      <c r="DF40" s="28"/>
-      <c r="DG40" s="28"/>
-      <c r="DH40" s="28"/>
-      <c r="DI40" s="28"/>
-      <c r="DJ40" s="28"/>
-      <c r="DK40" s="28"/>
-      <c r="DL40" s="28"/>
-      <c r="DM40" s="28"/>
-      <c r="DN40" s="28"/>
-      <c r="DO40" s="28"/>
-      <c r="DP40" s="28"/>
-      <c r="DQ40" s="28"/>
-      <c r="DR40" s="28"/>
-      <c r="DS40" s="28"/>
-      <c r="DT40" s="28"/>
-      <c r="DU40" s="28"/>
-      <c r="DV40" s="28"/>
-      <c r="DW40" s="28"/>
-      <c r="DX40" s="28"/>
-      <c r="DY40" s="28"/>
-      <c r="DZ40" s="28"/>
-      <c r="EA40" s="28"/>
-      <c r="EB40" s="28"/>
-      <c r="EC40" s="28"/>
-      <c r="ED40" s="28"/>
-      <c r="EE40" s="28"/>
-      <c r="EF40" s="28"/>
-      <c r="EG40" s="28"/>
-      <c r="EH40" s="28"/>
-      <c r="EI40" s="28"/>
-      <c r="EJ40" s="28"/>
-      <c r="EK40" s="28"/>
-      <c r="EL40" s="28"/>
-      <c r="EM40" s="28"/>
-      <c r="EN40" s="28"/>
-      <c r="EO40" s="28"/>
-      <c r="EP40" s="28"/>
-      <c r="EQ40" s="28"/>
-      <c r="ER40" s="28"/>
-      <c r="ES40" s="28"/>
-      <c r="ET40" s="28"/>
-      <c r="EU40" s="28"/>
-      <c r="EV40" s="28"/>
-      <c r="EW40" s="28"/>
-      <c r="EX40" s="28"/>
-      <c r="EY40" s="28"/>
-      <c r="EZ40" s="28"/>
-      <c r="FA40" s="28"/>
-      <c r="FB40" s="28"/>
-      <c r="FC40" s="28"/>
-      <c r="FD40" s="28"/>
-      <c r="FE40" s="28"/>
-      <c r="FF40" s="28"/>
-      <c r="FG40" s="28"/>
-      <c r="FH40" s="28"/>
-      <c r="FI40" s="28"/>
-      <c r="FJ40" s="28"/>
-      <c r="FK40" s="28"/>
-      <c r="FL40" s="28"/>
-      <c r="FM40" s="28"/>
-      <c r="FN40" s="28"/>
-      <c r="FO40" s="28"/>
-      <c r="FP40" s="28"/>
-      <c r="FQ40" s="28"/>
-      <c r="FR40" s="28"/>
-      <c r="FS40" s="28"/>
-      <c r="FT40" s="28"/>
-      <c r="FU40" s="28"/>
-      <c r="FV40" s="28"/>
-      <c r="FW40" s="28"/>
-      <c r="FX40" s="28"/>
-      <c r="FY40" s="28"/>
-      <c r="FZ40" s="28"/>
-      <c r="GA40" s="28"/>
-      <c r="GB40" s="28"/>
-      <c r="GC40" s="28"/>
-      <c r="GD40" s="28"/>
-      <c r="GE40" s="28"/>
-      <c r="GF40" s="28"/>
-      <c r="GG40" s="28"/>
-      <c r="GH40" s="28"/>
-      <c r="GI40" s="28"/>
-      <c r="GJ40" s="28"/>
-      <c r="GK40" s="28"/>
-      <c r="GL40" s="28"/>
-      <c r="GM40" s="28"/>
-      <c r="GN40" s="28"/>
-      <c r="GO40" s="28"/>
-      <c r="GP40" s="28"/>
-      <c r="GQ40" s="28"/>
-      <c r="GR40" s="28"/>
-      <c r="GS40" s="28"/>
-      <c r="GT40" s="28"/>
-      <c r="GU40" s="28"/>
-      <c r="GV40" s="28"/>
-      <c r="GW40" s="28"/>
-      <c r="GX40" s="28"/>
-      <c r="GY40" s="28"/>
-      <c r="GZ40" s="28"/>
-      <c r="HA40" s="28"/>
-      <c r="HB40" s="28"/>
-      <c r="HC40" s="28"/>
-      <c r="HD40" s="28"/>
-      <c r="HE40" s="28"/>
-      <c r="HF40" s="28"/>
-      <c r="HG40" s="28"/>
-      <c r="HH40" s="28"/>
-      <c r="HI40" s="28"/>
-      <c r="HJ40" s="28"/>
-      <c r="HK40" s="28"/>
-      <c r="HL40" s="28"/>
-      <c r="HM40" s="28"/>
-      <c r="HN40" s="28"/>
-      <c r="HO40" s="28"/>
-      <c r="HP40" s="28"/>
-      <c r="HQ40" s="28"/>
-      <c r="HR40" s="28"/>
-      <c r="HS40" s="28"/>
-      <c r="HT40" s="28"/>
-      <c r="HU40" s="28"/>
-      <c r="HV40" s="28"/>
-      <c r="HW40" s="28"/>
-      <c r="HX40" s="28"/>
-      <c r="HY40" s="28"/>
-      <c r="HZ40" s="28"/>
-      <c r="IA40" s="28"/>
-      <c r="IB40" s="28"/>
-      <c r="IC40" s="28"/>
-      <c r="ID40" s="28"/>
-      <c r="IE40" s="28"/>
-      <c r="IF40" s="28"/>
-      <c r="IG40" s="28"/>
-      <c r="IH40" s="28"/>
-      <c r="II40" s="28"/>
-      <c r="IJ40" s="28"/>
-      <c r="IK40" s="28"/>
-      <c r="IL40" s="28"/>
-      <c r="IM40" s="28"/>
-      <c r="IN40" s="28"/>
-      <c r="IO40" s="28"/>
-      <c r="IP40" s="28"/>
-      <c r="IQ40" s="28"/>
-      <c r="IR40" s="28"/>
-      <c r="IS40" s="28"/>
-      <c r="IT40" s="28"/>
-      <c r="IU40" s="28"/>
-      <c r="IV40" s="28"/>
-      <c r="IW40" s="28"/>
-      <c r="IX40" s="28"/>
-      <c r="IY40" s="28"/>
-      <c r="IZ40" s="28"/>
-      <c r="JA40" s="28"/>
-      <c r="JB40" s="28"/>
-      <c r="JC40" s="28"/>
-      <c r="JD40" s="28"/>
-      <c r="JE40" s="28"/>
-      <c r="JF40" s="28"/>
-      <c r="JG40" s="28"/>
-      <c r="JH40" s="28"/>
-      <c r="JI40" s="28"/>
-      <c r="JJ40" s="28"/>
-      <c r="JK40" s="28"/>
-      <c r="JL40" s="28"/>
-      <c r="JM40" s="28"/>
-      <c r="JN40" s="28"/>
-      <c r="JO40" s="28"/>
-      <c r="JP40" s="28"/>
-      <c r="JQ40" s="28"/>
-      <c r="JR40" s="28"/>
-      <c r="JS40" s="28"/>
-      <c r="JT40" s="28"/>
-      <c r="JU40" s="28"/>
-      <c r="JV40" s="28"/>
-      <c r="JW40" s="28"/>
-      <c r="JX40" s="28"/>
-      <c r="JY40" s="28"/>
-      <c r="JZ40" s="28"/>
-      <c r="KA40" s="28"/>
-      <c r="KB40" s="28"/>
-      <c r="KC40" s="28"/>
-      <c r="KD40" s="28"/>
-      <c r="KE40" s="28"/>
-      <c r="KF40" s="28"/>
-      <c r="KG40" s="28"/>
-      <c r="KH40" s="28"/>
-      <c r="KI40" s="28"/>
-      <c r="KJ40" s="28"/>
-      <c r="KK40" s="28"/>
-      <c r="KL40" s="28"/>
-      <c r="KM40" s="28"/>
-      <c r="KN40" s="28"/>
-      <c r="KO40" s="28"/>
-      <c r="KP40" s="28"/>
-      <c r="KQ40" s="28"/>
-      <c r="KR40" s="28"/>
-      <c r="KS40" s="28"/>
-      <c r="KT40" s="28"/>
-      <c r="KU40" s="28"/>
-      <c r="KV40" s="28"/>
-      <c r="KW40" s="28"/>
-      <c r="KX40" s="28"/>
-      <c r="KY40" s="28"/>
-      <c r="KZ40" s="28"/>
-      <c r="LA40" s="28"/>
-      <c r="LB40" s="28"/>
-      <c r="LC40" s="28"/>
-      <c r="LD40" s="28"/>
-      <c r="LE40" s="28"/>
-      <c r="LF40" s="28"/>
-      <c r="LG40" s="28"/>
-      <c r="LH40" s="28"/>
-      <c r="LI40" s="28"/>
-      <c r="LJ40" s="28"/>
-      <c r="LK40" s="28"/>
-      <c r="LL40" s="28"/>
-      <c r="LM40" s="28"/>
-      <c r="LN40" s="28"/>
-      <c r="LO40" s="28"/>
-      <c r="LP40" s="28"/>
-      <c r="LQ40" s="28"/>
-      <c r="LR40" s="28"/>
-      <c r="LS40" s="28"/>
-      <c r="LT40" s="28"/>
-      <c r="LU40" s="28"/>
-      <c r="LV40" s="28"/>
-      <c r="LW40" s="28"/>
-      <c r="LX40" s="28"/>
-      <c r="LY40" s="28"/>
-      <c r="LZ40" s="28"/>
-      <c r="MA40" s="28"/>
-      <c r="MB40" s="28"/>
-      <c r="MC40" s="28"/>
-      <c r="MD40" s="28"/>
-      <c r="ME40" s="28"/>
-      <c r="MF40" s="28"/>
-      <c r="MG40" s="28"/>
-      <c r="MH40" s="28"/>
-      <c r="MI40" s="28"/>
-      <c r="MJ40" s="28"/>
-      <c r="MK40" s="28"/>
-      <c r="ML40" s="28"/>
-      <c r="MM40" s="28"/>
-      <c r="MN40" s="28"/>
-      <c r="MO40" s="28"/>
-      <c r="MP40" s="28"/>
-      <c r="MQ40" s="28"/>
-      <c r="MR40" s="28"/>
-      <c r="MS40" s="28"/>
-      <c r="MT40" s="28"/>
-      <c r="MU40" s="28"/>
-      <c r="MV40" s="28"/>
-      <c r="MW40" s="28"/>
-      <c r="MX40" s="28"/>
-      <c r="MY40" s="28"/>
-      <c r="MZ40" s="28"/>
-      <c r="NA40" s="28"/>
+        <v>1</v>
+      </c>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="71"/>
+      <c r="M40" s="71"/>
+      <c r="N40" s="71"/>
+      <c r="O40" s="71"/>
+      <c r="P40" s="71"/>
+      <c r="Q40" s="71"/>
+      <c r="R40" s="71"/>
+      <c r="S40" s="71"/>
+      <c r="T40" s="71"/>
+      <c r="U40" s="71"/>
+      <c r="V40" s="71"/>
+      <c r="W40" s="71"/>
+      <c r="X40" s="71"/>
+      <c r="Y40" s="71"/>
+      <c r="Z40" s="71"/>
+      <c r="AA40" s="71"/>
+      <c r="AB40" s="71"/>
+      <c r="AC40" s="71"/>
+      <c r="AD40" s="71"/>
+      <c r="AE40" s="71"/>
+      <c r="AF40" s="71"/>
+      <c r="AG40" s="71"/>
+      <c r="AH40" s="71"/>
+      <c r="AI40" s="71"/>
+      <c r="AJ40" s="71"/>
+      <c r="AK40" s="71"/>
+      <c r="AL40" s="71"/>
+      <c r="AM40" s="71"/>
+      <c r="AN40" s="71"/>
+      <c r="AO40" s="71"/>
+      <c r="AP40" s="71"/>
+      <c r="AQ40" s="71"/>
+      <c r="AR40" s="71"/>
+      <c r="AS40" s="71"/>
+      <c r="AT40" s="71"/>
+      <c r="AU40" s="71"/>
+      <c r="AV40" s="71"/>
+      <c r="AW40" s="71"/>
+      <c r="AX40" s="71"/>
+      <c r="AY40" s="71"/>
+      <c r="AZ40" s="71"/>
+      <c r="BA40" s="71"/>
+      <c r="BB40" s="71"/>
+      <c r="BC40" s="71"/>
+      <c r="BD40" s="71"/>
+      <c r="BE40" s="71"/>
+      <c r="BF40" s="71"/>
+      <c r="BG40" s="71"/>
+      <c r="BH40" s="71"/>
+      <c r="BI40" s="71"/>
+      <c r="BJ40" s="71"/>
+      <c r="BK40" s="71"/>
+      <c r="BL40" s="71"/>
+      <c r="BM40" s="71"/>
+      <c r="BN40" s="71"/>
+      <c r="BO40" s="71"/>
+      <c r="BP40" s="71"/>
+      <c r="BQ40" s="71"/>
+      <c r="BR40" s="71"/>
+      <c r="BS40" s="71"/>
+      <c r="BT40" s="71"/>
+      <c r="BU40" s="71"/>
+      <c r="BV40" s="71"/>
+      <c r="BW40" s="71"/>
+      <c r="BX40" s="71"/>
+      <c r="BY40" s="71"/>
+      <c r="BZ40" s="71"/>
+      <c r="CA40" s="71"/>
+      <c r="CB40" s="71"/>
+      <c r="CC40" s="71"/>
+      <c r="CD40" s="71"/>
+      <c r="CE40" s="71"/>
+      <c r="CF40" s="71"/>
+      <c r="CG40" s="71"/>
+      <c r="CH40" s="71"/>
+      <c r="CI40" s="71"/>
+      <c r="CJ40" s="71"/>
+      <c r="CK40" s="71"/>
+      <c r="CL40" s="71"/>
+      <c r="CM40" s="71"/>
+      <c r="CN40" s="71"/>
+      <c r="CO40" s="71"/>
+      <c r="CP40" s="71"/>
+      <c r="CQ40" s="71"/>
+      <c r="CR40" s="71"/>
+      <c r="CS40" s="71"/>
+      <c r="CT40" s="71"/>
+      <c r="CU40" s="71"/>
+      <c r="CV40" s="71"/>
+      <c r="CW40" s="71"/>
+      <c r="CX40" s="71"/>
+      <c r="CY40" s="71"/>
+      <c r="CZ40" s="71"/>
+      <c r="DA40" s="71"/>
+      <c r="DB40" s="71"/>
+      <c r="DC40" s="71"/>
+      <c r="DD40" s="71"/>
+      <c r="DE40" s="71"/>
+      <c r="DF40" s="71"/>
+      <c r="DG40" s="71"/>
+      <c r="DH40" s="71"/>
+      <c r="DI40" s="71"/>
+      <c r="DJ40" s="71"/>
+      <c r="DK40" s="71"/>
+      <c r="DL40" s="71"/>
+      <c r="DM40" s="71"/>
+      <c r="DN40" s="71"/>
+      <c r="DO40" s="71"/>
+      <c r="DP40" s="71"/>
+      <c r="DQ40" s="71"/>
+      <c r="DR40" s="71"/>
+      <c r="DS40" s="71"/>
+      <c r="DT40" s="71"/>
+      <c r="DU40" s="71"/>
+      <c r="DV40" s="71"/>
+      <c r="DW40" s="71"/>
+      <c r="DX40" s="71"/>
+      <c r="DY40" s="71"/>
+      <c r="DZ40" s="71"/>
+      <c r="EA40" s="71"/>
+      <c r="EB40" s="71"/>
+      <c r="EC40" s="71"/>
+      <c r="ED40" s="71"/>
+      <c r="EE40" s="71"/>
+      <c r="EF40" s="71"/>
+      <c r="EG40" s="71"/>
+      <c r="EH40" s="71"/>
+      <c r="EI40" s="71"/>
+      <c r="EJ40" s="71"/>
+      <c r="EK40" s="71"/>
+      <c r="EL40" s="71"/>
+      <c r="EM40" s="71"/>
+      <c r="EN40" s="71"/>
+      <c r="EO40" s="71"/>
+      <c r="EP40" s="71"/>
+      <c r="EQ40" s="71"/>
+      <c r="ER40" s="71"/>
+      <c r="ES40" s="71"/>
+      <c r="ET40" s="71"/>
+      <c r="EU40" s="71"/>
+      <c r="EV40" s="71"/>
+      <c r="EW40" s="71"/>
+      <c r="EX40" s="71"/>
+      <c r="EY40" s="71"/>
+      <c r="EZ40" s="71"/>
+      <c r="FA40" s="71"/>
+      <c r="FB40" s="71"/>
+      <c r="FC40" s="71"/>
+      <c r="FD40" s="71"/>
+      <c r="FE40" s="71"/>
+      <c r="FF40" s="71"/>
+      <c r="FG40" s="71"/>
+      <c r="FH40" s="71"/>
+      <c r="FI40" s="71"/>
+      <c r="FJ40" s="71"/>
+      <c r="FK40" s="71"/>
+      <c r="FL40" s="71"/>
+      <c r="FM40" s="71"/>
+      <c r="FN40" s="71"/>
+      <c r="FO40" s="71"/>
+      <c r="FP40" s="71"/>
+      <c r="FQ40" s="71"/>
+      <c r="FR40" s="71"/>
+      <c r="FS40" s="71"/>
+      <c r="FT40" s="71"/>
+      <c r="FU40" s="71"/>
+      <c r="FV40" s="71"/>
+      <c r="FW40" s="71"/>
+      <c r="FX40" s="71"/>
+      <c r="FY40" s="71"/>
+      <c r="FZ40" s="71"/>
+      <c r="GA40" s="71"/>
+      <c r="GB40" s="71"/>
+      <c r="GC40" s="71"/>
+      <c r="GD40" s="71"/>
+      <c r="GE40" s="71"/>
+      <c r="GF40" s="71"/>
+      <c r="GG40" s="71"/>
+      <c r="GH40" s="71"/>
+      <c r="GI40" s="71"/>
+      <c r="GJ40" s="71"/>
+      <c r="GK40" s="71"/>
+      <c r="GL40" s="71"/>
+      <c r="GM40" s="71"/>
+      <c r="GN40" s="71"/>
+      <c r="GO40" s="71"/>
+      <c r="GP40" s="71"/>
+      <c r="GQ40" s="71"/>
+      <c r="GR40" s="71"/>
+      <c r="GS40" s="71"/>
+      <c r="GT40" s="71"/>
+      <c r="GU40" s="71"/>
+      <c r="GV40" s="71"/>
+      <c r="GW40" s="71"/>
+      <c r="GX40" s="71"/>
+      <c r="GY40" s="71"/>
+      <c r="GZ40" s="71"/>
+      <c r="HA40" s="71"/>
+      <c r="HB40" s="71"/>
+      <c r="HC40" s="71"/>
+      <c r="HD40" s="71"/>
+      <c r="HE40" s="71"/>
+      <c r="HF40" s="71"/>
+      <c r="HG40" s="71"/>
+      <c r="HH40" s="71"/>
+      <c r="HI40" s="71"/>
+      <c r="HJ40" s="71"/>
+      <c r="HK40" s="71"/>
+      <c r="HL40" s="71"/>
+      <c r="HM40" s="71"/>
+      <c r="HN40" s="71"/>
+      <c r="HO40" s="71"/>
+      <c r="HP40" s="71"/>
+      <c r="HQ40" s="71"/>
+      <c r="HR40" s="71"/>
+      <c r="HS40" s="71"/>
+      <c r="HT40" s="71"/>
+      <c r="HU40" s="71"/>
+      <c r="HV40" s="71"/>
+      <c r="HW40" s="71"/>
+      <c r="HX40" s="71"/>
+      <c r="HY40" s="71"/>
+      <c r="HZ40" s="71"/>
+      <c r="IA40" s="71"/>
+      <c r="IB40" s="71"/>
+      <c r="IC40" s="71"/>
+      <c r="ID40" s="71"/>
+      <c r="IE40" s="71"/>
+      <c r="IF40" s="71"/>
+      <c r="IG40" s="71"/>
+      <c r="IH40" s="71"/>
+      <c r="II40" s="71"/>
+      <c r="IJ40" s="71"/>
+      <c r="IK40" s="71"/>
+      <c r="IL40" s="71"/>
+      <c r="IM40" s="71"/>
+      <c r="IN40" s="71"/>
+      <c r="IO40" s="71"/>
+      <c r="IP40" s="71"/>
+      <c r="IQ40" s="71"/>
+      <c r="IR40" s="71"/>
+      <c r="IS40" s="71"/>
+      <c r="IT40" s="71"/>
+      <c r="IU40" s="71"/>
+      <c r="IV40" s="71"/>
+      <c r="IW40" s="71"/>
+      <c r="IX40" s="71"/>
+      <c r="IY40" s="71"/>
+      <c r="IZ40" s="71"/>
+      <c r="JA40" s="71"/>
+      <c r="JB40" s="71"/>
+      <c r="JC40" s="71"/>
+      <c r="JD40" s="71"/>
+      <c r="JE40" s="71"/>
+      <c r="JF40" s="71"/>
+      <c r="JG40" s="71"/>
+      <c r="JH40" s="71"/>
+      <c r="JI40" s="71"/>
+      <c r="JJ40" s="71"/>
+      <c r="JK40" s="71"/>
+      <c r="JL40" s="71"/>
+      <c r="JM40" s="71"/>
+      <c r="JN40" s="71"/>
+      <c r="JO40" s="71"/>
+      <c r="JP40" s="71"/>
+      <c r="JQ40" s="71"/>
+      <c r="JR40" s="71"/>
+      <c r="JS40" s="71"/>
+      <c r="JT40" s="71"/>
+      <c r="JU40" s="71"/>
+      <c r="JV40" s="71"/>
+      <c r="JW40" s="71"/>
+      <c r="JX40" s="71"/>
+      <c r="JY40" s="71"/>
+      <c r="JZ40" s="71"/>
+      <c r="KA40" s="71"/>
+      <c r="KB40" s="71"/>
+      <c r="KC40" s="71"/>
+      <c r="KD40" s="71"/>
+      <c r="KE40" s="71"/>
+      <c r="KF40" s="71"/>
+      <c r="KG40" s="71"/>
+      <c r="KH40" s="71"/>
+      <c r="KI40" s="71"/>
+      <c r="KJ40" s="71"/>
+      <c r="KK40" s="71"/>
+      <c r="KL40" s="71"/>
+      <c r="KM40" s="71"/>
+      <c r="KN40" s="71"/>
+      <c r="KO40" s="71"/>
+      <c r="KP40" s="71"/>
+      <c r="KQ40" s="71"/>
+      <c r="KR40" s="71"/>
+      <c r="KS40" s="71"/>
+      <c r="KT40" s="71"/>
+      <c r="KU40" s="71"/>
+      <c r="KV40" s="71"/>
+      <c r="KW40" s="71"/>
+      <c r="KX40" s="71"/>
+      <c r="KY40" s="71"/>
+      <c r="KZ40" s="71"/>
+      <c r="LA40" s="71"/>
+      <c r="LB40" s="71"/>
+      <c r="LC40" s="71"/>
+      <c r="LD40" s="71"/>
+      <c r="LE40" s="71"/>
+      <c r="LF40" s="71"/>
+      <c r="LG40" s="71"/>
+      <c r="LH40" s="71"/>
+      <c r="LI40" s="71"/>
+      <c r="LJ40" s="71"/>
+      <c r="LK40" s="71"/>
+      <c r="LL40" s="71"/>
+      <c r="LM40" s="71"/>
+      <c r="LN40" s="71"/>
+      <c r="LO40" s="71"/>
+      <c r="LP40" s="71"/>
+      <c r="LQ40" s="71"/>
+      <c r="LR40" s="71"/>
+      <c r="LS40" s="71"/>
+      <c r="LT40" s="71"/>
+      <c r="LU40" s="71"/>
+      <c r="LV40" s="71"/>
+      <c r="LW40" s="71"/>
+      <c r="LX40" s="71"/>
+      <c r="LY40" s="71"/>
+      <c r="LZ40" s="71"/>
+      <c r="MA40" s="71"/>
+      <c r="MB40" s="71"/>
+      <c r="MC40" s="71"/>
+      <c r="MD40" s="71"/>
+      <c r="ME40" s="71"/>
+      <c r="MF40" s="71"/>
+      <c r="MG40" s="71"/>
+      <c r="MH40" s="71"/>
+      <c r="MI40" s="71"/>
+      <c r="MJ40" s="71"/>
+      <c r="MK40" s="71"/>
+      <c r="ML40" s="71"/>
+      <c r="MM40" s="71"/>
+      <c r="MN40" s="71"/>
+      <c r="MO40" s="71"/>
+      <c r="MP40" s="71"/>
+      <c r="MQ40" s="71"/>
+      <c r="MR40" s="71"/>
+      <c r="MS40" s="71"/>
+      <c r="MT40" s="71"/>
+      <c r="MU40" s="71"/>
+      <c r="MV40" s="71"/>
+      <c r="MW40" s="71"/>
+      <c r="MX40" s="71"/>
+      <c r="MY40" s="71"/>
+      <c r="MZ40" s="71"/>
+      <c r="NA40" s="71"/>
     </row>
-    <row r="41" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="A41" s="41"/>
-      <c r="B41" s="69" t="s">
-        <v>56</v>
-      </c>
-      <c r="C41" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="D41" s="67">
-        <v>0</v>
-      </c>
-      <c r="E41" s="68">
-        <f>F40-2</f>
-        <v>46233</v>
-      </c>
-      <c r="F41" s="68">
-        <f>E41+4</f>
-        <v>46237</v>
-      </c>
+    <row r="41" spans="1:365" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="53"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="17">
-        <v>4</v>
-      </c>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="28"/>
-      <c r="Q41" s="28"/>
-      <c r="R41" s="28"/>
-      <c r="S41" s="28"/>
-      <c r="T41" s="28"/>
-      <c r="U41" s="28"/>
-      <c r="V41" s="28"/>
-      <c r="W41" s="28"/>
-      <c r="X41" s="28"/>
-      <c r="Y41" s="28"/>
-      <c r="Z41" s="28"/>
-      <c r="AA41" s="28"/>
-      <c r="AB41" s="28"/>
-      <c r="AC41" s="28"/>
-      <c r="AD41" s="28"/>
-      <c r="AE41" s="28"/>
-      <c r="AF41" s="28"/>
-      <c r="AG41" s="28"/>
-      <c r="AH41" s="28"/>
-      <c r="AI41" s="28"/>
-      <c r="AJ41" s="28"/>
-      <c r="AK41" s="28"/>
-      <c r="AL41" s="28"/>
-      <c r="AM41" s="28"/>
-      <c r="AN41" s="28"/>
-      <c r="AO41" s="28"/>
-      <c r="AP41" s="28"/>
-      <c r="AQ41" s="28"/>
-      <c r="AR41" s="28"/>
-      <c r="AS41" s="28"/>
-      <c r="AT41" s="28"/>
-      <c r="AU41" s="28"/>
-      <c r="AV41" s="28"/>
-      <c r="AW41" s="28"/>
-      <c r="AX41" s="28"/>
-      <c r="AY41" s="28"/>
-      <c r="AZ41" s="28"/>
-      <c r="BA41" s="28"/>
-      <c r="BB41" s="28"/>
-      <c r="BC41" s="28"/>
-      <c r="BD41" s="28"/>
-      <c r="BE41" s="28"/>
-      <c r="BF41" s="28"/>
-      <c r="BG41" s="28"/>
-      <c r="BH41" s="28"/>
-      <c r="BI41" s="28"/>
-      <c r="BJ41" s="28"/>
-      <c r="BK41" s="28"/>
-      <c r="BL41" s="28"/>
-      <c r="BM41" s="28"/>
-      <c r="BN41" s="28"/>
-      <c r="BO41" s="28"/>
-      <c r="BP41" s="28"/>
-      <c r="BQ41" s="28"/>
-      <c r="BR41" s="28"/>
-      <c r="BS41" s="28"/>
-      <c r="BT41" s="28"/>
-      <c r="BU41" s="28"/>
-      <c r="BV41" s="28"/>
-      <c r="BW41" s="28"/>
-      <c r="BX41" s="28"/>
-      <c r="BY41" s="28"/>
-      <c r="BZ41" s="28"/>
-      <c r="CA41" s="28"/>
-      <c r="CB41" s="28"/>
-      <c r="CC41" s="28"/>
-      <c r="CD41" s="28"/>
-      <c r="CE41" s="28"/>
-      <c r="CF41" s="28"/>
-      <c r="CG41" s="28"/>
-      <c r="CH41" s="28"/>
-      <c r="CI41" s="28"/>
-      <c r="CJ41" s="28"/>
-      <c r="CK41" s="28"/>
-      <c r="CL41" s="28"/>
-      <c r="CM41" s="28"/>
-      <c r="CN41" s="28"/>
-      <c r="CO41" s="28"/>
-      <c r="CP41" s="28"/>
-      <c r="CQ41" s="28"/>
-      <c r="CR41" s="28"/>
-      <c r="CS41" s="28"/>
-      <c r="CT41" s="28"/>
-      <c r="CU41" s="28"/>
-      <c r="CV41" s="28"/>
-      <c r="CW41" s="28"/>
-      <c r="CX41" s="28"/>
-      <c r="CY41" s="28"/>
-      <c r="CZ41" s="28"/>
-      <c r="DA41" s="28"/>
-      <c r="DB41" s="28"/>
-      <c r="DC41" s="28"/>
-      <c r="DD41" s="28"/>
-      <c r="DE41" s="28"/>
-      <c r="DF41" s="28"/>
-      <c r="DG41" s="28"/>
-      <c r="DH41" s="28"/>
-      <c r="DI41" s="28"/>
-      <c r="DJ41" s="28"/>
-      <c r="DK41" s="28"/>
-      <c r="DL41" s="28"/>
-      <c r="DM41" s="28"/>
-      <c r="DN41" s="28"/>
-      <c r="DO41" s="28"/>
-      <c r="DP41" s="28"/>
-      <c r="DQ41" s="28"/>
-      <c r="DR41" s="28"/>
-      <c r="DS41" s="28"/>
-      <c r="DT41" s="28"/>
-      <c r="DU41" s="28"/>
-      <c r="DV41" s="28"/>
-      <c r="DW41" s="28"/>
-      <c r="DX41" s="28"/>
-      <c r="DY41" s="28"/>
-      <c r="DZ41" s="28"/>
-      <c r="EA41" s="28"/>
-      <c r="EB41" s="28"/>
-      <c r="EC41" s="28"/>
-      <c r="ED41" s="28"/>
-      <c r="EE41" s="28"/>
-      <c r="EF41" s="28"/>
-      <c r="EG41" s="28"/>
-      <c r="EH41" s="28"/>
-      <c r="EI41" s="28"/>
-      <c r="EJ41" s="28"/>
-      <c r="EK41" s="28"/>
-      <c r="EL41" s="28"/>
-      <c r="EM41" s="28"/>
-      <c r="EN41" s="28"/>
-      <c r="EO41" s="28"/>
-      <c r="EP41" s="28"/>
-      <c r="EQ41" s="28"/>
-      <c r="ER41" s="28"/>
-      <c r="ES41" s="28"/>
-      <c r="ET41" s="28"/>
-      <c r="EU41" s="28"/>
-      <c r="EV41" s="28"/>
-      <c r="EW41" s="28"/>
-      <c r="EX41" s="28"/>
-      <c r="EY41" s="28"/>
-      <c r="EZ41" s="28"/>
-      <c r="FA41" s="28"/>
-      <c r="FB41" s="28"/>
-      <c r="FC41" s="28"/>
-      <c r="FD41" s="28"/>
-      <c r="FE41" s="28"/>
-      <c r="FF41" s="28"/>
-      <c r="FG41" s="28"/>
-      <c r="FH41" s="28"/>
-      <c r="FI41" s="28"/>
-      <c r="FJ41" s="28"/>
-      <c r="FK41" s="28"/>
-      <c r="FL41" s="28"/>
-      <c r="FM41" s="28"/>
-      <c r="FN41" s="28"/>
-      <c r="FO41" s="28"/>
-      <c r="FP41" s="28"/>
-      <c r="FQ41" s="28"/>
-      <c r="FR41" s="28"/>
-      <c r="FS41" s="28"/>
-      <c r="FT41" s="28"/>
-      <c r="FU41" s="28"/>
-      <c r="FV41" s="28"/>
-      <c r="FW41" s="28"/>
-      <c r="FX41" s="28"/>
-      <c r="FY41" s="28"/>
-      <c r="FZ41" s="28"/>
-      <c r="GA41" s="28"/>
-      <c r="GB41" s="28"/>
-      <c r="GC41" s="28"/>
-      <c r="GD41" s="28"/>
-      <c r="GE41" s="28"/>
-      <c r="GF41" s="28"/>
-      <c r="GG41" s="28"/>
-      <c r="GH41" s="28"/>
-      <c r="GI41" s="28"/>
-      <c r="GJ41" s="28"/>
-      <c r="GK41" s="28"/>
-      <c r="GL41" s="28"/>
-      <c r="GM41" s="28"/>
-      <c r="GN41" s="28"/>
-      <c r="GO41" s="28"/>
-      <c r="GP41" s="28"/>
-      <c r="GQ41" s="28"/>
-      <c r="GR41" s="28"/>
-      <c r="GS41" s="28"/>
-      <c r="GT41" s="28"/>
-      <c r="GU41" s="28"/>
-      <c r="GV41" s="28"/>
-      <c r="GW41" s="28"/>
-      <c r="GX41" s="28"/>
-      <c r="GY41" s="28"/>
-      <c r="GZ41" s="28"/>
-      <c r="HA41" s="28"/>
-      <c r="HB41" s="28"/>
-      <c r="HC41" s="28"/>
-      <c r="HD41" s="28"/>
-      <c r="HE41" s="28"/>
-      <c r="HF41" s="28"/>
-      <c r="HG41" s="28"/>
-      <c r="HH41" s="28"/>
-      <c r="HI41" s="28"/>
-      <c r="HJ41" s="28"/>
-      <c r="HK41" s="28"/>
-      <c r="HL41" s="28"/>
-      <c r="HM41" s="28"/>
-      <c r="HN41" s="28"/>
-      <c r="HO41" s="28"/>
-      <c r="HP41" s="28"/>
-      <c r="HQ41" s="28"/>
-      <c r="HR41" s="28"/>
-      <c r="HS41" s="28"/>
-      <c r="HT41" s="28"/>
-      <c r="HU41" s="28"/>
-      <c r="HV41" s="28"/>
-      <c r="HW41" s="28"/>
-      <c r="HX41" s="28"/>
-      <c r="HY41" s="28"/>
-      <c r="HZ41" s="28"/>
-      <c r="IA41" s="28"/>
-      <c r="IB41" s="28"/>
-      <c r="IC41" s="28"/>
-      <c r="ID41" s="28"/>
-      <c r="IE41" s="28"/>
-      <c r="IF41" s="28"/>
-      <c r="IG41" s="28"/>
-      <c r="IH41" s="28"/>
-      <c r="II41" s="28"/>
-      <c r="IJ41" s="28"/>
-      <c r="IK41" s="28"/>
-      <c r="IL41" s="28"/>
-      <c r="IM41" s="28"/>
-      <c r="IN41" s="28"/>
-      <c r="IO41" s="28"/>
-      <c r="IP41" s="28"/>
-      <c r="IQ41" s="28"/>
-      <c r="IR41" s="28"/>
-      <c r="IS41" s="28"/>
-      <c r="IT41" s="28"/>
-      <c r="IU41" s="28"/>
-      <c r="IV41" s="28"/>
-      <c r="IW41" s="28"/>
-      <c r="IX41" s="28"/>
-      <c r="IY41" s="28"/>
-      <c r="IZ41" s="28"/>
-      <c r="JA41" s="28"/>
-      <c r="JB41" s="28"/>
-      <c r="JC41" s="28"/>
-      <c r="JD41" s="28"/>
-      <c r="JE41" s="28"/>
-      <c r="JF41" s="28"/>
-      <c r="JG41" s="28"/>
-      <c r="JH41" s="28"/>
-      <c r="JI41" s="28"/>
-      <c r="JJ41" s="28"/>
-      <c r="JK41" s="28"/>
-      <c r="JL41" s="28"/>
-      <c r="JM41" s="28"/>
-      <c r="JN41" s="28"/>
-      <c r="JO41" s="28"/>
-      <c r="JP41" s="28"/>
-      <c r="JQ41" s="28"/>
-      <c r="JR41" s="28"/>
-      <c r="JS41" s="28"/>
-      <c r="JT41" s="28"/>
-      <c r="JU41" s="28"/>
-      <c r="JV41" s="28"/>
-      <c r="JW41" s="28"/>
-      <c r="JX41" s="28"/>
-      <c r="JY41" s="28"/>
-      <c r="JZ41" s="28"/>
-      <c r="KA41" s="28"/>
-      <c r="KB41" s="28"/>
-      <c r="KC41" s="28"/>
-      <c r="KD41" s="28"/>
-      <c r="KE41" s="28"/>
-      <c r="KF41" s="28"/>
-      <c r="KG41" s="28"/>
-      <c r="KH41" s="28"/>
-      <c r="KI41" s="28"/>
-      <c r="KJ41" s="28"/>
-      <c r="KK41" s="28"/>
-      <c r="KL41" s="28"/>
-      <c r="KM41" s="28"/>
-      <c r="KN41" s="28"/>
-      <c r="KO41" s="28"/>
-      <c r="KP41" s="28"/>
-      <c r="KQ41" s="28"/>
-      <c r="KR41" s="28"/>
-      <c r="KS41" s="28"/>
-      <c r="KT41" s="28"/>
-      <c r="KU41" s="28"/>
-      <c r="KV41" s="28"/>
-      <c r="KW41" s="28"/>
-      <c r="KX41" s="28"/>
-      <c r="KY41" s="28"/>
-      <c r="KZ41" s="28"/>
-      <c r="LA41" s="28"/>
-      <c r="LB41" s="28"/>
-      <c r="LC41" s="28"/>
-      <c r="LD41" s="28"/>
-      <c r="LE41" s="28"/>
-      <c r="LF41" s="28"/>
-      <c r="LG41" s="28"/>
-      <c r="LH41" s="28"/>
-      <c r="LI41" s="28"/>
-      <c r="LJ41" s="28"/>
-      <c r="LK41" s="28"/>
-      <c r="LL41" s="28"/>
-      <c r="LM41" s="28"/>
-      <c r="LN41" s="28"/>
-      <c r="LO41" s="28"/>
-      <c r="LP41" s="28"/>
-      <c r="LQ41" s="28"/>
-      <c r="LR41" s="28"/>
-      <c r="LS41" s="28"/>
-      <c r="LT41" s="28"/>
-      <c r="LU41" s="28"/>
-      <c r="LV41" s="28"/>
-      <c r="LW41" s="28"/>
-      <c r="LX41" s="28"/>
-      <c r="LY41" s="28"/>
-      <c r="LZ41" s="28"/>
-      <c r="MA41" s="28"/>
-      <c r="MB41" s="28"/>
-      <c r="MC41" s="28"/>
-      <c r="MD41" s="28"/>
-      <c r="ME41" s="28"/>
-      <c r="MF41" s="28"/>
-      <c r="MG41" s="28"/>
-      <c r="MH41" s="28"/>
-      <c r="MI41" s="28"/>
-      <c r="MJ41" s="28"/>
-      <c r="MK41" s="28"/>
-      <c r="ML41" s="28"/>
-      <c r="MM41" s="28"/>
-      <c r="MN41" s="28"/>
-      <c r="MO41" s="28"/>
-      <c r="MP41" s="28"/>
-      <c r="MQ41" s="28"/>
-      <c r="MR41" s="28"/>
-      <c r="MS41" s="28"/>
-      <c r="MT41" s="28"/>
-      <c r="MU41" s="28"/>
-      <c r="MV41" s="28"/>
-      <c r="MW41" s="28"/>
-      <c r="MX41" s="28"/>
-      <c r="MY41" s="28"/>
-      <c r="MZ41" s="28"/>
-      <c r="NA41" s="28"/>
+      <c r="H41" s="17" t="str">
+        <f t="shared" si="346"/>
+        <v/>
+      </c>
     </row>
-    <row r="42" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="A42" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" s="69" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="D42" s="67">
-        <v>0</v>
-      </c>
-      <c r="E42" s="68">
-        <v>46235</v>
-      </c>
-      <c r="F42" s="68">
-        <v>46242</v>
-      </c>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17">
-        <v>7</v>
-      </c>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28"/>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="28"/>
-      <c r="R42" s="28"/>
-      <c r="S42" s="28"/>
-      <c r="T42" s="28"/>
-      <c r="U42" s="28"/>
-      <c r="V42" s="28"/>
-      <c r="W42" s="28"/>
-      <c r="X42" s="28"/>
-      <c r="Y42" s="28"/>
-      <c r="Z42" s="28"/>
-      <c r="AA42" s="28"/>
-      <c r="AB42" s="28"/>
-      <c r="AC42" s="28"/>
-      <c r="AD42" s="28"/>
-      <c r="AE42" s="28"/>
-      <c r="AF42" s="28"/>
-      <c r="AG42" s="28"/>
-      <c r="AH42" s="28"/>
-      <c r="AI42" s="28"/>
-      <c r="AJ42" s="28"/>
-      <c r="AK42" s="28"/>
-      <c r="AL42" s="28"/>
-      <c r="AM42" s="28"/>
-      <c r="AN42" s="28"/>
-      <c r="AO42" s="28"/>
-      <c r="AP42" s="28"/>
-      <c r="AQ42" s="28"/>
-      <c r="AR42" s="28"/>
-      <c r="AS42" s="28"/>
-      <c r="AT42" s="28"/>
-      <c r="AU42" s="28"/>
-      <c r="AV42" s="28"/>
-      <c r="AW42" s="28"/>
-      <c r="AX42" s="28"/>
-      <c r="AY42" s="28"/>
-      <c r="AZ42" s="28"/>
-      <c r="BA42" s="28"/>
-      <c r="BB42" s="28"/>
-      <c r="BC42" s="28"/>
-      <c r="BD42" s="28"/>
-      <c r="BE42" s="28"/>
-      <c r="BF42" s="28"/>
-      <c r="BG42" s="28"/>
-      <c r="BH42" s="28"/>
-      <c r="BI42" s="28"/>
-      <c r="BJ42" s="28"/>
-      <c r="BK42" s="28"/>
-      <c r="BL42" s="28"/>
-      <c r="BM42" s="28"/>
-      <c r="BN42" s="28"/>
-      <c r="BO42" s="28"/>
-      <c r="BP42" s="28"/>
-      <c r="BQ42" s="28"/>
-      <c r="BR42" s="28"/>
-      <c r="BS42" s="28"/>
-      <c r="BT42" s="28"/>
-      <c r="BU42" s="28"/>
-      <c r="BV42" s="28"/>
-      <c r="BW42" s="28"/>
-      <c r="BX42" s="28"/>
-      <c r="BY42" s="28"/>
-      <c r="BZ42" s="28"/>
-      <c r="CA42" s="28"/>
-      <c r="CB42" s="28"/>
-      <c r="CC42" s="28"/>
-      <c r="CD42" s="28"/>
-      <c r="CE42" s="28"/>
-      <c r="CF42" s="28"/>
-      <c r="CG42" s="28"/>
-      <c r="CH42" s="28"/>
-      <c r="CI42" s="28"/>
-      <c r="CJ42" s="28"/>
-      <c r="CK42" s="28"/>
-      <c r="CL42" s="28"/>
-      <c r="CM42" s="28"/>
-      <c r="CN42" s="28"/>
-      <c r="CO42" s="28"/>
-      <c r="CP42" s="28"/>
-      <c r="CQ42" s="28"/>
-      <c r="CR42" s="28"/>
-      <c r="CS42" s="28"/>
-      <c r="CT42" s="28"/>
-      <c r="CU42" s="28"/>
-      <c r="CV42" s="28"/>
-      <c r="CW42" s="28"/>
-      <c r="CX42" s="28"/>
-      <c r="CY42" s="28"/>
-      <c r="CZ42" s="28"/>
-      <c r="DA42" s="28"/>
-      <c r="DB42" s="28"/>
-      <c r="DC42" s="28"/>
-      <c r="DD42" s="28"/>
-      <c r="DE42" s="28"/>
-      <c r="DF42" s="28"/>
-      <c r="DG42" s="28"/>
-      <c r="DH42" s="28"/>
-      <c r="DI42" s="28"/>
-      <c r="DJ42" s="28"/>
-      <c r="DK42" s="28"/>
-      <c r="DL42" s="28"/>
-      <c r="DM42" s="28"/>
-      <c r="DN42" s="28"/>
-      <c r="DO42" s="28"/>
-      <c r="DP42" s="28"/>
-      <c r="DQ42" s="28"/>
-      <c r="DR42" s="28"/>
-      <c r="DS42" s="28"/>
-      <c r="DT42" s="28"/>
-      <c r="DU42" s="28"/>
-      <c r="DV42" s="28"/>
-      <c r="DW42" s="28"/>
-      <c r="DX42" s="28"/>
-      <c r="DY42" s="28"/>
-      <c r="DZ42" s="28"/>
-      <c r="EA42" s="28"/>
-      <c r="EB42" s="28"/>
-      <c r="EC42" s="28"/>
-      <c r="ED42" s="28"/>
-      <c r="EE42" s="28"/>
-      <c r="EF42" s="28"/>
-      <c r="EG42" s="28"/>
-      <c r="EH42" s="28"/>
-      <c r="EI42" s="28"/>
-      <c r="EJ42" s="28"/>
-      <c r="EK42" s="28"/>
-      <c r="EL42" s="28"/>
-      <c r="EM42" s="28"/>
-      <c r="EN42" s="28"/>
-      <c r="EO42" s="28"/>
-      <c r="EP42" s="28"/>
-      <c r="EQ42" s="28"/>
-      <c r="ER42" s="28"/>
-      <c r="ES42" s="28"/>
-      <c r="ET42" s="28"/>
-      <c r="EU42" s="28"/>
-      <c r="EV42" s="28"/>
-      <c r="EW42" s="28"/>
-      <c r="EX42" s="28"/>
-      <c r="EY42" s="28"/>
-      <c r="EZ42" s="28"/>
-      <c r="FA42" s="28"/>
-      <c r="FB42" s="28"/>
-      <c r="FC42" s="28"/>
-      <c r="FD42" s="28"/>
-      <c r="FE42" s="28"/>
-      <c r="FF42" s="28"/>
-      <c r="FG42" s="28"/>
-      <c r="FH42" s="28"/>
-      <c r="FI42" s="28"/>
-      <c r="FJ42" s="28"/>
-      <c r="FK42" s="28"/>
-      <c r="FL42" s="28"/>
-      <c r="FM42" s="28"/>
-      <c r="FN42" s="28"/>
-      <c r="FO42" s="28"/>
-      <c r="FP42" s="28"/>
-      <c r="FQ42" s="28"/>
-      <c r="FR42" s="28"/>
-      <c r="FS42" s="28"/>
-      <c r="FT42" s="28"/>
-      <c r="FU42" s="28"/>
-      <c r="FV42" s="28"/>
-      <c r="FW42" s="28"/>
-      <c r="FX42" s="28"/>
-      <c r="FY42" s="28"/>
-      <c r="FZ42" s="28"/>
-      <c r="GA42" s="28"/>
-      <c r="GB42" s="28"/>
-      <c r="GC42" s="28"/>
-      <c r="GD42" s="28"/>
-      <c r="GE42" s="28"/>
-      <c r="GF42" s="28"/>
-      <c r="GG42" s="28"/>
-      <c r="GH42" s="28"/>
-      <c r="GI42" s="28"/>
-      <c r="GJ42" s="28"/>
-      <c r="GK42" s="28"/>
-      <c r="GL42" s="28"/>
-      <c r="GM42" s="28"/>
-      <c r="GN42" s="28"/>
-      <c r="GO42" s="28"/>
-      <c r="GP42" s="28"/>
-      <c r="GQ42" s="28"/>
-      <c r="GR42" s="28"/>
-      <c r="GS42" s="28"/>
-      <c r="GT42" s="28"/>
-      <c r="GU42" s="28"/>
-      <c r="GV42" s="28"/>
-      <c r="GW42" s="28"/>
-      <c r="GX42" s="28"/>
-      <c r="GY42" s="28"/>
-      <c r="GZ42" s="28"/>
-      <c r="HA42" s="28"/>
-      <c r="HB42" s="28"/>
-      <c r="HC42" s="28"/>
-      <c r="HD42" s="28"/>
-      <c r="HE42" s="28"/>
-      <c r="HF42" s="28"/>
-      <c r="HG42" s="28"/>
-      <c r="HH42" s="28"/>
-      <c r="HI42" s="28"/>
-      <c r="HJ42" s="28"/>
-      <c r="HK42" s="28"/>
-      <c r="HL42" s="28"/>
-      <c r="HM42" s="28"/>
-      <c r="HN42" s="28"/>
-      <c r="HO42" s="28"/>
-      <c r="HP42" s="28"/>
-      <c r="HQ42" s="28"/>
-      <c r="HR42" s="28"/>
-      <c r="HS42" s="28"/>
-      <c r="HT42" s="28"/>
-      <c r="HU42" s="28"/>
-      <c r="HV42" s="28"/>
-      <c r="HW42" s="28"/>
-      <c r="HX42" s="28"/>
-      <c r="HY42" s="28"/>
-      <c r="HZ42" s="28"/>
-      <c r="IA42" s="28"/>
-      <c r="IB42" s="28"/>
-      <c r="IC42" s="28"/>
-      <c r="ID42" s="28"/>
-      <c r="IE42" s="28"/>
-      <c r="IF42" s="28"/>
-      <c r="IG42" s="28"/>
-      <c r="IH42" s="28"/>
-      <c r="II42" s="28"/>
-      <c r="IJ42" s="28"/>
-      <c r="IK42" s="28"/>
-      <c r="IL42" s="28"/>
-      <c r="IM42" s="28"/>
-      <c r="IN42" s="28"/>
-      <c r="IO42" s="28"/>
-      <c r="IP42" s="28"/>
-      <c r="IQ42" s="28"/>
-      <c r="IR42" s="28"/>
-      <c r="IS42" s="28"/>
-      <c r="IT42" s="28"/>
-      <c r="IU42" s="28"/>
-      <c r="IV42" s="28"/>
-      <c r="IW42" s="28"/>
-      <c r="IX42" s="28"/>
-      <c r="IY42" s="28"/>
-      <c r="IZ42" s="28"/>
-      <c r="JA42" s="28"/>
-      <c r="JB42" s="28"/>
-      <c r="JC42" s="28"/>
-      <c r="JD42" s="28"/>
-      <c r="JE42" s="28"/>
-      <c r="JF42" s="28"/>
-      <c r="JG42" s="28"/>
-      <c r="JH42" s="28"/>
-      <c r="JI42" s="28"/>
-      <c r="JJ42" s="28"/>
-      <c r="JK42" s="28"/>
-      <c r="JL42" s="28"/>
-      <c r="JM42" s="28"/>
-      <c r="JN42" s="28"/>
-      <c r="JO42" s="28"/>
-      <c r="JP42" s="28"/>
-      <c r="JQ42" s="28"/>
-      <c r="JR42" s="28"/>
-      <c r="JS42" s="28"/>
-      <c r="JT42" s="28"/>
-      <c r="JU42" s="28"/>
-      <c r="JV42" s="28"/>
-      <c r="JW42" s="28"/>
-      <c r="JX42" s="28"/>
-      <c r="JY42" s="28"/>
-      <c r="JZ42" s="28"/>
-      <c r="KA42" s="28"/>
-      <c r="KB42" s="28"/>
-      <c r="KC42" s="28"/>
-      <c r="KD42" s="28"/>
-      <c r="KE42" s="28"/>
-      <c r="KF42" s="28"/>
-      <c r="KG42" s="28"/>
-      <c r="KH42" s="28"/>
-      <c r="KI42" s="28"/>
-      <c r="KJ42" s="28"/>
-      <c r="KK42" s="28"/>
-      <c r="KL42" s="28"/>
-      <c r="KM42" s="28"/>
-      <c r="KN42" s="28"/>
-      <c r="KO42" s="28"/>
-      <c r="KP42" s="28"/>
-      <c r="KQ42" s="28"/>
-      <c r="KR42" s="28"/>
-      <c r="KS42" s="28"/>
-      <c r="KT42" s="28"/>
-      <c r="KU42" s="28"/>
-      <c r="KV42" s="28"/>
-      <c r="KW42" s="28"/>
-      <c r="KX42" s="28"/>
-      <c r="KY42" s="28"/>
-      <c r="KZ42" s="28"/>
-      <c r="LA42" s="28"/>
-      <c r="LB42" s="28"/>
-      <c r="LC42" s="28"/>
-      <c r="LD42" s="28"/>
-      <c r="LE42" s="28"/>
-      <c r="LF42" s="28"/>
-      <c r="LG42" s="28"/>
-      <c r="LH42" s="28"/>
-      <c r="LI42" s="28"/>
-      <c r="LJ42" s="28"/>
-      <c r="LK42" s="28"/>
-      <c r="LL42" s="28"/>
-      <c r="LM42" s="28"/>
-      <c r="LN42" s="28"/>
-      <c r="LO42" s="28"/>
-      <c r="LP42" s="28"/>
-      <c r="LQ42" s="28"/>
-      <c r="LR42" s="28"/>
-      <c r="LS42" s="28"/>
-      <c r="LT42" s="28"/>
-      <c r="LU42" s="28"/>
-      <c r="LV42" s="28"/>
-      <c r="LW42" s="28"/>
-      <c r="LX42" s="28"/>
-      <c r="LY42" s="28"/>
-      <c r="LZ42" s="28"/>
-      <c r="MA42" s="28"/>
-      <c r="MB42" s="28"/>
-      <c r="MC42" s="28"/>
-      <c r="MD42" s="28"/>
-      <c r="ME42" s="28"/>
-      <c r="MF42" s="28"/>
-      <c r="MG42" s="28"/>
-      <c r="MH42" s="28"/>
-      <c r="MI42" s="28"/>
-      <c r="MJ42" s="28"/>
-      <c r="MK42" s="28"/>
-      <c r="ML42" s="28"/>
-      <c r="MM42" s="28"/>
-      <c r="MN42" s="28"/>
-      <c r="MO42" s="28"/>
-      <c r="MP42" s="28"/>
-      <c r="MQ42" s="28"/>
-      <c r="MR42" s="28"/>
-      <c r="MS42" s="28"/>
-      <c r="MT42" s="28"/>
-      <c r="MU42" s="28"/>
-      <c r="MV42" s="28"/>
-      <c r="MW42" s="28"/>
-      <c r="MX42" s="28"/>
-      <c r="MY42" s="28"/>
-      <c r="MZ42" s="28"/>
-      <c r="NA42" s="28"/>
+    <row r="42" spans="1:365" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="23"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27" t="str">
+        <f t="shared" si="346"/>
+        <v/>
+      </c>
     </row>
-    <row r="43" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="A43" s="42"/>
-      <c r="B43" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43" s="66" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="67">
-        <v>0</v>
-      </c>
-      <c r="E43" s="68">
-        <v>46238</v>
-      </c>
-      <c r="F43" s="68">
-        <v>46243</v>
-      </c>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17">
-        <v>5</v>
-      </c>
-      <c r="I43" s="74"/>
-      <c r="J43" s="74"/>
-      <c r="K43" s="74"/>
-      <c r="L43" s="74"/>
-      <c r="M43" s="74"/>
-      <c r="N43" s="74"/>
-      <c r="O43" s="74"/>
-      <c r="P43" s="74"/>
-      <c r="Q43" s="74"/>
-      <c r="R43" s="74"/>
-      <c r="S43" s="74"/>
-      <c r="T43" s="74"/>
-      <c r="U43" s="74"/>
-      <c r="V43" s="74"/>
-      <c r="W43" s="74"/>
-      <c r="X43" s="74"/>
-      <c r="Y43" s="74"/>
-      <c r="Z43" s="74"/>
-      <c r="AA43" s="74"/>
-      <c r="AB43" s="74"/>
-      <c r="AC43" s="74"/>
-      <c r="AD43" s="74"/>
-      <c r="AE43" s="74"/>
-      <c r="AF43" s="74"/>
-      <c r="AG43" s="74"/>
-      <c r="AH43" s="74"/>
-      <c r="AI43" s="74"/>
-      <c r="AJ43" s="74"/>
-      <c r="AK43" s="74"/>
-      <c r="AL43" s="74"/>
-      <c r="AM43" s="74"/>
-      <c r="AN43" s="74"/>
-      <c r="AO43" s="74"/>
-      <c r="AP43" s="74"/>
-      <c r="AQ43" s="74"/>
-      <c r="AR43" s="74"/>
-      <c r="AS43" s="74"/>
-      <c r="AT43" s="74"/>
-      <c r="AU43" s="74"/>
-      <c r="AV43" s="74"/>
-      <c r="AW43" s="74"/>
-      <c r="AX43" s="74"/>
-      <c r="AY43" s="74"/>
-      <c r="AZ43" s="74"/>
-      <c r="BA43" s="74"/>
-      <c r="BB43" s="74"/>
-      <c r="BC43" s="74"/>
-      <c r="BD43" s="74"/>
-      <c r="BE43" s="74"/>
-      <c r="BF43" s="74"/>
-      <c r="BG43" s="74"/>
-      <c r="BH43" s="74"/>
-      <c r="BI43" s="74"/>
-      <c r="BJ43" s="74"/>
-      <c r="BK43" s="74"/>
-      <c r="BL43" s="74"/>
-      <c r="BM43" s="74"/>
-      <c r="BN43" s="74"/>
-      <c r="BO43" s="74"/>
-      <c r="BP43" s="74"/>
-      <c r="BQ43" s="74"/>
-      <c r="BR43" s="74"/>
-      <c r="BS43" s="74"/>
-      <c r="BT43" s="74"/>
-      <c r="BU43" s="74"/>
-      <c r="BV43" s="74"/>
-      <c r="BW43" s="74"/>
-      <c r="BX43" s="74"/>
-      <c r="BY43" s="74"/>
-      <c r="BZ43" s="74"/>
-      <c r="CA43" s="74"/>
-      <c r="CB43" s="74"/>
-      <c r="CC43" s="74"/>
-      <c r="CD43" s="74"/>
-      <c r="CE43" s="74"/>
-      <c r="CF43" s="74"/>
-      <c r="CG43" s="74"/>
-      <c r="CH43" s="74"/>
-      <c r="CI43" s="74"/>
-      <c r="CJ43" s="74"/>
-      <c r="CK43" s="74"/>
-      <c r="CL43" s="74"/>
-      <c r="CM43" s="74"/>
-      <c r="CN43" s="74"/>
-      <c r="CO43" s="74"/>
-      <c r="CP43" s="74"/>
-      <c r="CQ43" s="74"/>
-      <c r="CR43" s="74"/>
-      <c r="CS43" s="74"/>
-      <c r="CT43" s="74"/>
-      <c r="CU43" s="74"/>
-      <c r="CV43" s="74"/>
-      <c r="CW43" s="74"/>
-      <c r="CX43" s="74"/>
-      <c r="CY43" s="74"/>
-      <c r="CZ43" s="74"/>
-      <c r="DA43" s="74"/>
-      <c r="DB43" s="74"/>
-      <c r="DC43" s="74"/>
-      <c r="DD43" s="74"/>
-      <c r="DE43" s="74"/>
-      <c r="DF43" s="74"/>
-      <c r="DG43" s="74"/>
-      <c r="DH43" s="74"/>
-      <c r="DI43" s="74"/>
-      <c r="DJ43" s="74"/>
-      <c r="DK43" s="74"/>
-      <c r="DL43" s="74"/>
-      <c r="DM43" s="74"/>
-      <c r="DN43" s="74"/>
-      <c r="DO43" s="74"/>
-      <c r="DP43" s="74"/>
-      <c r="DQ43" s="74"/>
-      <c r="DR43" s="74"/>
-      <c r="DS43" s="74"/>
-      <c r="DT43" s="74"/>
-      <c r="DU43" s="74"/>
-      <c r="DV43" s="74"/>
-      <c r="DW43" s="74"/>
-      <c r="DX43" s="74"/>
-      <c r="DY43" s="74"/>
-      <c r="DZ43" s="74"/>
-      <c r="EA43" s="74"/>
-      <c r="EB43" s="74"/>
-      <c r="EC43" s="74"/>
-      <c r="ED43" s="74"/>
-      <c r="EE43" s="74"/>
-      <c r="EF43" s="74"/>
-      <c r="EG43" s="74"/>
-      <c r="EH43" s="74"/>
-      <c r="EI43" s="74"/>
-      <c r="EJ43" s="74"/>
-      <c r="EK43" s="74"/>
-      <c r="EL43" s="74"/>
-      <c r="EM43" s="74"/>
-      <c r="EN43" s="74"/>
-      <c r="EO43" s="74"/>
-      <c r="EP43" s="74"/>
-      <c r="EQ43" s="74"/>
-      <c r="ER43" s="74"/>
-      <c r="ES43" s="74"/>
-      <c r="ET43" s="74"/>
-      <c r="EU43" s="74"/>
-      <c r="EV43" s="74"/>
-      <c r="EW43" s="74"/>
-      <c r="EX43" s="74"/>
-      <c r="EY43" s="74"/>
-      <c r="EZ43" s="74"/>
-      <c r="FA43" s="74"/>
-      <c r="FB43" s="74"/>
-      <c r="FC43" s="74"/>
-      <c r="FD43" s="74"/>
-      <c r="FE43" s="74"/>
-      <c r="FF43" s="74"/>
-      <c r="FG43" s="74"/>
-      <c r="FH43" s="74"/>
-      <c r="FI43" s="74"/>
-      <c r="FJ43" s="74"/>
-      <c r="FK43" s="74"/>
-      <c r="FL43" s="74"/>
-      <c r="FM43" s="74"/>
-      <c r="FN43" s="74"/>
-      <c r="FO43" s="74"/>
-      <c r="FP43" s="74"/>
-      <c r="FQ43" s="74"/>
-      <c r="FR43" s="74"/>
-      <c r="FS43" s="74"/>
-      <c r="FT43" s="74"/>
-      <c r="FU43" s="74"/>
-      <c r="FV43" s="74"/>
-      <c r="FW43" s="74"/>
-      <c r="FX43" s="74"/>
-      <c r="FY43" s="74"/>
-      <c r="FZ43" s="74"/>
-      <c r="GA43" s="74"/>
-      <c r="GB43" s="74"/>
-      <c r="GC43" s="74"/>
-      <c r="GD43" s="74"/>
-      <c r="GE43" s="74"/>
-      <c r="GF43" s="74"/>
-      <c r="GG43" s="74"/>
-      <c r="GH43" s="74"/>
-      <c r="GI43" s="74"/>
-      <c r="GJ43" s="74"/>
-      <c r="GK43" s="74"/>
-      <c r="GL43" s="74"/>
-      <c r="GM43" s="74"/>
-      <c r="GN43" s="74"/>
-      <c r="GO43" s="74"/>
-      <c r="GP43" s="74"/>
-      <c r="GQ43" s="74"/>
-      <c r="GR43" s="74"/>
-      <c r="GS43" s="74"/>
-      <c r="GT43" s="74"/>
-      <c r="GU43" s="74"/>
-      <c r="GV43" s="74"/>
-      <c r="GW43" s="74"/>
-      <c r="GX43" s="74"/>
-      <c r="GY43" s="74"/>
-      <c r="GZ43" s="74"/>
-      <c r="HA43" s="74"/>
-      <c r="HB43" s="74"/>
-      <c r="HC43" s="74"/>
-      <c r="HD43" s="74"/>
-      <c r="HE43" s="74"/>
-      <c r="HF43" s="74"/>
-      <c r="HG43" s="74"/>
-      <c r="HH43" s="74"/>
-      <c r="HI43" s="74"/>
-      <c r="HJ43" s="74"/>
-      <c r="HK43" s="74"/>
-      <c r="HL43" s="74"/>
-      <c r="HM43" s="74"/>
-      <c r="HN43" s="74"/>
-      <c r="HO43" s="74"/>
-      <c r="HP43" s="74"/>
-      <c r="HQ43" s="74"/>
-      <c r="HR43" s="74"/>
-      <c r="HS43" s="74"/>
-      <c r="HT43" s="74"/>
-      <c r="HU43" s="74"/>
-      <c r="HV43" s="74"/>
-      <c r="HW43" s="74"/>
-      <c r="HX43" s="74"/>
-      <c r="HY43" s="74"/>
-      <c r="HZ43" s="74"/>
-      <c r="IA43" s="74"/>
-      <c r="IB43" s="74"/>
-      <c r="IC43" s="74"/>
-      <c r="ID43" s="74"/>
-      <c r="IE43" s="74"/>
-      <c r="IF43" s="74"/>
-      <c r="IG43" s="74"/>
-      <c r="IH43" s="74"/>
-      <c r="II43" s="74"/>
-      <c r="IJ43" s="74"/>
-      <c r="IK43" s="74"/>
-      <c r="IL43" s="74"/>
-      <c r="IM43" s="74"/>
-      <c r="IN43" s="74"/>
-      <c r="IO43" s="74"/>
-      <c r="IP43" s="74"/>
-      <c r="IQ43" s="74"/>
-      <c r="IR43" s="74"/>
-      <c r="IS43" s="74"/>
-      <c r="IT43" s="74"/>
-      <c r="IU43" s="74"/>
-      <c r="IV43" s="74"/>
-      <c r="IW43" s="74"/>
-      <c r="IX43" s="74"/>
-      <c r="IY43" s="74"/>
-      <c r="IZ43" s="74"/>
-      <c r="JA43" s="74"/>
-      <c r="JB43" s="74"/>
-      <c r="JC43" s="74"/>
-      <c r="JD43" s="74"/>
-      <c r="JE43" s="74"/>
-      <c r="JF43" s="74"/>
-      <c r="JG43" s="74"/>
-      <c r="JH43" s="74"/>
-      <c r="JI43" s="74"/>
-      <c r="JJ43" s="74"/>
-      <c r="JK43" s="74"/>
-      <c r="JL43" s="74"/>
-      <c r="JM43" s="74"/>
-      <c r="JN43" s="74"/>
-      <c r="JO43" s="74"/>
-      <c r="JP43" s="74"/>
-      <c r="JQ43" s="74"/>
-      <c r="JR43" s="74"/>
-      <c r="JS43" s="74"/>
-      <c r="JT43" s="74"/>
-      <c r="JU43" s="74"/>
-      <c r="JV43" s="74"/>
-      <c r="JW43" s="74"/>
-      <c r="JX43" s="74"/>
-      <c r="JY43" s="74"/>
-      <c r="JZ43" s="74"/>
-      <c r="KA43" s="74"/>
-      <c r="KB43" s="74"/>
-      <c r="KC43" s="74"/>
-      <c r="KD43" s="74"/>
-      <c r="KE43" s="74"/>
-      <c r="KF43" s="74"/>
-      <c r="KG43" s="74"/>
-      <c r="KH43" s="74"/>
-      <c r="KI43" s="74"/>
-      <c r="KJ43" s="74"/>
-      <c r="KK43" s="74"/>
-      <c r="KL43" s="74"/>
-      <c r="KM43" s="74"/>
-      <c r="KN43" s="74"/>
-      <c r="KO43" s="74"/>
-      <c r="KP43" s="74"/>
-      <c r="KQ43" s="74"/>
-      <c r="KR43" s="74"/>
-      <c r="KS43" s="74"/>
-      <c r="KT43" s="74"/>
-      <c r="KU43" s="74"/>
-      <c r="KV43" s="74"/>
-      <c r="KW43" s="74"/>
-      <c r="KX43" s="74"/>
-      <c r="KY43" s="74"/>
-      <c r="KZ43" s="74"/>
-      <c r="LA43" s="74"/>
-      <c r="LB43" s="74"/>
-      <c r="LC43" s="74"/>
-      <c r="LD43" s="74"/>
-      <c r="LE43" s="74"/>
-      <c r="LF43" s="74"/>
-      <c r="LG43" s="74"/>
-      <c r="LH43" s="74"/>
-      <c r="LI43" s="74"/>
-      <c r="LJ43" s="74"/>
-      <c r="LK43" s="74"/>
-      <c r="LL43" s="74"/>
-      <c r="LM43" s="74"/>
-      <c r="LN43" s="74"/>
-      <c r="LO43" s="74"/>
-      <c r="LP43" s="74"/>
-      <c r="LQ43" s="74"/>
-      <c r="LR43" s="74"/>
-      <c r="LS43" s="74"/>
-      <c r="LT43" s="74"/>
-      <c r="LU43" s="74"/>
-      <c r="LV43" s="74"/>
-      <c r="LW43" s="74"/>
-      <c r="LX43" s="74"/>
-      <c r="LY43" s="74"/>
-      <c r="LZ43" s="74"/>
-      <c r="MA43" s="74"/>
-      <c r="MB43" s="74"/>
-      <c r="MC43" s="74"/>
-      <c r="MD43" s="74"/>
-      <c r="ME43" s="74"/>
-      <c r="MF43" s="74"/>
-      <c r="MG43" s="74"/>
-      <c r="MH43" s="74"/>
-      <c r="MI43" s="74"/>
-      <c r="MJ43" s="74"/>
-      <c r="MK43" s="74"/>
-      <c r="ML43" s="74"/>
-      <c r="MM43" s="74"/>
-      <c r="MN43" s="74"/>
-      <c r="MO43" s="74"/>
-      <c r="MP43" s="74"/>
-      <c r="MQ43" s="74"/>
-      <c r="MR43" s="74"/>
-      <c r="MS43" s="74"/>
-      <c r="MT43" s="74"/>
-      <c r="MU43" s="74"/>
-      <c r="MV43" s="74"/>
-      <c r="MW43" s="74"/>
-      <c r="MX43" s="74"/>
-      <c r="MY43" s="74"/>
-      <c r="MZ43" s="74"/>
-      <c r="NA43" s="74"/>
+    <row r="43" spans="1:365" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G43" s="6"/>
     </row>
-    <row r="44" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="A44" s="42"/>
-      <c r="B44" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="C44" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="67">
-        <v>0</v>
-      </c>
-      <c r="E44" s="68">
-        <v>46245</v>
-      </c>
-      <c r="F44" s="68">
-        <v>46245</v>
-      </c>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17">
-        <v>1</v>
-      </c>
-      <c r="I44" s="74"/>
-      <c r="J44" s="74"/>
-      <c r="K44" s="74"/>
-      <c r="L44" s="74"/>
-      <c r="M44" s="74"/>
-      <c r="N44" s="74"/>
-      <c r="O44" s="74"/>
-      <c r="P44" s="74"/>
-      <c r="Q44" s="74"/>
-      <c r="R44" s="74"/>
-      <c r="S44" s="74"/>
-      <c r="T44" s="74"/>
-      <c r="U44" s="74"/>
-      <c r="V44" s="74"/>
-      <c r="W44" s="74"/>
-      <c r="X44" s="74"/>
-      <c r="Y44" s="74"/>
-      <c r="Z44" s="74"/>
-      <c r="AA44" s="74"/>
-      <c r="AB44" s="74"/>
-      <c r="AC44" s="74"/>
-      <c r="AD44" s="74"/>
-      <c r="AE44" s="74"/>
-      <c r="AF44" s="74"/>
-      <c r="AG44" s="74"/>
-      <c r="AH44" s="74"/>
-      <c r="AI44" s="74"/>
-      <c r="AJ44" s="74"/>
-      <c r="AK44" s="74"/>
-      <c r="AL44" s="74"/>
-      <c r="AM44" s="74"/>
-      <c r="AN44" s="74"/>
-      <c r="AO44" s="74"/>
-      <c r="AP44" s="74"/>
-      <c r="AQ44" s="74"/>
-      <c r="AR44" s="74"/>
-      <c r="AS44" s="74"/>
-      <c r="AT44" s="74"/>
-      <c r="AU44" s="74"/>
-      <c r="AV44" s="74"/>
-      <c r="AW44" s="74"/>
-      <c r="AX44" s="74"/>
-      <c r="AY44" s="74"/>
-      <c r="AZ44" s="74"/>
-      <c r="BA44" s="74"/>
-      <c r="BB44" s="74"/>
-      <c r="BC44" s="74"/>
-      <c r="BD44" s="74"/>
-      <c r="BE44" s="74"/>
-      <c r="BF44" s="74"/>
-      <c r="BG44" s="74"/>
-      <c r="BH44" s="74"/>
-      <c r="BI44" s="74"/>
-      <c r="BJ44" s="74"/>
-      <c r="BK44" s="74"/>
-      <c r="BL44" s="74"/>
-      <c r="BM44" s="74"/>
-      <c r="BN44" s="74"/>
-      <c r="BO44" s="74"/>
-      <c r="BP44" s="74"/>
-      <c r="BQ44" s="74"/>
-      <c r="BR44" s="74"/>
-      <c r="BS44" s="74"/>
-      <c r="BT44" s="74"/>
-      <c r="BU44" s="74"/>
-      <c r="BV44" s="74"/>
-      <c r="BW44" s="74"/>
-      <c r="BX44" s="74"/>
-      <c r="BY44" s="74"/>
-      <c r="BZ44" s="74"/>
-      <c r="CA44" s="74"/>
-      <c r="CB44" s="74"/>
-      <c r="CC44" s="74"/>
-      <c r="CD44" s="74"/>
-      <c r="CE44" s="74"/>
-      <c r="CF44" s="74"/>
-      <c r="CG44" s="74"/>
-      <c r="CH44" s="74"/>
-      <c r="CI44" s="74"/>
-      <c r="CJ44" s="74"/>
-      <c r="CK44" s="74"/>
-      <c r="CL44" s="74"/>
-      <c r="CM44" s="74"/>
-      <c r="CN44" s="74"/>
-      <c r="CO44" s="74"/>
-      <c r="CP44" s="74"/>
-      <c r="CQ44" s="74"/>
-      <c r="CR44" s="74"/>
-      <c r="CS44" s="74"/>
-      <c r="CT44" s="74"/>
-      <c r="CU44" s="74"/>
-      <c r="CV44" s="74"/>
-      <c r="CW44" s="74"/>
-      <c r="CX44" s="74"/>
-      <c r="CY44" s="74"/>
-      <c r="CZ44" s="74"/>
-      <c r="DA44" s="74"/>
-      <c r="DB44" s="74"/>
-      <c r="DC44" s="74"/>
-      <c r="DD44" s="74"/>
-      <c r="DE44" s="74"/>
-      <c r="DF44" s="74"/>
-      <c r="DG44" s="74"/>
-      <c r="DH44" s="74"/>
-      <c r="DI44" s="74"/>
-      <c r="DJ44" s="74"/>
-      <c r="DK44" s="74"/>
-      <c r="DL44" s="74"/>
-      <c r="DM44" s="74"/>
-      <c r="DN44" s="74"/>
-      <c r="DO44" s="74"/>
-      <c r="DP44" s="74"/>
-      <c r="DQ44" s="74"/>
-      <c r="DR44" s="74"/>
-      <c r="DS44" s="74"/>
-      <c r="DT44" s="74"/>
-      <c r="DU44" s="74"/>
-      <c r="DV44" s="74"/>
-      <c r="DW44" s="74"/>
-      <c r="DX44" s="74"/>
-      <c r="DY44" s="74"/>
-      <c r="DZ44" s="74"/>
-      <c r="EA44" s="74"/>
-      <c r="EB44" s="74"/>
-      <c r="EC44" s="74"/>
-      <c r="ED44" s="74"/>
-      <c r="EE44" s="74"/>
-      <c r="EF44" s="74"/>
-      <c r="EG44" s="74"/>
-      <c r="EH44" s="74"/>
-      <c r="EI44" s="74"/>
-      <c r="EJ44" s="74"/>
-      <c r="EK44" s="74"/>
-      <c r="EL44" s="74"/>
-      <c r="EM44" s="74"/>
-      <c r="EN44" s="74"/>
-      <c r="EO44" s="74"/>
-      <c r="EP44" s="74"/>
-      <c r="EQ44" s="74"/>
-      <c r="ER44" s="74"/>
-      <c r="ES44" s="74"/>
-      <c r="ET44" s="74"/>
-      <c r="EU44" s="74"/>
-      <c r="EV44" s="74"/>
-      <c r="EW44" s="74"/>
-      <c r="EX44" s="74"/>
-      <c r="EY44" s="74"/>
-      <c r="EZ44" s="74"/>
-      <c r="FA44" s="74"/>
-      <c r="FB44" s="74"/>
-      <c r="FC44" s="74"/>
-      <c r="FD44" s="74"/>
-      <c r="FE44" s="74"/>
-      <c r="FF44" s="74"/>
-      <c r="FG44" s="74"/>
-      <c r="FH44" s="74"/>
-      <c r="FI44" s="74"/>
-      <c r="FJ44" s="74"/>
-      <c r="FK44" s="74"/>
-      <c r="FL44" s="74"/>
-      <c r="FM44" s="74"/>
-      <c r="FN44" s="74"/>
-      <c r="FO44" s="74"/>
-      <c r="FP44" s="74"/>
-      <c r="FQ44" s="74"/>
-      <c r="FR44" s="74"/>
-      <c r="FS44" s="74"/>
-      <c r="FT44" s="74"/>
-      <c r="FU44" s="74"/>
-      <c r="FV44" s="74"/>
-      <c r="FW44" s="74"/>
-      <c r="FX44" s="74"/>
-      <c r="FY44" s="74"/>
-      <c r="FZ44" s="74"/>
-      <c r="GA44" s="74"/>
-      <c r="GB44" s="74"/>
-      <c r="GC44" s="74"/>
-      <c r="GD44" s="74"/>
-      <c r="GE44" s="74"/>
-      <c r="GF44" s="74"/>
-      <c r="GG44" s="74"/>
-      <c r="GH44" s="74"/>
-      <c r="GI44" s="74"/>
-      <c r="GJ44" s="74"/>
-      <c r="GK44" s="74"/>
-      <c r="GL44" s="74"/>
-      <c r="GM44" s="74"/>
-      <c r="GN44" s="74"/>
-      <c r="GO44" s="74"/>
-      <c r="GP44" s="74"/>
-      <c r="GQ44" s="74"/>
-      <c r="GR44" s="74"/>
-      <c r="GS44" s="74"/>
-      <c r="GT44" s="74"/>
-      <c r="GU44" s="74"/>
-      <c r="GV44" s="74"/>
-      <c r="GW44" s="74"/>
-      <c r="GX44" s="74"/>
-      <c r="GY44" s="74"/>
-      <c r="GZ44" s="74"/>
-      <c r="HA44" s="74"/>
-      <c r="HB44" s="74"/>
-      <c r="HC44" s="74"/>
-      <c r="HD44" s="74"/>
-      <c r="HE44" s="74"/>
-      <c r="HF44" s="74"/>
-      <c r="HG44" s="74"/>
-      <c r="HH44" s="74"/>
-      <c r="HI44" s="74"/>
-      <c r="HJ44" s="74"/>
-      <c r="HK44" s="74"/>
-      <c r="HL44" s="74"/>
-      <c r="HM44" s="74"/>
-      <c r="HN44" s="74"/>
-      <c r="HO44" s="74"/>
-      <c r="HP44" s="74"/>
-      <c r="HQ44" s="74"/>
-      <c r="HR44" s="74"/>
-      <c r="HS44" s="74"/>
-      <c r="HT44" s="74"/>
-      <c r="HU44" s="74"/>
-      <c r="HV44" s="74"/>
-      <c r="HW44" s="74"/>
-      <c r="HX44" s="74"/>
-      <c r="HY44" s="74"/>
-      <c r="HZ44" s="74"/>
-      <c r="IA44" s="74"/>
-      <c r="IB44" s="74"/>
-      <c r="IC44" s="74"/>
-      <c r="ID44" s="74"/>
-      <c r="IE44" s="74"/>
-      <c r="IF44" s="74"/>
-      <c r="IG44" s="74"/>
-      <c r="IH44" s="74"/>
-      <c r="II44" s="74"/>
-      <c r="IJ44" s="74"/>
-      <c r="IK44" s="74"/>
-      <c r="IL44" s="74"/>
-      <c r="IM44" s="74"/>
-      <c r="IN44" s="74"/>
-      <c r="IO44" s="74"/>
-      <c r="IP44" s="74"/>
-      <c r="IQ44" s="74"/>
-      <c r="IR44" s="74"/>
-      <c r="IS44" s="74"/>
-      <c r="IT44" s="74"/>
-      <c r="IU44" s="74"/>
-      <c r="IV44" s="74"/>
-      <c r="IW44" s="74"/>
-      <c r="IX44" s="74"/>
-      <c r="IY44" s="74"/>
-      <c r="IZ44" s="74"/>
-      <c r="JA44" s="74"/>
-      <c r="JB44" s="74"/>
-      <c r="JC44" s="74"/>
-      <c r="JD44" s="74"/>
-      <c r="JE44" s="74"/>
-      <c r="JF44" s="74"/>
-      <c r="JG44" s="74"/>
-      <c r="JH44" s="74"/>
-      <c r="JI44" s="74"/>
-      <c r="JJ44" s="74"/>
-      <c r="JK44" s="74"/>
-      <c r="JL44" s="74"/>
-      <c r="JM44" s="74"/>
-      <c r="JN44" s="74"/>
-      <c r="JO44" s="74"/>
-      <c r="JP44" s="74"/>
-      <c r="JQ44" s="74"/>
-      <c r="JR44" s="74"/>
-      <c r="JS44" s="74"/>
-      <c r="JT44" s="74"/>
-      <c r="JU44" s="74"/>
-      <c r="JV44" s="74"/>
-      <c r="JW44" s="74"/>
-      <c r="JX44" s="74"/>
-      <c r="JY44" s="74"/>
-      <c r="JZ44" s="74"/>
-      <c r="KA44" s="74"/>
-      <c r="KB44" s="74"/>
-      <c r="KC44" s="74"/>
-      <c r="KD44" s="74"/>
-      <c r="KE44" s="74"/>
-      <c r="KF44" s="74"/>
-      <c r="KG44" s="74"/>
-      <c r="KH44" s="74"/>
-      <c r="KI44" s="74"/>
-      <c r="KJ44" s="74"/>
-      <c r="KK44" s="74"/>
-      <c r="KL44" s="74"/>
-      <c r="KM44" s="74"/>
-      <c r="KN44" s="74"/>
-      <c r="KO44" s="74"/>
-      <c r="KP44" s="74"/>
-      <c r="KQ44" s="74"/>
-      <c r="KR44" s="74"/>
-      <c r="KS44" s="74"/>
-      <c r="KT44" s="74"/>
-      <c r="KU44" s="74"/>
-      <c r="KV44" s="74"/>
-      <c r="KW44" s="74"/>
-      <c r="KX44" s="74"/>
-      <c r="KY44" s="74"/>
-      <c r="KZ44" s="74"/>
-      <c r="LA44" s="74"/>
-      <c r="LB44" s="74"/>
-      <c r="LC44" s="74"/>
-      <c r="LD44" s="74"/>
-      <c r="LE44" s="74"/>
-      <c r="LF44" s="74"/>
-      <c r="LG44" s="74"/>
-      <c r="LH44" s="74"/>
-      <c r="LI44" s="74"/>
-      <c r="LJ44" s="74"/>
-      <c r="LK44" s="74"/>
-      <c r="LL44" s="74"/>
-      <c r="LM44" s="74"/>
-      <c r="LN44" s="74"/>
-      <c r="LO44" s="74"/>
-      <c r="LP44" s="74"/>
-      <c r="LQ44" s="74"/>
-      <c r="LR44" s="74"/>
-      <c r="LS44" s="74"/>
-      <c r="LT44" s="74"/>
-      <c r="LU44" s="74"/>
-      <c r="LV44" s="74"/>
-      <c r="LW44" s="74"/>
-      <c r="LX44" s="74"/>
-      <c r="LY44" s="74"/>
-      <c r="LZ44" s="74"/>
-      <c r="MA44" s="74"/>
-      <c r="MB44" s="74"/>
-      <c r="MC44" s="74"/>
-      <c r="MD44" s="74"/>
-      <c r="ME44" s="74"/>
-      <c r="MF44" s="74"/>
-      <c r="MG44" s="74"/>
-      <c r="MH44" s="74"/>
-      <c r="MI44" s="74"/>
-      <c r="MJ44" s="74"/>
-      <c r="MK44" s="74"/>
-      <c r="ML44" s="74"/>
-      <c r="MM44" s="74"/>
-      <c r="MN44" s="74"/>
-      <c r="MO44" s="74"/>
-      <c r="MP44" s="74"/>
-      <c r="MQ44" s="74"/>
-      <c r="MR44" s="74"/>
-      <c r="MS44" s="74"/>
-      <c r="MT44" s="74"/>
-      <c r="MU44" s="74"/>
-      <c r="MV44" s="74"/>
-      <c r="MW44" s="74"/>
-      <c r="MX44" s="74"/>
-      <c r="MY44" s="74"/>
-      <c r="MZ44" s="74"/>
-      <c r="NA44" s="74"/>
+    <row r="44" spans="1:365" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="14"/>
+      <c r="F44" s="43"/>
     </row>
-    <row r="45" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="A45" s="42"/>
-      <c r="B45" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="C45" s="66" t="s">
-        <v>37</v>
-      </c>
-      <c r="D45" s="67">
-        <v>0</v>
-      </c>
-      <c r="E45" s="68">
-        <v>46244</v>
-      </c>
-      <c r="F45" s="68">
-        <v>46183</v>
-      </c>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17">
-        <v>1</v>
-      </c>
-      <c r="I45" s="74"/>
-      <c r="J45" s="74"/>
-      <c r="K45" s="74"/>
-      <c r="L45" s="74"/>
-      <c r="M45" s="74"/>
-      <c r="N45" s="74"/>
-      <c r="O45" s="74"/>
-      <c r="P45" s="74"/>
-      <c r="Q45" s="74"/>
-      <c r="R45" s="74"/>
-      <c r="S45" s="74"/>
-      <c r="T45" s="74"/>
-      <c r="U45" s="74"/>
-      <c r="V45" s="74"/>
-      <c r="W45" s="74"/>
-      <c r="X45" s="74"/>
-      <c r="Y45" s="74"/>
-      <c r="Z45" s="74"/>
-      <c r="AA45" s="74"/>
-      <c r="AB45" s="74"/>
-      <c r="AC45" s="74"/>
-      <c r="AD45" s="74"/>
-      <c r="AE45" s="74"/>
-      <c r="AF45" s="74"/>
-      <c r="AG45" s="74"/>
-      <c r="AH45" s="74"/>
-      <c r="AI45" s="74"/>
-      <c r="AJ45" s="74"/>
-      <c r="AK45" s="74"/>
-      <c r="AL45" s="74"/>
-      <c r="AM45" s="74"/>
-      <c r="AN45" s="74"/>
-      <c r="AO45" s="74"/>
-      <c r="AP45" s="74"/>
-      <c r="AQ45" s="74"/>
-      <c r="AR45" s="74"/>
-      <c r="AS45" s="74"/>
-      <c r="AT45" s="74"/>
-      <c r="AU45" s="74"/>
-      <c r="AV45" s="74"/>
-      <c r="AW45" s="74"/>
-      <c r="AX45" s="74"/>
-      <c r="AY45" s="74"/>
-      <c r="AZ45" s="74"/>
-      <c r="BA45" s="74"/>
-      <c r="BB45" s="74"/>
-      <c r="BC45" s="74"/>
-      <c r="BD45" s="74"/>
-      <c r="BE45" s="74"/>
-      <c r="BF45" s="74"/>
-      <c r="BG45" s="74"/>
-      <c r="BH45" s="74"/>
-      <c r="BI45" s="74"/>
-      <c r="BJ45" s="74"/>
-      <c r="BK45" s="74"/>
-      <c r="BL45" s="74"/>
-      <c r="BM45" s="74"/>
-      <c r="BN45" s="74"/>
-      <c r="BO45" s="74"/>
-      <c r="BP45" s="74"/>
-      <c r="BQ45" s="74"/>
-      <c r="BR45" s="74"/>
-      <c r="BS45" s="74"/>
-      <c r="BT45" s="74"/>
-      <c r="BU45" s="74"/>
-      <c r="BV45" s="74"/>
-      <c r="BW45" s="74"/>
-      <c r="BX45" s="74"/>
-      <c r="BY45" s="74"/>
-      <c r="BZ45" s="74"/>
-      <c r="CA45" s="74"/>
-      <c r="CB45" s="74"/>
-      <c r="CC45" s="74"/>
-      <c r="CD45" s="74"/>
-      <c r="CE45" s="74"/>
-      <c r="CF45" s="74"/>
-      <c r="CG45" s="74"/>
-      <c r="CH45" s="74"/>
-      <c r="CI45" s="74"/>
-      <c r="CJ45" s="74"/>
-      <c r="CK45" s="74"/>
-      <c r="CL45" s="74"/>
-      <c r="CM45" s="74"/>
-      <c r="CN45" s="74"/>
-      <c r="CO45" s="74"/>
-      <c r="CP45" s="74"/>
-      <c r="CQ45" s="74"/>
-      <c r="CR45" s="74"/>
-      <c r="CS45" s="74"/>
-      <c r="CT45" s="74"/>
-      <c r="CU45" s="74"/>
-      <c r="CV45" s="74"/>
-      <c r="CW45" s="74"/>
-      <c r="CX45" s="74"/>
-      <c r="CY45" s="74"/>
-      <c r="CZ45" s="74"/>
-      <c r="DA45" s="74"/>
-      <c r="DB45" s="74"/>
-      <c r="DC45" s="74"/>
-      <c r="DD45" s="74"/>
-      <c r="DE45" s="74"/>
-      <c r="DF45" s="74"/>
-      <c r="DG45" s="74"/>
-      <c r="DH45" s="74"/>
-      <c r="DI45" s="74"/>
-      <c r="DJ45" s="74"/>
-      <c r="DK45" s="74"/>
-      <c r="DL45" s="74"/>
-      <c r="DM45" s="74"/>
-      <c r="DN45" s="74"/>
-      <c r="DO45" s="74"/>
-      <c r="DP45" s="74"/>
-      <c r="DQ45" s="74"/>
-      <c r="DR45" s="74"/>
-      <c r="DS45" s="74"/>
-      <c r="DT45" s="74"/>
-      <c r="DU45" s="74"/>
-      <c r="DV45" s="74"/>
-      <c r="DW45" s="74"/>
-      <c r="DX45" s="74"/>
-      <c r="DY45" s="74"/>
-      <c r="DZ45" s="74"/>
-      <c r="EA45" s="74"/>
-      <c r="EB45" s="74"/>
-      <c r="EC45" s="74"/>
-      <c r="ED45" s="74"/>
-      <c r="EE45" s="74"/>
-      <c r="EF45" s="74"/>
-      <c r="EG45" s="74"/>
-      <c r="EH45" s="74"/>
-      <c r="EI45" s="74"/>
-      <c r="EJ45" s="74"/>
-      <c r="EK45" s="74"/>
-      <c r="EL45" s="74"/>
-      <c r="EM45" s="74"/>
-      <c r="EN45" s="74"/>
-      <c r="EO45" s="74"/>
-      <c r="EP45" s="74"/>
-      <c r="EQ45" s="74"/>
-      <c r="ER45" s="74"/>
-      <c r="ES45" s="74"/>
-      <c r="ET45" s="74"/>
-      <c r="EU45" s="74"/>
-      <c r="EV45" s="74"/>
-      <c r="EW45" s="74"/>
-      <c r="EX45" s="74"/>
-      <c r="EY45" s="74"/>
-      <c r="EZ45" s="74"/>
-      <c r="FA45" s="74"/>
-      <c r="FB45" s="74"/>
-      <c r="FC45" s="74"/>
-      <c r="FD45" s="74"/>
-      <c r="FE45" s="74"/>
-      <c r="FF45" s="74"/>
-      <c r="FG45" s="74"/>
-      <c r="FH45" s="74"/>
-      <c r="FI45" s="74"/>
-      <c r="FJ45" s="74"/>
-      <c r="FK45" s="74"/>
-      <c r="FL45" s="74"/>
-      <c r="FM45" s="74"/>
-      <c r="FN45" s="74"/>
-      <c r="FO45" s="74"/>
-      <c r="FP45" s="74"/>
-      <c r="FQ45" s="74"/>
-      <c r="FR45" s="74"/>
-      <c r="FS45" s="74"/>
-      <c r="FT45" s="74"/>
-      <c r="FU45" s="74"/>
-      <c r="FV45" s="74"/>
-      <c r="FW45" s="74"/>
-      <c r="FX45" s="74"/>
-      <c r="FY45" s="74"/>
-      <c r="FZ45" s="74"/>
-      <c r="GA45" s="74"/>
-      <c r="GB45" s="74"/>
-      <c r="GC45" s="74"/>
-      <c r="GD45" s="74"/>
-      <c r="GE45" s="74"/>
-      <c r="GF45" s="74"/>
-      <c r="GG45" s="74"/>
-      <c r="GH45" s="74"/>
-      <c r="GI45" s="74"/>
-      <c r="GJ45" s="74"/>
-      <c r="GK45" s="74"/>
-      <c r="GL45" s="74"/>
-      <c r="GM45" s="74"/>
-      <c r="GN45" s="74"/>
-      <c r="GO45" s="74"/>
-      <c r="GP45" s="74"/>
-      <c r="GQ45" s="74"/>
-      <c r="GR45" s="74"/>
-      <c r="GS45" s="74"/>
-      <c r="GT45" s="74"/>
-      <c r="GU45" s="74"/>
-      <c r="GV45" s="74"/>
-      <c r="GW45" s="74"/>
-      <c r="GX45" s="74"/>
-      <c r="GY45" s="74"/>
-      <c r="GZ45" s="74"/>
-      <c r="HA45" s="74"/>
-      <c r="HB45" s="74"/>
-      <c r="HC45" s="74"/>
-      <c r="HD45" s="74"/>
-      <c r="HE45" s="74"/>
-      <c r="HF45" s="74"/>
-      <c r="HG45" s="74"/>
-      <c r="HH45" s="74"/>
-      <c r="HI45" s="74"/>
-      <c r="HJ45" s="74"/>
-      <c r="HK45" s="74"/>
-      <c r="HL45" s="74"/>
-      <c r="HM45" s="74"/>
-      <c r="HN45" s="74"/>
-      <c r="HO45" s="74"/>
-      <c r="HP45" s="74"/>
-      <c r="HQ45" s="74"/>
-      <c r="HR45" s="74"/>
-      <c r="HS45" s="74"/>
-      <c r="HT45" s="74"/>
-      <c r="HU45" s="74"/>
-      <c r="HV45" s="74"/>
-      <c r="HW45" s="74"/>
-      <c r="HX45" s="74"/>
-      <c r="HY45" s="74"/>
-      <c r="HZ45" s="74"/>
-      <c r="IA45" s="74"/>
-      <c r="IB45" s="74"/>
-      <c r="IC45" s="74"/>
-      <c r="ID45" s="74"/>
-      <c r="IE45" s="74"/>
-      <c r="IF45" s="74"/>
-      <c r="IG45" s="74"/>
-      <c r="IH45" s="74"/>
-      <c r="II45" s="74"/>
-      <c r="IJ45" s="74"/>
-      <c r="IK45" s="74"/>
-      <c r="IL45" s="74"/>
-      <c r="IM45" s="74"/>
-      <c r="IN45" s="74"/>
-      <c r="IO45" s="74"/>
-      <c r="IP45" s="74"/>
-      <c r="IQ45" s="74"/>
-      <c r="IR45" s="74"/>
-      <c r="IS45" s="74"/>
-      <c r="IT45" s="74"/>
-      <c r="IU45" s="74"/>
-      <c r="IV45" s="74"/>
-      <c r="IW45" s="74"/>
-      <c r="IX45" s="74"/>
-      <c r="IY45" s="74"/>
-      <c r="IZ45" s="74"/>
-      <c r="JA45" s="74"/>
-      <c r="JB45" s="74"/>
-      <c r="JC45" s="74"/>
-      <c r="JD45" s="74"/>
-      <c r="JE45" s="74"/>
-      <c r="JF45" s="74"/>
-      <c r="JG45" s="74"/>
-      <c r="JH45" s="74"/>
-      <c r="JI45" s="74"/>
-      <c r="JJ45" s="74"/>
-      <c r="JK45" s="74"/>
-      <c r="JL45" s="74"/>
-      <c r="JM45" s="74"/>
-      <c r="JN45" s="74"/>
-      <c r="JO45" s="74"/>
-      <c r="JP45" s="74"/>
-      <c r="JQ45" s="74"/>
-      <c r="JR45" s="74"/>
-      <c r="JS45" s="74"/>
-      <c r="JT45" s="74"/>
-      <c r="JU45" s="74"/>
-      <c r="JV45" s="74"/>
-      <c r="JW45" s="74"/>
-      <c r="JX45" s="74"/>
-      <c r="JY45" s="74"/>
-      <c r="JZ45" s="74"/>
-      <c r="KA45" s="74"/>
-      <c r="KB45" s="74"/>
-      <c r="KC45" s="74"/>
-      <c r="KD45" s="74"/>
-      <c r="KE45" s="74"/>
-      <c r="KF45" s="74"/>
-      <c r="KG45" s="74"/>
-      <c r="KH45" s="74"/>
-      <c r="KI45" s="74"/>
-      <c r="KJ45" s="74"/>
-      <c r="KK45" s="74"/>
-      <c r="KL45" s="74"/>
-      <c r="KM45" s="74"/>
-      <c r="KN45" s="74"/>
-      <c r="KO45" s="74"/>
-      <c r="KP45" s="74"/>
-      <c r="KQ45" s="74"/>
-      <c r="KR45" s="74"/>
-      <c r="KS45" s="74"/>
-      <c r="KT45" s="74"/>
-      <c r="KU45" s="74"/>
-      <c r="KV45" s="74"/>
-      <c r="KW45" s="74"/>
-      <c r="KX45" s="74"/>
-      <c r="KY45" s="74"/>
-      <c r="KZ45" s="74"/>
-      <c r="LA45" s="74"/>
-      <c r="LB45" s="74"/>
-      <c r="LC45" s="74"/>
-      <c r="LD45" s="74"/>
-      <c r="LE45" s="74"/>
-      <c r="LF45" s="74"/>
-      <c r="LG45" s="74"/>
-      <c r="LH45" s="74"/>
-      <c r="LI45" s="74"/>
-      <c r="LJ45" s="74"/>
-      <c r="LK45" s="74"/>
-      <c r="LL45" s="74"/>
-      <c r="LM45" s="74"/>
-      <c r="LN45" s="74"/>
-      <c r="LO45" s="74"/>
-      <c r="LP45" s="74"/>
-      <c r="LQ45" s="74"/>
-      <c r="LR45" s="74"/>
-      <c r="LS45" s="74"/>
-      <c r="LT45" s="74"/>
-      <c r="LU45" s="74"/>
-      <c r="LV45" s="74"/>
-      <c r="LW45" s="74"/>
-      <c r="LX45" s="74"/>
-      <c r="LY45" s="74"/>
-      <c r="LZ45" s="74"/>
-      <c r="MA45" s="74"/>
-      <c r="MB45" s="74"/>
-      <c r="MC45" s="74"/>
-      <c r="MD45" s="74"/>
-      <c r="ME45" s="74"/>
-      <c r="MF45" s="74"/>
-      <c r="MG45" s="74"/>
-      <c r="MH45" s="74"/>
-      <c r="MI45" s="74"/>
-      <c r="MJ45" s="74"/>
-      <c r="MK45" s="74"/>
-      <c r="ML45" s="74"/>
-      <c r="MM45" s="74"/>
-      <c r="MN45" s="74"/>
-      <c r="MO45" s="74"/>
-      <c r="MP45" s="74"/>
-      <c r="MQ45" s="74"/>
-      <c r="MR45" s="74"/>
-      <c r="MS45" s="74"/>
-      <c r="MT45" s="74"/>
-      <c r="MU45" s="74"/>
-      <c r="MV45" s="74"/>
-      <c r="MW45" s="74"/>
-      <c r="MX45" s="74"/>
-      <c r="MY45" s="74"/>
-      <c r="MZ45" s="74"/>
-      <c r="NA45" s="74"/>
-    </row>
-    <row r="46" spans="1:365" s="3" customFormat="1" ht="30" customHeight="1">
-      <c r="A46" s="42"/>
-      <c r="B46" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="66" t="s">
-        <v>37</v>
-      </c>
-      <c r="D46" s="67">
-        <v>0</v>
-      </c>
-      <c r="E46" s="68">
-        <v>46248</v>
-      </c>
-      <c r="F46" s="68">
-        <v>46259</v>
-      </c>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17">
-        <v>11</v>
-      </c>
-      <c r="I46" s="74"/>
-      <c r="J46" s="74"/>
-      <c r="K46" s="74"/>
-      <c r="L46" s="74"/>
-      <c r="M46" s="74"/>
-      <c r="N46" s="74"/>
-      <c r="O46" s="74"/>
-      <c r="P46" s="74"/>
-      <c r="Q46" s="74"/>
-      <c r="R46" s="74"/>
-      <c r="S46" s="74"/>
-      <c r="T46" s="74"/>
-      <c r="U46" s="74"/>
-      <c r="V46" s="74"/>
-      <c r="W46" s="74"/>
-      <c r="X46" s="74"/>
-      <c r="Y46" s="74"/>
-      <c r="Z46" s="74"/>
-      <c r="AA46" s="74"/>
-      <c r="AB46" s="74"/>
-      <c r="AC46" s="74"/>
-      <c r="AD46" s="74"/>
-      <c r="AE46" s="74"/>
-      <c r="AF46" s="74"/>
-      <c r="AG46" s="74"/>
-      <c r="AH46" s="74"/>
-      <c r="AI46" s="74"/>
-      <c r="AJ46" s="74"/>
-      <c r="AK46" s="74"/>
-      <c r="AL46" s="74"/>
-      <c r="AM46" s="74"/>
-      <c r="AN46" s="74"/>
-      <c r="AO46" s="74"/>
-      <c r="AP46" s="74"/>
-      <c r="AQ46" s="74"/>
-      <c r="AR46" s="74"/>
-      <c r="AS46" s="74"/>
-      <c r="AT46" s="74"/>
-      <c r="AU46" s="74"/>
-      <c r="AV46" s="74"/>
-      <c r="AW46" s="74"/>
-      <c r="AX46" s="74"/>
-      <c r="AY46" s="74"/>
-      <c r="AZ46" s="74"/>
-      <c r="BA46" s="74"/>
-      <c r="BB46" s="74"/>
-      <c r="BC46" s="74"/>
-      <c r="BD46" s="74"/>
-      <c r="BE46" s="74"/>
-      <c r="BF46" s="74"/>
-      <c r="BG46" s="74"/>
-      <c r="BH46" s="74"/>
-      <c r="BI46" s="74"/>
-      <c r="BJ46" s="74"/>
-      <c r="BK46" s="74"/>
-      <c r="BL46" s="74"/>
-      <c r="BM46" s="74"/>
-      <c r="BN46" s="74"/>
-      <c r="BO46" s="74"/>
-      <c r="BP46" s="74"/>
-      <c r="BQ46" s="74"/>
-      <c r="BR46" s="74"/>
-      <c r="BS46" s="74"/>
-      <c r="BT46" s="74"/>
-      <c r="BU46" s="74"/>
-      <c r="BV46" s="74"/>
-      <c r="BW46" s="74"/>
-      <c r="BX46" s="74"/>
-      <c r="BY46" s="74"/>
-      <c r="BZ46" s="74"/>
-      <c r="CA46" s="74"/>
-      <c r="CB46" s="74"/>
-      <c r="CC46" s="74"/>
-      <c r="CD46" s="74"/>
-      <c r="CE46" s="74"/>
-      <c r="CF46" s="74"/>
-      <c r="CG46" s="74"/>
-      <c r="CH46" s="74"/>
-      <c r="CI46" s="74"/>
-      <c r="CJ46" s="74"/>
-      <c r="CK46" s="74"/>
-      <c r="CL46" s="74"/>
-      <c r="CM46" s="74"/>
-      <c r="CN46" s="74"/>
-      <c r="CO46" s="74"/>
-      <c r="CP46" s="74"/>
-      <c r="CQ46" s="74"/>
-      <c r="CR46" s="74"/>
-      <c r="CS46" s="74"/>
-      <c r="CT46" s="74"/>
-      <c r="CU46" s="74"/>
-      <c r="CV46" s="74"/>
-      <c r="CW46" s="74"/>
-      <c r="CX46" s="74"/>
-      <c r="CY46" s="74"/>
-      <c r="CZ46" s="74"/>
-      <c r="DA46" s="74"/>
-      <c r="DB46" s="74"/>
-      <c r="DC46" s="74"/>
-      <c r="DD46" s="74"/>
-      <c r="DE46" s="74"/>
-      <c r="DF46" s="74"/>
-      <c r="DG46" s="74"/>
-      <c r="DH46" s="74"/>
-      <c r="DI46" s="74"/>
-      <c r="DJ46" s="74"/>
-      <c r="DK46" s="74"/>
-      <c r="DL46" s="74"/>
-      <c r="DM46" s="74"/>
-      <c r="DN46" s="74"/>
-      <c r="DO46" s="74"/>
-      <c r="DP46" s="74"/>
-      <c r="DQ46" s="74"/>
-      <c r="DR46" s="74"/>
-      <c r="DS46" s="74"/>
-      <c r="DT46" s="74"/>
-      <c r="DU46" s="74"/>
-      <c r="DV46" s="74"/>
-      <c r="DW46" s="74"/>
-      <c r="DX46" s="74"/>
-      <c r="DY46" s="74"/>
-      <c r="DZ46" s="74"/>
-      <c r="EA46" s="74"/>
-      <c r="EB46" s="74"/>
-      <c r="EC46" s="74"/>
-      <c r="ED46" s="74"/>
-      <c r="EE46" s="74"/>
-      <c r="EF46" s="74"/>
-      <c r="EG46" s="74"/>
-      <c r="EH46" s="74"/>
-      <c r="EI46" s="74"/>
-      <c r="EJ46" s="74"/>
-      <c r="EK46" s="74"/>
-      <c r="EL46" s="74"/>
-      <c r="EM46" s="74"/>
-      <c r="EN46" s="74"/>
-      <c r="EO46" s="74"/>
-      <c r="EP46" s="74"/>
-      <c r="EQ46" s="74"/>
-      <c r="ER46" s="74"/>
-      <c r="ES46" s="74"/>
-      <c r="ET46" s="74"/>
-      <c r="EU46" s="74"/>
-      <c r="EV46" s="74"/>
-      <c r="EW46" s="74"/>
-      <c r="EX46" s="74"/>
-      <c r="EY46" s="74"/>
-      <c r="EZ46" s="74"/>
-      <c r="FA46" s="74"/>
-      <c r="FB46" s="74"/>
-      <c r="FC46" s="74"/>
-      <c r="FD46" s="74"/>
-      <c r="FE46" s="74"/>
-      <c r="FF46" s="74"/>
-      <c r="FG46" s="74"/>
-      <c r="FH46" s="74"/>
-      <c r="FI46" s="74"/>
-      <c r="FJ46" s="74"/>
-      <c r="FK46" s="74"/>
-      <c r="FL46" s="74"/>
-      <c r="FM46" s="74"/>
-      <c r="FN46" s="74"/>
-      <c r="FO46" s="74"/>
-      <c r="FP46" s="74"/>
-      <c r="FQ46" s="74"/>
-      <c r="FR46" s="74"/>
-      <c r="FS46" s="74"/>
-      <c r="FT46" s="74"/>
-      <c r="FU46" s="74"/>
-      <c r="FV46" s="74"/>
-      <c r="FW46" s="74"/>
-      <c r="FX46" s="74"/>
-      <c r="FY46" s="74"/>
-      <c r="FZ46" s="74"/>
-      <c r="GA46" s="74"/>
-      <c r="GB46" s="74"/>
-      <c r="GC46" s="74"/>
-      <c r="GD46" s="74"/>
-      <c r="GE46" s="74"/>
-      <c r="GF46" s="74"/>
-      <c r="GG46" s="74"/>
-      <c r="GH46" s="74"/>
-      <c r="GI46" s="74"/>
-      <c r="GJ46" s="74"/>
-      <c r="GK46" s="74"/>
-      <c r="GL46" s="74"/>
-      <c r="GM46" s="74"/>
-      <c r="GN46" s="74"/>
-      <c r="GO46" s="74"/>
-      <c r="GP46" s="74"/>
-      <c r="GQ46" s="74"/>
-      <c r="GR46" s="74"/>
-      <c r="GS46" s="74"/>
-      <c r="GT46" s="74"/>
-      <c r="GU46" s="74"/>
-      <c r="GV46" s="74"/>
-      <c r="GW46" s="74"/>
-      <c r="GX46" s="74"/>
-      <c r="GY46" s="74"/>
-      <c r="GZ46" s="74"/>
-      <c r="HA46" s="74"/>
-      <c r="HB46" s="74"/>
-      <c r="HC46" s="74"/>
-      <c r="HD46" s="74"/>
-      <c r="HE46" s="74"/>
-      <c r="HF46" s="74"/>
-      <c r="HG46" s="74"/>
-      <c r="HH46" s="74"/>
-      <c r="HI46" s="74"/>
-      <c r="HJ46" s="74"/>
-      <c r="HK46" s="74"/>
-      <c r="HL46" s="74"/>
-      <c r="HM46" s="74"/>
-      <c r="HN46" s="74"/>
-      <c r="HO46" s="74"/>
-      <c r="HP46" s="74"/>
-      <c r="HQ46" s="74"/>
-      <c r="HR46" s="74"/>
-      <c r="HS46" s="74"/>
-      <c r="HT46" s="74"/>
-      <c r="HU46" s="74"/>
-      <c r="HV46" s="74"/>
-      <c r="HW46" s="74"/>
-      <c r="HX46" s="74"/>
-      <c r="HY46" s="74"/>
-      <c r="HZ46" s="74"/>
-      <c r="IA46" s="74"/>
-      <c r="IB46" s="74"/>
-      <c r="IC46" s="74"/>
-      <c r="ID46" s="74"/>
-      <c r="IE46" s="74"/>
-      <c r="IF46" s="74"/>
-      <c r="IG46" s="74"/>
-      <c r="IH46" s="74"/>
-      <c r="II46" s="74"/>
-      <c r="IJ46" s="74"/>
-      <c r="IK46" s="74"/>
-      <c r="IL46" s="74"/>
-      <c r="IM46" s="74"/>
-      <c r="IN46" s="74"/>
-      <c r="IO46" s="74"/>
-      <c r="IP46" s="74"/>
-      <c r="IQ46" s="74"/>
-      <c r="IR46" s="74"/>
-      <c r="IS46" s="74"/>
-      <c r="IT46" s="74"/>
-      <c r="IU46" s="74"/>
-      <c r="IV46" s="74"/>
-      <c r="IW46" s="74"/>
-      <c r="IX46" s="74"/>
-      <c r="IY46" s="74"/>
-      <c r="IZ46" s="74"/>
-      <c r="JA46" s="74"/>
-      <c r="JB46" s="74"/>
-      <c r="JC46" s="74"/>
-      <c r="JD46" s="74"/>
-      <c r="JE46" s="74"/>
-      <c r="JF46" s="74"/>
-      <c r="JG46" s="74"/>
-      <c r="JH46" s="74"/>
-      <c r="JI46" s="74"/>
-      <c r="JJ46" s="74"/>
-      <c r="JK46" s="74"/>
-      <c r="JL46" s="74"/>
-      <c r="JM46" s="74"/>
-      <c r="JN46" s="74"/>
-      <c r="JO46" s="74"/>
-      <c r="JP46" s="74"/>
-      <c r="JQ46" s="74"/>
-      <c r="JR46" s="74"/>
-      <c r="JS46" s="74"/>
-      <c r="JT46" s="74"/>
-      <c r="JU46" s="74"/>
-      <c r="JV46" s="74"/>
-      <c r="JW46" s="74"/>
-      <c r="JX46" s="74"/>
-      <c r="JY46" s="74"/>
-      <c r="JZ46" s="74"/>
-      <c r="KA46" s="74"/>
-      <c r="KB46" s="74"/>
-      <c r="KC46" s="74"/>
-      <c r="KD46" s="74"/>
-      <c r="KE46" s="74"/>
-      <c r="KF46" s="74"/>
-      <c r="KG46" s="74"/>
-      <c r="KH46" s="74"/>
-      <c r="KI46" s="74"/>
-      <c r="KJ46" s="74"/>
-      <c r="KK46" s="74"/>
-      <c r="KL46" s="74"/>
-      <c r="KM46" s="74"/>
-      <c r="KN46" s="74"/>
-      <c r="KO46" s="74"/>
-      <c r="KP46" s="74"/>
-      <c r="KQ46" s="74"/>
-      <c r="KR46" s="74"/>
-      <c r="KS46" s="74"/>
-      <c r="KT46" s="74"/>
-      <c r="KU46" s="74"/>
-      <c r="KV46" s="74"/>
-      <c r="KW46" s="74"/>
-      <c r="KX46" s="74"/>
-      <c r="KY46" s="74"/>
-      <c r="KZ46" s="74"/>
-      <c r="LA46" s="74"/>
-      <c r="LB46" s="74"/>
-      <c r="LC46" s="74"/>
-      <c r="LD46" s="74"/>
-      <c r="LE46" s="74"/>
-      <c r="LF46" s="74"/>
-      <c r="LG46" s="74"/>
-      <c r="LH46" s="74"/>
-      <c r="LI46" s="74"/>
-      <c r="LJ46" s="74"/>
-      <c r="LK46" s="74"/>
-      <c r="LL46" s="74"/>
-      <c r="LM46" s="74"/>
-      <c r="LN46" s="74"/>
-      <c r="LO46" s="74"/>
-      <c r="LP46" s="74"/>
-      <c r="LQ46" s="74"/>
-      <c r="LR46" s="74"/>
-      <c r="LS46" s="74"/>
-      <c r="LT46" s="74"/>
-      <c r="LU46" s="74"/>
-      <c r="LV46" s="74"/>
-      <c r="LW46" s="74"/>
-      <c r="LX46" s="74"/>
-      <c r="LY46" s="74"/>
-      <c r="LZ46" s="74"/>
-      <c r="MA46" s="74"/>
-      <c r="MB46" s="74"/>
-      <c r="MC46" s="74"/>
-      <c r="MD46" s="74"/>
-      <c r="ME46" s="74"/>
-      <c r="MF46" s="74"/>
-      <c r="MG46" s="74"/>
-      <c r="MH46" s="74"/>
-      <c r="MI46" s="74"/>
-      <c r="MJ46" s="74"/>
-      <c r="MK46" s="74"/>
-      <c r="ML46" s="74"/>
-      <c r="MM46" s="74"/>
-      <c r="MN46" s="74"/>
-      <c r="MO46" s="74"/>
-      <c r="MP46" s="74"/>
-      <c r="MQ46" s="74"/>
-      <c r="MR46" s="74"/>
-      <c r="MS46" s="74"/>
-      <c r="MT46" s="74"/>
-      <c r="MU46" s="74"/>
-      <c r="MV46" s="74"/>
-      <c r="MW46" s="74"/>
-      <c r="MX46" s="74"/>
-      <c r="MY46" s="74"/>
-      <c r="MZ46" s="74"/>
-      <c r="NA46" s="74"/>
-    </row>
-    <row r="47" spans="1:365" ht="30" customHeight="1">
-      <c r="B47" s="53"/>
-      <c r="C47" s="52"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17" t="str">
-        <f t="shared" ca="1" si="346"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:365" ht="30" customHeight="1">
-      <c r="B48" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C48" s="23"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="27" t="str">
-        <f t="shared" ca="1" si="346"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="3:7" ht="30" customHeight="1">
-      <c r="G49" s="6"/>
-    </row>
-    <row r="50" spans="3:7" ht="30" customHeight="1">
-      <c r="C50" s="14"/>
-      <c r="F50" s="43"/>
-    </row>
-    <row r="51" spans="3:7" ht="30" customHeight="1">
-      <c r="C51" s="15"/>
+    <row r="45" spans="1:365" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="55">
@@ -20344,7 +18021,7 @@
     <mergeCell ref="LS4:LY4"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
-  <conditionalFormatting sqref="D7:D48">
+  <conditionalFormatting sqref="D7:D42">
     <cfRule type="dataBar" priority="17">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -20358,32 +18035,17 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="KI29:KI30 KP31:KP32 KW31:KW32 LD33 LK33:LK34 MG5:ML34 MH35:ML35 LY35 I5:KH46 KJ5:KO46 KQ5:KV46 KX5:LC46 LE5:LJ46 LS5:LX46 LZ5:ME46 MN5:MS46 MU5:MZ46 MG36:ML46 LL5:LQ46">
-    <cfRule type="expression" dxfId="15" priority="36">
-      <formula>AND(TODAY()&gt;=I$5,TODAY()&lt;J$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="KI29:KI30 KP31:KP32 KW31:KW32 LD33 LK33:LK34 MG7:ML34 MH35:ML35 LY35 I7:KH46 KJ7:KO46 KQ7:KV46 KX7:LC46 LE7:LJ46 LS7:LX46 LZ7:ME46 MN7:MS46 MU7:MZ46 MG36:ML46 LL7:LQ46">
-    <cfRule type="expression" dxfId="14" priority="31" stopIfTrue="1">
-      <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7:NA32 I33:LB33 LE33:NA33 I34:NA34 MH35:NA35 I35:ME35 I36:NA46">
-    <cfRule type="expression" dxfId="13" priority="1">
+  <conditionalFormatting sqref="I32:ME32 MH32:NA32 I7:NA31 I33:NA40">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="KI5:KI36 KW5:KW36 LK5:LK36 LY5:LY36 MM5:MM36 NA5:NA36 LD5:LD32 MG35 KP5:KP46 KI39:KI46 KW39:KW46 LK39:LK46 MF5:MF46 LY39:LY46 MT5:MT46 MM39:MM46 NA39:NA46 LD34:LD46 LR5:LR46">
-    <cfRule type="expression" dxfId="12" priority="38">
+  <conditionalFormatting sqref="MG32 KI35:KI40 KW35:KW40 LK35:LK40 LY35:LY40 MM35:MM40 NA35:NA40 KI5:KI32 KW5:KW32 LK5:LK32 LY5:LY32 MM5:MM32 NA5:NA32 LD5:LD40 KP5:KP40 LR5:LR40 MF5:MF40 MT5:MT40">
+    <cfRule type="expression" dxfId="11" priority="38">
       <formula>AND(TODAY()&gt;=KI$5,TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="KI7:KI36 KW7:KW36 LK7:LK36 LY7:LY36 MM7:MM36 NA7:NA36 LD7:LD32 MG35 KP7:KP46 KI39:KI46 KW39:KW46 LK39:LK46 MF7:MF46 LY39:LY46 MT7:MT46 MM39:MM46 NA39:NA46 LD34:LD46 LR7:LR46">
-    <cfRule type="expression" dxfId="11" priority="42" stopIfTrue="1">
-      <formula>AND(task_end&gt;=KI$5,task_start&lt;#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="KI37:KI38 KW37:KW38 LK37:LK38 LY37:LY38 MM37:MM38">
+  <conditionalFormatting sqref="KI33:KI34 KW33:KW34 LK33:LK34 LY33:LY34 MM33:MM34">
     <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
       <formula>AND(task_end&gt;=KI$5,task_start&lt;KJ$5)</formula>
     </cfRule>
@@ -20391,47 +18053,45 @@
       <formula>AND(TODAY()&gt;=KI$5,TODAY()&lt;KJ$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="NA37:NA38">
-    <cfRule type="expression" dxfId="8" priority="44" stopIfTrue="1">
-      <formula>AND(task_end&gt;=NA$5,task_start&lt;#REF!)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="45">
-      <formula>AND(TODAY()&gt;=NA$5,TODAY()&lt;#REF!)</formula>
+  <conditionalFormatting sqref="MG32 KI35:KI40 KW35:KW40 LK35:LK40 LY35:LY40 MM35:MM40 KI7:KI32 KW7:KW32 LK7:LK32 LY7:LY32 MM7:MM32 LD7:LD40 KP7:KP40 LR7:LR40 MF7:MF40 MT7:MT40 NA7:NA40">
+    <cfRule type="expression" dxfId="8" priority="42" stopIfTrue="1">
+      <formula>AND(task_end&gt;=KI$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="LC33:LD33 MF35:MG35">
-    <cfRule type="expression" dxfId="6" priority="47">
-      <formula>AND(task_start&lt;=LD$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=LD$5)</formula>
+  <conditionalFormatting sqref="LR32">
+    <cfRule type="expression" dxfId="7" priority="57">
+      <formula>AND(TODAY()&gt;=LQ$5,TODAY()&lt;LR$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="59" stopIfTrue="1">
+      <formula>AND(task_end&gt;=LQ$5,task_start&lt;LR$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="LC33:LD33">
-    <cfRule type="expression" dxfId="5" priority="49">
-      <formula>AND(TODAY()&gt;=LD$5,TODAY()&lt;#REF!)</formula>
+  <conditionalFormatting sqref="MF32:MG32">
+    <cfRule type="expression" dxfId="5" priority="47">
+      <formula>AND(task_start&lt;=MG$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=MG$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="LC33:LD33">
-    <cfRule type="expression" dxfId="4" priority="51" stopIfTrue="1">
-      <formula>AND(task_end&gt;=LD$5,task_start&lt;#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="MF35:MG35">
-    <cfRule type="expression" dxfId="3" priority="53">
+  <conditionalFormatting sqref="MF32:MG32">
+    <cfRule type="expression" dxfId="4" priority="53">
       <formula>AND(TODAY()&gt;=MG$5,TODAY()&lt;MH$5)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="MF35:MG35">
-    <cfRule type="expression" dxfId="2" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="55" stopIfTrue="1">
       <formula>AND(task_end&gt;=MG$5,task_start&lt;MH$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="LR35">
-    <cfRule type="expression" dxfId="1" priority="57">
-      <formula>AND(TODAY()&gt;=LQ$5,TODAY()&lt;LR$5)</formula>
+  <conditionalFormatting sqref="KI27:KI28 KP29:KP30 KW29:KW30 LY32 MH32:ML32 LK31 MG5:ML31 MG33:ML40 I5:KH40 KJ5:KO40 KQ5:KV40 KX5:LC40 LE5:LJ40 LL5:LQ40 LS5:LX40 LZ5:ME40 MN5:MS40 MU5:MZ40">
+    <cfRule type="expression" dxfId="2" priority="36">
+      <formula>AND(TODAY()&gt;=I$5,TODAY()&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="LR35">
-    <cfRule type="expression" dxfId="0" priority="59" stopIfTrue="1">
-      <formula>AND(task_end&gt;=LQ$5,task_start&lt;LR$5)</formula>
+  <conditionalFormatting sqref="KI27:KI28 KP29:KP30 KW29:KW30 LY32 MH32:ML32 LK31 MG7:ML31 MG33:ML40 I7:KH40 KJ7:KO40 KQ7:KV40 KX7:LC40 LE7:LJ40 LL7:LQ40 LS7:LX40 LZ7:ME40 MN7:MS40 MU7:MZ40">
+    <cfRule type="expression" dxfId="1" priority="31" stopIfTrue="1">
+      <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="NA33:NA34">
+    <cfRule type="expression" dxfId="0" priority="45">
+      <formula>AND(TODAY()&gt;=NA$5,TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -20461,7 +18121,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D7:D48</xm:sqref>
+          <xm:sqref>D7:D42</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -20472,88 +18132,88 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="87.140625" style="31" customWidth="1"/>
     <col min="2" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="46.5" customHeight="1"/>
-    <row r="2" spans="1:2" s="33" customFormat="1" ht="15.75">
+    <row r="1" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:2" s="33" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B2" s="32"/>
     </row>
-    <row r="3" spans="1:2" s="37" customFormat="1" ht="27" customHeight="1">
+    <row r="3" spans="1:2" s="37" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B3" s="38"/>
     </row>
-    <row r="4" spans="1:2" s="34" customFormat="1" ht="26.25">
+    <row r="4" spans="1:2" s="34" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A4" s="35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="31" customFormat="1" ht="204.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="34" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A8" s="35" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+      <c r="A9" s="36" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="74.099999999999994" customHeight="1">
-      <c r="A5" s="36" t="s">
+    <row r="10" spans="1:2" s="31" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.25" customHeight="1">
-      <c r="A6" s="35" t="s">
+    <row r="11" spans="1:2" s="34" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A11" s="35" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="31" customFormat="1" ht="204.95" customHeight="1">
-      <c r="A7" s="40" t="s">
+    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A12" s="36" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="34" customFormat="1" ht="26.25">
-      <c r="A8" s="35" t="s">
+    <row r="13" spans="1:2" s="31" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="39" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="60">
-      <c r="A9" s="36" t="s">
+    <row r="14" spans="1:2" s="34" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A14" s="35" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="31" customFormat="1" ht="27.95" customHeight="1">
-      <c r="A10" s="39" t="s">
+    <row r="15" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="34" customFormat="1" ht="26.25">
-      <c r="A11" s="35" t="s">
+    <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+      <c r="A16" s="36" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30">
-      <c r="A12" s="36" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" s="31" customFormat="1" ht="27.95" customHeight="1">
-      <c r="A13" s="39" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" s="34" customFormat="1" ht="26.25">
-      <c r="A14" s="35" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="75" customHeight="1">
-      <c r="A15" s="36" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="75">
-      <c r="A16" s="36" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
